--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155327F7-7CE6-4345-8DC1-4FA2D2ECD3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC44113-6D2A-614C-8BF6-8010ABBA8C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48100" yWindow="-4660" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50860" yWindow="-4140" windowWidth="28800" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单支" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="1403">
   <si>
     <t>商品条码</t>
   </si>
@@ -4190,10 +4190,6 @@
     <t>CK 自由男士EDT100ml</t>
   </si>
   <si>
-    <t>否</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>伟博金萃高纯度鱼油1100毫克Omega-3 60粒</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -4296,10 +4292,6 @@
   </si>
   <si>
     <t>Helena Rubinstein 赫莲娜 黑绷带活颜修护晚霜100ml（50%玻色因）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -5749,7 +5741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K439"/>
+  <dimension ref="A1:K450"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.33203125" customWidth="1"/>
@@ -5764,7 +5756,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>883</v>
@@ -5773,7 +5765,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1315</v>
@@ -5791,19 +5783,19 @@
         <v>1084</v>
       </c>
       <c r="J1" s="32" t="s">
+        <v>1397</v>
+      </c>
+      <c r="K1" s="32" t="s">
         <v>1398</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15">
       <c r="A2" s="20">
-        <v>162.80000000000001</v>
+        <v>319</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="22" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="15" t="s">
@@ -5831,11 +5823,11 @@
     </row>
     <row r="3" spans="1:11" ht="15">
       <c r="A3" s="20">
-        <v>217.8</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="15" t="s">
@@ -5863,11 +5855,11 @@
     </row>
     <row r="4" spans="1:11" ht="15">
       <c r="A4" s="20">
-        <v>183.26</v>
+        <v>217.8</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="15" t="s">
@@ -5895,11 +5887,11 @@
     </row>
     <row r="5" spans="1:11" ht="15">
       <c r="A5" s="20">
-        <v>135</v>
+        <v>183.26</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="15" t="s">
@@ -5927,11 +5919,11 @@
     </row>
     <row r="6" spans="1:11" ht="15">
       <c r="A6" s="20">
-        <v>71.28</v>
+        <v>135</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="15" t="s">
@@ -5959,11 +5951,11 @@
     </row>
     <row r="7" spans="1:11" ht="15">
       <c r="A7" s="20">
-        <v>122.1</v>
+        <v>71.28</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D7" s="20"/>
       <c r="E7" s="15" t="s">
@@ -5991,11 +5983,11 @@
     </row>
     <row r="8" spans="1:11" ht="15">
       <c r="A8" s="20">
-        <v>460</v>
+        <v>122.1</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="15" t="s">
@@ -6023,11 +6015,11 @@
     </row>
     <row r="9" spans="1:11" ht="15">
       <c r="A9" s="20">
-        <v>274</v>
+        <v>460</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="15" t="s">
@@ -6055,11 +6047,11 @@
     </row>
     <row r="10" spans="1:11" ht="15">
       <c r="A10" s="20">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D10" s="26"/>
       <c r="E10" s="15" t="s">
@@ -6087,11 +6079,11 @@
     </row>
     <row r="11" spans="1:11" ht="15">
       <c r="A11" s="20">
-        <v>168.3</v>
+        <v>182</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="15" t="s">
@@ -6119,11 +6111,11 @@
     </row>
     <row r="12" spans="1:11" ht="15">
       <c r="A12" s="20">
-        <v>295</v>
+        <v>168.3</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="15" t="s">
@@ -6151,21 +6143,21 @@
     </row>
     <row r="13" spans="1:11" ht="15">
       <c r="A13" s="20">
-        <v>211.2</v>
+        <v>295</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="15" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>1379</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1380</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>1381</v>
       </c>
       <c r="H13" s="4">
         <f t="shared" si="1"/>
@@ -6183,11 +6175,11 @@
     </row>
     <row r="14" spans="1:11" ht="15">
       <c r="A14" s="20">
-        <v>294.89999999999998</v>
+        <v>211.2</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="15" t="s">
@@ -6215,11 +6207,11 @@
     </row>
     <row r="15" spans="1:11" ht="15">
       <c r="A15" s="20">
-        <v>236.5</v>
+        <v>294.89999999999998</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="15" t="s">
@@ -6247,11 +6239,11 @@
     </row>
     <row r="16" spans="1:11" ht="15">
       <c r="A16" s="20">
-        <v>295.89999999999998</v>
+        <v>236.5</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>898</v>
@@ -6278,11 +6270,11 @@
     </row>
     <row r="17" spans="1:11" ht="15">
       <c r="A17" s="20">
-        <v>220</v>
+        <v>295.89999999999998</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="15" t="s">
@@ -6310,11 +6302,11 @@
     </row>
     <row r="18" spans="1:11" ht="15">
       <c r="A18" s="20">
-        <v>88</v>
+        <v>220</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="15" t="s">
@@ -6342,11 +6334,11 @@
     </row>
     <row r="19" spans="1:11" ht="15">
       <c r="A19" s="20">
-        <v>59.9</v>
+        <v>88</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="15" t="s">
@@ -6378,11 +6370,11 @@
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="15" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>93</v>
@@ -6410,7 +6402,7 @@
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="15" t="s">
@@ -6442,7 +6434,7 @@
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="15" t="s">
@@ -6470,11 +6462,11 @@
     </row>
     <row r="23" spans="1:11" ht="15">
       <c r="A23" s="20">
-        <v>12.95</v>
+        <v>59.9</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="15" t="s">
@@ -6502,11 +6494,11 @@
     </row>
     <row r="24" spans="1:11" ht="15">
       <c r="A24" s="20">
-        <v>781</v>
+        <v>12.95</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="15" t="s">
@@ -6534,11 +6526,11 @@
     </row>
     <row r="25" spans="1:11" ht="15">
       <c r="A25" s="20">
-        <v>943.8</v>
+        <v>781</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="15" t="s">
@@ -6566,11 +6558,11 @@
     </row>
     <row r="26" spans="1:11" ht="15">
       <c r="A26" s="20">
-        <v>1017.5</v>
+        <v>943.8</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D26" s="26"/>
       <c r="E26" s="15" t="s">
@@ -6598,11 +6590,11 @@
     </row>
     <row r="27" spans="1:11" ht="15">
       <c r="A27" s="20">
-        <v>262.88</v>
+        <v>1017.5</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="15" t="s">
@@ -6630,11 +6622,11 @@
     </row>
     <row r="28" spans="1:11" ht="15">
       <c r="A28" s="20">
-        <v>931.7</v>
+        <v>262.88</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="15" t="s">
@@ -6662,21 +6654,21 @@
     </row>
     <row r="29" spans="1:11" ht="15">
       <c r="A29" s="20">
-        <v>1150</v>
+        <v>931.7</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="15" t="s">
         <v>906</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H29" s="4">
         <f>D29+1095</f>
@@ -6698,7 +6690,7 @@
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="15" t="s">
@@ -6726,11 +6718,11 @@
     </row>
     <row r="31" spans="1:11" ht="15">
       <c r="A31" s="20">
-        <v>1996</v>
+        <v>1150</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="15" t="s">
@@ -6758,11 +6750,11 @@
     </row>
     <row r="32" spans="1:11" ht="15">
       <c r="A32" s="20">
-        <v>1188</v>
+        <v>1996</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="15" t="s">
@@ -6790,11 +6782,11 @@
     </row>
     <row r="33" spans="1:11" ht="15">
       <c r="A33" s="20">
-        <v>310</v>
+        <v>1188</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="15" t="s">
@@ -6822,15 +6814,15 @@
     </row>
     <row r="34" spans="1:11" ht="15">
       <c r="A34" s="20">
-        <v>77.599999999999994</v>
+        <v>310</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="15" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>147</v>
@@ -6854,11 +6846,11 @@
     </row>
     <row r="35" spans="1:11" ht="15">
       <c r="A35" s="20">
-        <v>298</v>
+        <v>77.599999999999994</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="15" t="s">
@@ -6886,11 +6878,11 @@
     </row>
     <row r="36" spans="1:11" ht="15">
       <c r="A36" s="20">
-        <v>610</v>
+        <v>298</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="15" t="s">
@@ -6918,11 +6910,11 @@
     </row>
     <row r="37" spans="1:11" ht="15">
       <c r="A37" s="20">
-        <v>158</v>
+        <v>610</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="15" t="s">
@@ -6950,11 +6942,11 @@
     </row>
     <row r="38" spans="1:11" ht="15">
       <c r="A38" s="20">
-        <v>1593.9</v>
+        <v>158</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="15" t="s">
@@ -6982,11 +6974,11 @@
     </row>
     <row r="39" spans="1:11" ht="15">
       <c r="A39" s="20">
-        <v>325</v>
+        <v>1593.9</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="15" t="s">
@@ -7014,11 +7006,11 @@
     </row>
     <row r="40" spans="1:11" ht="15">
       <c r="A40" s="20">
-        <v>38.85</v>
+        <v>325</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="15" t="s">
@@ -7046,11 +7038,11 @@
     </row>
     <row r="41" spans="1:11" ht="15">
       <c r="A41" s="20">
-        <v>228</v>
+        <v>38.85</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="15" t="s">
@@ -7078,11 +7070,11 @@
     </row>
     <row r="42" spans="1:11" ht="15">
       <c r="A42" s="20">
-        <v>140.36000000000001</v>
+        <v>228</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>159</v>
@@ -7113,7 +7105,7 @@
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="15" t="s">
@@ -7141,11 +7133,11 @@
     </row>
     <row r="44" spans="1:11" ht="15">
       <c r="A44" s="20">
-        <v>501.27</v>
+        <v>140.36000000000001</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="15" t="s">
@@ -7173,11 +7165,11 @@
     </row>
     <row r="45" spans="1:11" ht="15">
       <c r="A45" s="20">
-        <v>219</v>
+        <v>501.27</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D45" s="20"/>
       <c r="E45" s="15" t="s">
@@ -7205,11 +7197,11 @@
     </row>
     <row r="46" spans="1:11" ht="15">
       <c r="A46" s="20">
-        <v>324.5</v>
+        <v>219</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="15" t="s">
@@ -7237,11 +7229,11 @@
     </row>
     <row r="47" spans="1:11" ht="15">
       <c r="A47" s="20">
-        <v>286</v>
+        <v>324.5</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="15" t="s">
@@ -7269,11 +7261,11 @@
     </row>
     <row r="48" spans="1:11" ht="15">
       <c r="A48" s="20">
-        <v>476.3</v>
+        <v>286</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D48" s="26"/>
       <c r="E48" s="15" t="s">
@@ -7301,11 +7293,11 @@
     </row>
     <row r="49" spans="1:11" ht="15">
       <c r="A49" s="20">
-        <v>299</v>
+        <v>476.3</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D49" s="26"/>
       <c r="E49" s="15" t="s">
@@ -7333,11 +7325,11 @@
     </row>
     <row r="50" spans="1:11" ht="15">
       <c r="A50" s="20">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="15" t="s">
@@ -7365,11 +7357,11 @@
     </row>
     <row r="51" spans="1:11" ht="15">
       <c r="A51" s="20">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D51" s="20"/>
       <c r="E51" s="15" t="s">
@@ -7397,11 +7389,11 @@
     </row>
     <row r="52" spans="1:11" ht="15">
       <c r="A52" s="20">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D52" s="26"/>
       <c r="E52" s="15" t="s">
@@ -7429,11 +7421,11 @@
     </row>
     <row r="53" spans="1:11" ht="15">
       <c r="A53" s="20">
-        <v>271.7</v>
+        <v>315</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="15" t="s">
@@ -7461,11 +7453,11 @@
     </row>
     <row r="54" spans="1:11" ht="15">
       <c r="A54" s="20">
-        <v>399</v>
+        <v>271.7</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D54" s="26"/>
       <c r="E54" s="15" t="s">
@@ -7493,11 +7485,11 @@
     </row>
     <row r="55" spans="1:11" ht="15">
       <c r="A55" s="20">
-        <v>544.5</v>
+        <v>399</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D55" s="26"/>
       <c r="E55" s="15" t="s">
@@ -7525,11 +7517,11 @@
     </row>
     <row r="56" spans="1:11" ht="15">
       <c r="A56" s="20">
-        <v>645.70000000000005</v>
+        <v>544.5</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D56" s="25"/>
       <c r="E56" s="15" t="s">
@@ -7557,11 +7549,11 @@
     </row>
     <row r="57" spans="1:11" ht="15">
       <c r="A57" s="20">
-        <v>327.47000000000003</v>
+        <v>645.70000000000005</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="15" t="s">
@@ -7589,11 +7581,11 @@
     </row>
     <row r="58" spans="1:11" ht="15">
       <c r="A58" s="20">
-        <v>125</v>
+        <v>327.47000000000003</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D58" s="25"/>
       <c r="E58" s="15" t="s">
@@ -7621,11 +7613,11 @@
     </row>
     <row r="59" spans="1:11" ht="15">
       <c r="A59" s="20">
-        <v>163.79</v>
+        <v>125</v>
       </c>
       <c r="B59" s="20"/>
       <c r="C59" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D59" s="20"/>
       <c r="E59" s="15" t="s">
@@ -7653,11 +7645,11 @@
     </row>
     <row r="60" spans="1:11" ht="15">
       <c r="A60" s="20">
-        <v>137.06</v>
+        <v>163.79</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D60" s="25"/>
       <c r="E60" s="15" t="s">
@@ -7685,11 +7677,11 @@
     </row>
     <row r="61" spans="1:11" ht="15">
       <c r="A61" s="20">
-        <v>76</v>
+        <v>137.06</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D61" s="20"/>
       <c r="E61" s="15" t="s">
@@ -7717,11 +7709,11 @@
     </row>
     <row r="62" spans="1:11" ht="15">
       <c r="A62" s="20">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="15" t="s">
@@ -7749,11 +7741,11 @@
     </row>
     <row r="63" spans="1:11" ht="15">
       <c r="A63" s="20">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D63" s="26"/>
       <c r="E63" s="15" t="s">
@@ -7781,11 +7773,11 @@
     </row>
     <row r="64" spans="1:11" ht="15">
       <c r="A64" s="20">
-        <v>56.9</v>
+        <v>170</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D64" s="26"/>
       <c r="E64" s="15" t="s">
@@ -7813,11 +7805,11 @@
     </row>
     <row r="65" spans="1:11" ht="15">
       <c r="A65" s="20">
-        <v>203.5</v>
+        <v>56.9</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D65" s="20"/>
       <c r="E65" s="15" t="s">
@@ -7845,11 +7837,11 @@
     </row>
     <row r="66" spans="1:11" ht="15">
       <c r="A66" s="20">
-        <v>196</v>
+        <v>203.5</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D66" s="20"/>
       <c r="E66" s="15" t="s">
@@ -7877,11 +7869,11 @@
     </row>
     <row r="67" spans="1:11" ht="15">
       <c r="A67" s="20">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D67" s="25"/>
       <c r="E67" s="15" t="s">
@@ -7909,11 +7901,11 @@
     </row>
     <row r="68" spans="1:11" ht="15">
       <c r="A68" s="20">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="15" t="s">
@@ -7941,11 +7933,11 @@
     </row>
     <row r="69" spans="1:11" ht="15">
       <c r="A69" s="20">
-        <v>2167.6999999999998</v>
+        <v>176</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="15" t="s">
@@ -7973,11 +7965,11 @@
     </row>
     <row r="70" spans="1:11" ht="15">
       <c r="A70" s="20">
-        <v>114.18</v>
+        <v>2167.6999999999998</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D70" s="25"/>
       <c r="E70" s="15" t="s">
@@ -8005,11 +7997,11 @@
     </row>
     <row r="71" spans="1:11" ht="15">
       <c r="A71" s="20">
-        <v>94.5</v>
+        <v>114.18</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D71" s="25"/>
       <c r="E71" s="15" t="s">
@@ -8037,11 +8029,11 @@
     </row>
     <row r="72" spans="1:11" ht="15">
       <c r="A72" s="20">
-        <v>106</v>
+        <v>94.5</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D72" s="25"/>
       <c r="E72" s="15" t="s">
@@ -8069,11 +8061,11 @@
     </row>
     <row r="73" spans="1:11" ht="15">
       <c r="A73" s="20">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D73" s="20"/>
       <c r="E73" s="15" t="s">
@@ -8105,7 +8097,7 @@
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D74" s="20"/>
       <c r="E74" s="15" t="s">
@@ -8133,11 +8125,11 @@
     </row>
     <row r="75" spans="1:11" ht="15">
       <c r="A75" s="20">
-        <v>468</v>
+        <v>139</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="15" t="s">
@@ -8165,11 +8157,11 @@
     </row>
     <row r="76" spans="1:11" ht="15">
       <c r="A76" s="20">
-        <v>218</v>
+        <v>468</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D76" s="25"/>
       <c r="E76" s="15" t="s">
@@ -8197,11 +8189,11 @@
     </row>
     <row r="77" spans="1:11" ht="15">
       <c r="A77" s="20">
-        <v>390</v>
+        <v>218</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D77" s="20"/>
       <c r="E77" s="15" t="s">
@@ -8229,11 +8221,11 @@
     </row>
     <row r="78" spans="1:11" ht="15">
       <c r="A78" s="20">
-        <v>191.1</v>
+        <v>390</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D78" s="25"/>
       <c r="E78" s="15" t="s">
@@ -8261,11 +8253,11 @@
     </row>
     <row r="79" spans="1:11" ht="15">
       <c r="A79" s="20">
-        <v>390</v>
+        <v>191.1</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D79" s="25"/>
       <c r="E79" s="15" t="s">
@@ -8293,11 +8285,11 @@
     </row>
     <row r="80" spans="1:11" ht="15">
       <c r="A80" s="20">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="B80" s="20"/>
       <c r="C80" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="15" t="s">
@@ -8325,11 +8317,11 @@
     </row>
     <row r="81" spans="1:11" ht="15">
       <c r="A81" s="20">
-        <v>110.13</v>
+        <v>128</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D81" s="25"/>
       <c r="E81" s="15" t="s">
@@ -8357,11 +8349,11 @@
     </row>
     <row r="82" spans="1:11" ht="15">
       <c r="A82" s="20">
-        <v>94</v>
+        <v>110.13</v>
       </c>
       <c r="B82" s="20"/>
       <c r="C82" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D82" s="25"/>
       <c r="E82" s="15" t="s">
@@ -8389,11 +8381,11 @@
     </row>
     <row r="83" spans="1:11" ht="15">
       <c r="A83" s="20">
-        <v>243</v>
+        <v>94</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D83" s="20"/>
       <c r="E83" s="15" t="s">
@@ -8421,11 +8413,11 @@
     </row>
     <row r="84" spans="1:11" ht="15">
       <c r="A84" s="20">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D84" s="25"/>
       <c r="E84" s="15" t="s">
@@ -8453,11 +8445,11 @@
     </row>
     <row r="85" spans="1:11" ht="15">
       <c r="A85" s="20">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B85" s="20"/>
       <c r="C85" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="15" t="s">
@@ -8485,11 +8477,11 @@
     </row>
     <row r="86" spans="1:11" ht="15">
       <c r="A86" s="20">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="15" t="s">
@@ -8517,11 +8509,11 @@
     </row>
     <row r="87" spans="1:11" ht="15">
       <c r="A87" s="20">
-        <v>97.8</v>
+        <v>110</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D87" s="20"/>
       <c r="E87" s="15" t="s">
@@ -8549,11 +8541,11 @@
     </row>
     <row r="88" spans="1:11" ht="15">
       <c r="A88" s="20">
-        <v>84.99</v>
+        <v>97.8</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D88" s="25"/>
       <c r="E88" s="15" t="s">
@@ -8581,11 +8573,11 @@
     </row>
     <row r="89" spans="1:11" ht="15">
       <c r="A89" s="20">
-        <v>68.2</v>
+        <v>84.99</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D89" s="25"/>
       <c r="E89" s="15" t="s">
@@ -8613,11 +8605,11 @@
     </row>
     <row r="90" spans="1:11" ht="15">
       <c r="A90" s="20">
-        <v>335</v>
+        <v>68.2</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D90" s="25"/>
       <c r="E90" s="15" t="s">
@@ -8645,11 +8637,11 @@
     </row>
     <row r="91" spans="1:11" ht="15">
       <c r="A91" s="20">
-        <v>122.9</v>
+        <v>335</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D91" s="26"/>
       <c r="E91" s="15" t="s">
@@ -8677,11 +8669,11 @@
     </row>
     <row r="92" spans="1:11" ht="15">
       <c r="A92" s="20">
-        <v>169</v>
+        <v>122.9</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D92" s="25"/>
       <c r="E92" s="15" t="s">
@@ -8709,11 +8701,11 @@
     </row>
     <row r="93" spans="1:11" ht="15">
       <c r="A93" s="20">
-        <v>480</v>
+        <v>169</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D93" s="25"/>
       <c r="E93" s="15" t="s">
@@ -8741,11 +8733,11 @@
     </row>
     <row r="94" spans="1:11" ht="15">
       <c r="A94" s="20">
-        <v>103.9</v>
+        <v>480</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D94" s="25"/>
       <c r="E94" s="15" t="s">
@@ -8773,11 +8765,11 @@
     </row>
     <row r="95" spans="1:11" ht="15">
       <c r="A95" s="20">
-        <v>169</v>
+        <v>103.9</v>
       </c>
       <c r="B95" s="20"/>
       <c r="C95" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D95" s="25"/>
       <c r="E95" s="15" t="s">
@@ -8805,11 +8797,11 @@
     </row>
     <row r="96" spans="1:11" ht="15">
       <c r="A96" s="20">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="B96" s="20"/>
       <c r="C96" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="15" t="s">
@@ -8837,11 +8829,11 @@
     </row>
     <row r="97" spans="1:11" ht="15">
       <c r="A97" s="20">
-        <v>319</v>
+        <v>239</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="15" t="s">
@@ -8869,11 +8861,11 @@
     </row>
     <row r="98" spans="1:11" ht="15">
       <c r="A98" s="20">
-        <v>205.81</v>
+        <v>319</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="15" t="s">
@@ -8901,11 +8893,11 @@
     </row>
     <row r="99" spans="1:11" ht="15">
       <c r="A99" s="20">
-        <v>292</v>
+        <v>205.81</v>
       </c>
       <c r="B99" s="20"/>
       <c r="C99" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D99" s="25"/>
       <c r="E99" s="15" t="s">
@@ -8933,11 +8925,11 @@
     </row>
     <row r="100" spans="1:11" ht="15">
       <c r="A100" s="20">
-        <v>1109</v>
+        <v>292</v>
       </c>
       <c r="B100" s="20"/>
       <c r="C100" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D100" s="20"/>
       <c r="E100" s="15" t="s">
@@ -8965,11 +8957,11 @@
     </row>
     <row r="101" spans="1:11" ht="15">
       <c r="A101" s="20">
-        <v>683.65</v>
+        <v>1109</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D101" s="25"/>
       <c r="E101" s="15" t="s">
@@ -8997,11 +8989,11 @@
     </row>
     <row r="102" spans="1:11" ht="15">
       <c r="A102" s="20">
-        <v>1454.2</v>
+        <v>683.65</v>
       </c>
       <c r="B102" s="20"/>
       <c r="C102" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D102" s="25"/>
       <c r="E102" s="15" t="s">
@@ -9029,11 +9021,11 @@
     </row>
     <row r="103" spans="1:11" ht="15">
       <c r="A103" s="20">
-        <v>968</v>
+        <v>1454.2</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D103" s="25"/>
       <c r="E103" s="15" t="s">
@@ -9061,11 +9053,11 @@
     </row>
     <row r="104" spans="1:11" ht="15">
       <c r="A104" s="20">
-        <v>1999</v>
+        <v>968</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D104" s="25"/>
       <c r="E104" s="15" t="s">
@@ -9093,11 +9085,11 @@
     </row>
     <row r="105" spans="1:11" ht="15">
       <c r="A105" s="20">
-        <v>686</v>
+        <v>1999</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D105" s="25"/>
       <c r="E105" s="15" t="s">
@@ -9125,11 +9117,11 @@
     </row>
     <row r="106" spans="1:11" ht="15">
       <c r="A106" s="20">
-        <v>1947</v>
+        <v>686</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D106" s="25"/>
       <c r="E106" s="15" t="s">
@@ -9157,11 +9149,11 @@
     </row>
     <row r="107" spans="1:11" ht="15">
       <c r="A107" s="20">
-        <v>2775.3</v>
+        <v>1947</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D107" s="25"/>
       <c r="E107" s="15" t="s">
@@ -9188,10 +9180,12 @@
       </c>
     </row>
     <row r="108" spans="1:11" ht="15">
-      <c r="A108" s="20"/>
+      <c r="A108" s="20">
+        <v>2775.3</v>
+      </c>
       <c r="B108" s="20"/>
       <c r="C108" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D108" s="25"/>
       <c r="E108" s="15" t="s">
@@ -9218,12 +9212,10 @@
       </c>
     </row>
     <row r="109" spans="1:11" ht="15">
-      <c r="A109" s="20">
-        <v>2180</v>
-      </c>
+      <c r="A109" s="20"/>
       <c r="B109" s="28"/>
       <c r="C109" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E109" s="15" t="s">
         <v>342</v>
@@ -9250,11 +9242,11 @@
     </row>
     <row r="110" spans="1:11" ht="15">
       <c r="A110" s="20">
-        <v>856.9</v>
+        <v>2180</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D110" s="20"/>
       <c r="E110" s="15" t="s">
@@ -9282,11 +9274,11 @@
     </row>
     <row r="111" spans="1:11" ht="15">
       <c r="A111" s="20">
-        <v>789</v>
+        <v>856.9</v>
       </c>
       <c r="B111" s="20"/>
       <c r="C111" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D111" s="25"/>
       <c r="E111" s="15" t="s">
@@ -9314,11 +9306,11 @@
     </row>
     <row r="112" spans="1:11" ht="15">
       <c r="A112" s="20">
-        <v>84.59</v>
+        <v>789</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D112" s="25"/>
       <c r="E112" s="15" t="s">
@@ -9346,11 +9338,11 @@
     </row>
     <row r="113" spans="1:11" ht="15">
       <c r="A113" s="20">
-        <v>63.3</v>
+        <v>84.59</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D113" s="25"/>
       <c r="E113" s="15" t="s">
@@ -9378,11 +9370,11 @@
     </row>
     <row r="114" spans="1:11" ht="15">
       <c r="A114" s="20">
-        <v>77.44</v>
+        <v>63.3</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D114" s="25"/>
       <c r="E114" s="15" t="s">
@@ -9410,11 +9402,11 @@
     </row>
     <row r="115" spans="1:11" ht="15">
       <c r="A115" s="20">
-        <v>98</v>
+        <v>77.44</v>
       </c>
       <c r="B115" s="20"/>
       <c r="C115" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D115" s="20"/>
       <c r="E115" s="15" t="s">
@@ -9442,11 +9434,11 @@
     </row>
     <row r="116" spans="1:11" ht="15">
       <c r="A116" s="20">
-        <v>62.7</v>
+        <v>98</v>
       </c>
       <c r="B116" s="20"/>
       <c r="C116" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D116" s="25"/>
       <c r="E116" s="15" t="s">
@@ -9474,11 +9466,11 @@
     </row>
     <row r="117" spans="1:11" ht="15">
       <c r="A117" s="20">
-        <v>106.7</v>
+        <v>62.7</v>
       </c>
       <c r="B117" s="20"/>
       <c r="C117" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D117" s="25"/>
       <c r="E117" s="15" t="s">
@@ -9506,11 +9498,11 @@
     </row>
     <row r="118" spans="1:11" ht="15">
       <c r="A118" s="20">
-        <v>198</v>
+        <v>106.7</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D118" s="25"/>
       <c r="E118" s="15" t="s">
@@ -9538,11 +9530,11 @@
     </row>
     <row r="119" spans="1:11" ht="15">
       <c r="A119" s="20">
-        <v>79.989999999999995</v>
+        <v>198</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D119" s="25"/>
       <c r="E119" s="15" t="s">
@@ -9570,11 +9562,11 @@
     </row>
     <row r="120" spans="1:11" ht="15">
       <c r="A120" s="20">
-        <v>153</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D120" s="25"/>
       <c r="E120" s="15" t="s">
@@ -9602,11 +9594,11 @@
     </row>
     <row r="121" spans="1:11" ht="15">
       <c r="A121" s="20">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D121" s="25"/>
       <c r="E121" s="15" t="s">
@@ -9634,11 +9626,11 @@
     </row>
     <row r="122" spans="1:11" ht="15">
       <c r="A122" s="20">
-        <v>125.24</v>
+        <v>198</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D122" s="25"/>
       <c r="E122" s="15" t="s">
@@ -9666,11 +9658,11 @@
     </row>
     <row r="123" spans="1:11" ht="15">
       <c r="A123" s="20">
-        <v>136.5</v>
+        <v>125.24</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D123" s="20"/>
       <c r="E123" s="15" t="s">
@@ -9698,11 +9690,11 @@
     </row>
     <row r="124" spans="1:11" ht="15">
       <c r="A124" s="20">
-        <v>238</v>
+        <v>136.5</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D124" s="25"/>
       <c r="E124" s="15" t="s">
@@ -9730,11 +9722,11 @@
     </row>
     <row r="125" spans="1:11" ht="15">
       <c r="A125" s="20">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D125" s="25"/>
       <c r="E125" s="15" t="s">
@@ -9762,11 +9754,11 @@
     </row>
     <row r="126" spans="1:11" ht="15">
       <c r="A126" s="20">
-        <v>482.35</v>
+        <v>180</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D126" s="25"/>
       <c r="E126" s="15" t="s">
@@ -9794,11 +9786,11 @@
     </row>
     <row r="127" spans="1:11" ht="15">
       <c r="A127" s="20">
-        <v>299</v>
+        <v>482.35</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D127" s="25"/>
       <c r="E127" s="15" t="s">
@@ -9826,11 +9818,11 @@
     </row>
     <row r="128" spans="1:11" ht="15">
       <c r="A128" s="20">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D128" s="25"/>
       <c r="E128" s="15" t="s">
@@ -9858,11 +9850,11 @@
     </row>
     <row r="129" spans="1:11" ht="15">
       <c r="A129" s="20">
-        <v>476.3</v>
+        <v>245</v>
       </c>
       <c r="B129" s="20"/>
       <c r="C129" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D129" s="25"/>
       <c r="E129" s="15" t="s">
@@ -9890,11 +9882,11 @@
     </row>
     <row r="130" spans="1:11" ht="15">
       <c r="A130" s="20">
-        <v>240</v>
+        <v>476.3</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D130" s="25"/>
       <c r="E130" s="15" t="s">
@@ -9922,11 +9914,11 @@
     </row>
     <row r="131" spans="1:11" ht="15">
       <c r="A131" s="20">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D131" s="25"/>
       <c r="E131" s="15" t="s">
@@ -9954,11 +9946,11 @@
     </row>
     <row r="132" spans="1:11" ht="15">
       <c r="A132" s="20">
-        <v>122.5</v>
+        <v>259</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D132" s="25"/>
       <c r="E132" s="15" t="s">
@@ -9986,11 +9978,11 @@
     </row>
     <row r="133" spans="1:11" ht="15">
       <c r="A133" s="20">
-        <v>187</v>
+        <v>122.5</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D133" s="25"/>
       <c r="E133" s="15" t="s">
@@ -10018,11 +10010,11 @@
     </row>
     <row r="134" spans="1:11" ht="15">
       <c r="A134" s="20">
-        <v>111.74</v>
+        <v>187</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D134" s="25"/>
       <c r="E134" s="15" t="s">
@@ -10050,11 +10042,11 @@
     </row>
     <row r="135" spans="1:11" ht="15">
       <c r="A135" s="20">
-        <v>318.39999999999998</v>
+        <v>111.74</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D135" s="20"/>
       <c r="E135" s="15" t="s">
@@ -10082,11 +10074,11 @@
     </row>
     <row r="136" spans="1:11" ht="15">
       <c r="A136" s="20">
-        <v>129.93</v>
+        <v>318.39999999999998</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D136" s="20"/>
       <c r="E136" s="15" t="s">
@@ -10114,11 +10106,11 @@
     </row>
     <row r="137" spans="1:11" ht="15">
       <c r="A137" s="20">
-        <v>112.75</v>
+        <v>129.93</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D137" s="20"/>
       <c r="E137" s="15" t="s">
@@ -10146,11 +10138,11 @@
     </row>
     <row r="138" spans="1:11" ht="15">
       <c r="A138" s="20">
-        <v>239.8</v>
+        <v>112.75</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D138" s="25"/>
       <c r="E138" s="15" t="s">
@@ -10178,11 +10170,11 @@
     </row>
     <row r="139" spans="1:11" ht="15">
       <c r="A139" s="20">
-        <v>399.97</v>
+        <v>239.8</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D139" s="25"/>
       <c r="E139" s="15" t="s">
@@ -10210,11 +10202,11 @@
     </row>
     <row r="140" spans="1:11" ht="15">
       <c r="A140" s="20">
-        <v>328.5</v>
+        <v>399.97</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D140" s="25"/>
       <c r="E140" s="15" t="s">
@@ -10242,11 +10234,11 @@
     </row>
     <row r="141" spans="1:11" ht="15">
       <c r="A141" s="20">
-        <v>164.89</v>
+        <v>328.5</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D141" s="25"/>
       <c r="E141" s="15" t="s">
@@ -10274,11 +10266,11 @@
     </row>
     <row r="142" spans="1:11" ht="15">
       <c r="A142" s="20">
-        <v>100.1</v>
+        <v>164.89</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D142" s="25"/>
       <c r="E142" s="15" t="s">
@@ -10306,11 +10298,11 @@
     </row>
     <row r="143" spans="1:11" ht="15">
       <c r="A143" s="20">
-        <v>139</v>
+        <v>100.1</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D143" s="25"/>
       <c r="E143" s="15" t="s">
@@ -10338,11 +10330,11 @@
     </row>
     <row r="144" spans="1:11" ht="15">
       <c r="A144" s="20">
-        <v>859</v>
+        <v>139</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D144" s="25"/>
       <c r="E144" s="15" t="s">
@@ -10370,11 +10362,11 @@
     </row>
     <row r="145" spans="1:11" ht="15">
       <c r="A145" s="20">
-        <v>288</v>
+        <v>859</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D145" s="20"/>
       <c r="E145" s="15" t="s">
@@ -10402,11 +10394,11 @@
     </row>
     <row r="146" spans="1:11" ht="15">
       <c r="A146" s="20">
-        <v>2736.8</v>
+        <v>66</v>
       </c>
       <c r="B146" s="20"/>
       <c r="C146" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D146" s="25"/>
       <c r="E146" s="15" t="s">
@@ -10434,11 +10426,11 @@
     </row>
     <row r="147" spans="1:11" ht="15">
       <c r="A147" s="20">
-        <v>173.8</v>
+        <v>2736.8</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D147" s="25"/>
       <c r="E147" s="15" t="s">
@@ -10466,11 +10458,11 @@
     </row>
     <row r="148" spans="1:11" ht="15">
       <c r="A148" s="20">
-        <v>487</v>
+        <v>173.8</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D148" s="25"/>
       <c r="E148" s="15" t="s">
@@ -10498,11 +10490,11 @@
     </row>
     <row r="149" spans="1:11" ht="15">
       <c r="A149" s="20">
-        <v>550</v>
+        <v>487</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D149" s="20"/>
       <c r="E149" s="15" t="s">
@@ -10530,11 +10522,11 @@
     </row>
     <row r="150" spans="1:11" ht="15">
       <c r="A150" s="20">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="B150" s="20"/>
       <c r="C150" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D150" s="25"/>
       <c r="E150" s="15" t="s">
@@ -10562,11 +10554,11 @@
     </row>
     <row r="151" spans="1:11" ht="15">
       <c r="A151" s="20">
-        <v>147</v>
+        <v>479</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D151" s="20"/>
       <c r="E151" s="15" t="s">
@@ -10594,11 +10586,11 @@
     </row>
     <row r="152" spans="1:11" ht="15">
       <c r="A152" s="20">
-        <v>184.5</v>
+        <v>147</v>
       </c>
       <c r="B152" s="20"/>
       <c r="C152" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D152" s="25"/>
       <c r="E152" s="15" t="s">
@@ -10626,11 +10618,11 @@
     </row>
     <row r="153" spans="1:11" ht="15">
       <c r="A153" s="20">
-        <v>380</v>
+        <v>184.5</v>
       </c>
       <c r="B153" s="20"/>
       <c r="C153" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D153" s="25"/>
       <c r="E153" s="15" t="s">
@@ -10658,11 +10650,11 @@
     </row>
     <row r="154" spans="1:11" ht="15">
       <c r="A154" s="20">
-        <v>259</v>
+        <v>380</v>
       </c>
       <c r="B154" s="20"/>
       <c r="C154" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D154" s="20"/>
       <c r="E154" s="15" t="s">
@@ -10690,11 +10682,11 @@
     </row>
     <row r="155" spans="1:11" ht="15">
       <c r="A155" s="20">
-        <v>444</v>
+        <v>259</v>
       </c>
       <c r="B155" s="20"/>
       <c r="C155" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D155" s="25"/>
       <c r="E155" s="15" t="s">
@@ -10722,11 +10714,11 @@
     </row>
     <row r="156" spans="1:11" ht="15">
       <c r="A156" s="20">
-        <v>159</v>
+        <v>444</v>
       </c>
       <c r="B156" s="20"/>
       <c r="C156" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D156" s="25"/>
       <c r="E156" s="15" t="s">
@@ -10754,11 +10746,11 @@
     </row>
     <row r="157" spans="1:11" ht="15">
       <c r="A157" s="20">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="B157" s="20"/>
       <c r="C157" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D157" s="20"/>
       <c r="E157" s="15" t="s">
@@ -10786,11 +10778,11 @@
     </row>
     <row r="158" spans="1:11" ht="15">
       <c r="A158" s="20">
-        <v>304.5</v>
+        <v>259</v>
       </c>
       <c r="B158" s="20"/>
       <c r="C158" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D158" s="25"/>
       <c r="E158" s="15" t="s">
@@ -10818,11 +10810,11 @@
     </row>
     <row r="159" spans="1:11" ht="15">
       <c r="A159" s="20">
-        <v>419</v>
+        <v>304.5</v>
       </c>
       <c r="B159" s="20"/>
       <c r="C159" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D159" s="25"/>
       <c r="E159" s="15" t="s">
@@ -10850,11 +10842,11 @@
     </row>
     <row r="160" spans="1:11" ht="15">
       <c r="A160" s="20">
-        <v>329</v>
+        <v>419</v>
       </c>
       <c r="B160" s="20"/>
       <c r="C160" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D160" s="25"/>
       <c r="E160" s="15" t="s">
@@ -10882,11 +10874,11 @@
     </row>
     <row r="161" spans="1:11" ht="15">
       <c r="A161" s="20">
-        <v>760</v>
+        <v>329</v>
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D161" s="25"/>
       <c r="E161" s="15" t="s">
@@ -10914,11 +10906,11 @@
     </row>
     <row r="162" spans="1:11" ht="15">
       <c r="A162" s="20">
-        <v>230</v>
+        <v>760</v>
       </c>
       <c r="B162" s="20"/>
       <c r="C162" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D162" s="25"/>
       <c r="E162" s="15" t="s">
@@ -10946,11 +10938,11 @@
     </row>
     <row r="163" spans="1:11" ht="15">
       <c r="A163" s="20">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B163" s="20"/>
       <c r="C163" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D163" s="20"/>
       <c r="E163" s="15" t="s">
@@ -10978,11 +10970,11 @@
     </row>
     <row r="164" spans="1:11" ht="15">
       <c r="A164" s="20">
-        <v>100.98</v>
+        <v>209</v>
       </c>
       <c r="B164" s="20"/>
       <c r="C164" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D164" s="26"/>
       <c r="E164" s="15" t="s">
@@ -11010,11 +11002,11 @@
     </row>
     <row r="165" spans="1:11" ht="15">
       <c r="A165" s="20">
-        <v>389.4</v>
+        <v>100.98</v>
       </c>
       <c r="B165" s="20"/>
       <c r="C165" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D165" s="25"/>
       <c r="E165" s="15" t="s">
@@ -11042,11 +11034,11 @@
     </row>
     <row r="166" spans="1:11" ht="15">
       <c r="A166" s="20">
-        <v>298.10000000000002</v>
+        <v>389.4</v>
       </c>
       <c r="B166" s="20"/>
       <c r="C166" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D166" s="26"/>
       <c r="E166" s="15" t="s">
@@ -11074,11 +11066,11 @@
     </row>
     <row r="167" spans="1:11" ht="15">
       <c r="A167" s="20">
-        <v>75</v>
+        <v>298.10000000000002</v>
       </c>
       <c r="B167" s="20"/>
       <c r="C167" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D167" s="26"/>
       <c r="E167" s="15" t="s">
@@ -11106,11 +11098,11 @@
     </row>
     <row r="168" spans="1:11" ht="15">
       <c r="A168" s="20">
-        <v>589</v>
+        <v>75</v>
       </c>
       <c r="B168" s="20"/>
       <c r="C168" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D168" s="20"/>
       <c r="E168" s="15" t="s">
@@ -11138,11 +11130,11 @@
     </row>
     <row r="169" spans="1:11" ht="15">
       <c r="A169" s="20">
-        <v>477.4</v>
+        <v>589</v>
       </c>
       <c r="B169" s="20"/>
       <c r="C169" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D169" s="26"/>
       <c r="E169" s="15" t="s">
@@ -11170,11 +11162,11 @@
     </row>
     <row r="170" spans="1:11" ht="15">
       <c r="A170" s="20">
-        <v>259</v>
+        <v>477.4</v>
       </c>
       <c r="B170" s="20"/>
       <c r="C170" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E170" s="15" t="s">
         <v>980</v>
@@ -11201,11 +11193,11 @@
     </row>
     <row r="171" spans="1:11" ht="15">
       <c r="A171" s="20">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D171" s="25"/>
       <c r="E171" s="15" t="s">
@@ -11233,11 +11225,11 @@
     </row>
     <row r="172" spans="1:11" ht="15">
       <c r="A172" s="20">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="B172" s="20"/>
       <c r="C172" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D172" s="20"/>
       <c r="E172" s="15" t="s">
@@ -11264,10 +11256,12 @@
       </c>
     </row>
     <row r="173" spans="1:11" ht="15">
-      <c r="A173" s="20"/>
+      <c r="A173" s="20">
+        <v>259</v>
+      </c>
       <c r="B173" s="20"/>
       <c r="C173" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D173" s="25"/>
       <c r="E173" s="15" t="s">
@@ -11294,12 +11288,10 @@
       </c>
     </row>
     <row r="174" spans="1:11" ht="15">
-      <c r="A174" s="20">
-        <v>15.29</v>
-      </c>
+      <c r="A174" s="20"/>
       <c r="B174" s="28"/>
       <c r="C174" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D174" s="26"/>
       <c r="E174" s="15" t="s">
@@ -11327,11 +11319,11 @@
     </row>
     <row r="175" spans="1:11" ht="15">
       <c r="A175" s="20">
-        <v>111.1</v>
+        <v>15.29</v>
       </c>
       <c r="B175" s="20"/>
       <c r="C175" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D175" s="25"/>
       <c r="E175" s="15" t="s">
@@ -11359,11 +11351,11 @@
     </row>
     <row r="176" spans="1:11" ht="15">
       <c r="A176" s="20">
-        <v>106.99</v>
+        <v>111.1</v>
       </c>
       <c r="B176" s="20"/>
       <c r="C176" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D176" s="25"/>
       <c r="E176" s="15" t="s">
@@ -11391,11 +11383,11 @@
     </row>
     <row r="177" spans="1:11" ht="15">
       <c r="A177" s="20">
-        <v>62.5</v>
+        <v>106.99</v>
       </c>
       <c r="B177" s="20"/>
       <c r="C177" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D177" s="25"/>
       <c r="E177" s="15" t="s">
@@ -11423,11 +11415,11 @@
     </row>
     <row r="178" spans="1:11" ht="15">
       <c r="A178" s="20">
-        <v>80.19</v>
+        <v>62.5</v>
       </c>
       <c r="B178" s="20"/>
       <c r="C178" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D178" s="25"/>
       <c r="E178" s="15" t="s">
@@ -11455,11 +11447,11 @@
     </row>
     <row r="179" spans="1:11" ht="15">
       <c r="A179" s="20">
-        <v>185</v>
+        <v>80.19</v>
       </c>
       <c r="B179" s="20"/>
       <c r="C179" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D179" s="26"/>
       <c r="E179" s="15" t="s">
@@ -11491,7 +11483,7 @@
       </c>
       <c r="B180" s="20"/>
       <c r="C180" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D180" s="26"/>
       <c r="E180" s="15" t="s">
@@ -11501,7 +11493,7 @@
         <v>605</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H180" s="4">
         <f>D180+1095</f>
@@ -11519,11 +11511,11 @@
     </row>
     <row r="181" spans="1:11" ht="15">
       <c r="A181" s="20">
-        <v>427.5</v>
+        <v>185</v>
       </c>
       <c r="B181" s="20"/>
       <c r="C181" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D181" s="26"/>
       <c r="E181" s="15" t="s">
@@ -11551,11 +11543,11 @@
     </row>
     <row r="182" spans="1:11" ht="15">
       <c r="A182" s="20">
-        <v>688</v>
+        <v>427.5</v>
       </c>
       <c r="B182" s="20"/>
       <c r="C182" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D182" s="20"/>
       <c r="E182" s="15" t="s">
@@ -11583,11 +11575,11 @@
     </row>
     <row r="183" spans="1:11" ht="15">
       <c r="A183" s="20">
-        <v>104</v>
+        <v>688</v>
       </c>
       <c r="B183" s="20"/>
       <c r="C183" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D183" s="26"/>
       <c r="E183" s="15" t="s">
@@ -11615,11 +11607,11 @@
     </row>
     <row r="184" spans="1:11" ht="15">
       <c r="A184" s="20">
-        <v>255</v>
+        <v>104</v>
       </c>
       <c r="B184" s="20"/>
       <c r="C184" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D184" s="25"/>
       <c r="E184" s="15" t="s">
@@ -11647,11 +11639,11 @@
     </row>
     <row r="185" spans="1:11" ht="15">
       <c r="A185" s="20">
-        <v>278.08</v>
+        <v>255</v>
       </c>
       <c r="B185" s="20"/>
       <c r="C185" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D185" s="20"/>
       <c r="E185" s="15" t="s">
@@ -11679,11 +11671,11 @@
     </row>
     <row r="186" spans="1:11" ht="15">
       <c r="A186" s="20">
-        <v>57.1</v>
+        <v>278.08</v>
       </c>
       <c r="B186" s="20"/>
       <c r="C186" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D186" s="25"/>
       <c r="E186" s="15" t="s">
@@ -11711,11 +11703,11 @@
     </row>
     <row r="187" spans="1:11" ht="15">
       <c r="A187" s="20">
-        <v>1199</v>
+        <v>57.1</v>
       </c>
       <c r="B187" s="20"/>
       <c r="C187" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D187" s="20"/>
       <c r="E187" s="15" t="s">
@@ -11743,11 +11735,11 @@
     </row>
     <row r="188" spans="1:11" ht="15">
       <c r="A188" s="20">
-        <v>302</v>
+        <v>1199</v>
       </c>
       <c r="B188" s="20"/>
       <c r="C188" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D188" s="26"/>
       <c r="E188" s="15" t="s">
@@ -11775,11 +11767,11 @@
     </row>
     <row r="189" spans="1:11" ht="15">
       <c r="A189" s="20">
-        <v>249.5</v>
+        <v>302</v>
       </c>
       <c r="B189" s="20"/>
       <c r="C189" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D189" s="26"/>
       <c r="E189" s="15" t="s">
@@ -11807,11 +11799,11 @@
     </row>
     <row r="190" spans="1:11" ht="15">
       <c r="A190" s="20">
-        <v>499</v>
+        <v>249.5</v>
       </c>
       <c r="B190" s="20"/>
       <c r="C190" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D190" s="25"/>
       <c r="E190" s="15" t="s">
@@ -11839,11 +11831,11 @@
     </row>
     <row r="191" spans="1:11" ht="15">
       <c r="A191" s="20">
-        <v>117.7</v>
+        <v>499</v>
       </c>
       <c r="B191" s="20"/>
       <c r="C191" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D191" s="25"/>
       <c r="E191" s="15" t="s">
@@ -11871,11 +11863,11 @@
     </row>
     <row r="192" spans="1:11" ht="15">
       <c r="A192" s="20">
-        <v>77.900000000000006</v>
+        <v>117.7</v>
       </c>
       <c r="B192" s="20"/>
       <c r="C192" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D192" s="25"/>
       <c r="E192" s="15" t="s">
@@ -11903,11 +11895,11 @@
     </row>
     <row r="193" spans="1:11" ht="15">
       <c r="A193" s="20">
-        <v>231</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="B193" s="20"/>
       <c r="C193" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D193" s="25"/>
       <c r="E193" s="15" t="s">
@@ -11935,11 +11927,11 @@
     </row>
     <row r="194" spans="1:11" ht="15">
       <c r="A194" s="20">
-        <v>113.08</v>
+        <v>231</v>
       </c>
       <c r="B194" s="20"/>
       <c r="C194" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D194" s="25"/>
       <c r="E194" s="15" t="s">
@@ -11967,11 +11959,11 @@
     </row>
     <row r="195" spans="1:11" ht="15">
       <c r="A195" s="20">
-        <v>101.2</v>
+        <v>113.08</v>
       </c>
       <c r="B195" s="20"/>
       <c r="C195" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D195" s="25"/>
       <c r="E195" s="15" t="s">
@@ -12003,7 +11995,7 @@
       </c>
       <c r="B196" s="20"/>
       <c r="C196" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D196" s="25"/>
       <c r="E196" s="15" t="s">
@@ -12031,11 +12023,11 @@
     </row>
     <row r="197" spans="1:11" ht="15">
       <c r="A197" s="20">
-        <v>121.66</v>
+        <v>101.2</v>
       </c>
       <c r="B197" s="20"/>
       <c r="C197" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D197" s="20"/>
       <c r="E197" s="15" t="s">
@@ -12063,11 +12055,11 @@
     </row>
     <row r="198" spans="1:11" ht="15">
       <c r="A198" s="20">
-        <v>48</v>
+        <v>121.66</v>
       </c>
       <c r="B198" s="20"/>
       <c r="C198" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D198" s="25"/>
       <c r="E198" s="15" t="s">
@@ -12095,11 +12087,11 @@
     </row>
     <row r="199" spans="1:11" ht="15">
       <c r="A199" s="20">
-        <v>76.900000000000006</v>
+        <v>48</v>
       </c>
       <c r="B199" s="20"/>
       <c r="C199" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D199" s="20"/>
       <c r="E199" s="15" t="s">
@@ -12127,11 +12119,11 @@
     </row>
     <row r="200" spans="1:11" ht="15">
       <c r="A200" s="20">
-        <v>87.2</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="B200" s="20"/>
       <c r="C200" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D200" s="25"/>
       <c r="E200" s="15" t="s">
@@ -12159,11 +12151,11 @@
     </row>
     <row r="201" spans="1:11" ht="15">
       <c r="A201" s="20">
-        <v>165</v>
+        <v>87.2</v>
       </c>
       <c r="B201" s="20"/>
       <c r="C201" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D201" s="25"/>
       <c r="E201" s="15" t="s">
@@ -12191,11 +12183,11 @@
     </row>
     <row r="202" spans="1:11" ht="15">
       <c r="A202" s="20">
-        <v>75.900000000000006</v>
+        <v>165</v>
       </c>
       <c r="B202" s="20"/>
       <c r="C202" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D202" s="20"/>
       <c r="E202" s="15" t="s">
@@ -12223,11 +12215,11 @@
     </row>
     <row r="203" spans="1:11" ht="15">
       <c r="A203" s="20">
-        <v>168.3</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="B203" s="20"/>
       <c r="C203" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D203" s="25"/>
       <c r="E203" s="15" t="s">
@@ -12255,11 +12247,11 @@
     </row>
     <row r="204" spans="1:11" ht="15">
       <c r="A204" s="20">
-        <v>176</v>
+        <v>168.3</v>
       </c>
       <c r="B204" s="20"/>
       <c r="C204" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D204" s="21"/>
       <c r="E204" s="15" t="s">
@@ -12287,11 +12279,11 @@
     </row>
     <row r="205" spans="1:11" ht="15">
       <c r="A205" s="20">
-        <v>203.6</v>
+        <v>176</v>
       </c>
       <c r="B205" s="20"/>
       <c r="C205" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D205" s="21"/>
       <c r="E205" s="15" t="s">
@@ -12319,11 +12311,11 @@
     </row>
     <row r="206" spans="1:11" ht="15">
       <c r="A206" s="20">
-        <v>175.45</v>
+        <v>203.6</v>
       </c>
       <c r="B206" s="20"/>
       <c r="C206" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D206" s="25"/>
       <c r="E206" s="15" t="s">
@@ -12351,11 +12343,11 @@
     </row>
     <row r="207" spans="1:11" ht="15">
       <c r="A207" s="20">
-        <v>219</v>
+        <v>175.45</v>
       </c>
       <c r="B207" s="20"/>
       <c r="C207" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D207" s="25"/>
       <c r="E207" s="15" t="s">
@@ -12383,11 +12375,11 @@
     </row>
     <row r="208" spans="1:11" ht="15">
       <c r="A208" s="20">
-        <v>628</v>
+        <v>219</v>
       </c>
       <c r="B208" s="20"/>
       <c r="C208" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D208" s="25"/>
       <c r="E208" s="15" t="s">
@@ -12415,11 +12407,11 @@
     </row>
     <row r="209" spans="1:11" ht="15">
       <c r="A209" s="20">
-        <v>244.2</v>
+        <v>628</v>
       </c>
       <c r="B209" s="20"/>
       <c r="C209" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D209" s="25"/>
       <c r="E209" s="15" t="s">
@@ -12447,11 +12439,11 @@
     </row>
     <row r="210" spans="1:11" ht="15">
       <c r="A210" s="20">
-        <v>388</v>
+        <v>244.2</v>
       </c>
       <c r="B210" s="20"/>
       <c r="C210" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D210" s="25"/>
       <c r="E210" s="15" t="s">
@@ -12479,11 +12471,11 @@
     </row>
     <row r="211" spans="1:11" ht="15">
       <c r="A211" s="20">
-        <v>212.63</v>
+        <v>388</v>
       </c>
       <c r="B211" s="20"/>
       <c r="C211" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D211" s="25"/>
       <c r="E211" s="15" t="s">
@@ -12511,11 +12503,11 @@
     </row>
     <row r="212" spans="1:11" ht="15">
       <c r="A212" s="20">
-        <v>228.8</v>
+        <v>212.63</v>
       </c>
       <c r="B212" s="20"/>
       <c r="C212" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D212" s="25"/>
       <c r="E212" s="15" t="s">
@@ -12543,11 +12535,11 @@
     </row>
     <row r="213" spans="1:11" ht="15">
       <c r="A213" s="20">
-        <v>205.7</v>
+        <v>228.8</v>
       </c>
       <c r="B213" s="20"/>
       <c r="C213" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D213" s="14"/>
       <c r="E213" s="15" t="s">
@@ -12575,11 +12567,11 @@
     </row>
     <row r="214" spans="1:11" ht="15">
       <c r="A214" s="20">
-        <v>81</v>
+        <v>205.7</v>
       </c>
       <c r="B214" s="20"/>
       <c r="C214" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D214" s="25"/>
       <c r="E214" s="15" t="s">
@@ -12607,11 +12599,11 @@
     </row>
     <row r="215" spans="1:11" ht="15">
       <c r="A215" s="20">
-        <v>192.5</v>
+        <v>81</v>
       </c>
       <c r="B215" s="20"/>
       <c r="C215" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D215" s="25"/>
       <c r="E215" s="15" t="s">
@@ -12639,11 +12631,11 @@
     </row>
     <row r="216" spans="1:11" ht="15">
       <c r="A216" s="20">
-        <v>361.9</v>
+        <v>192.5</v>
       </c>
       <c r="B216" s="20"/>
       <c r="C216" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D216" s="25"/>
       <c r="E216" s="15" t="s">
@@ -12671,11 +12663,11 @@
     </row>
     <row r="217" spans="1:11" ht="15">
       <c r="A217" s="20">
-        <v>302.5</v>
+        <v>361.9</v>
       </c>
       <c r="B217" s="20"/>
       <c r="C217" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D217" s="25"/>
       <c r="E217" s="15" t="s">
@@ -12703,11 +12695,11 @@
     </row>
     <row r="218" spans="1:11" ht="15">
       <c r="A218" s="20">
-        <v>440</v>
+        <v>302.5</v>
       </c>
       <c r="B218" s="20"/>
       <c r="C218" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D218" s="25"/>
       <c r="E218" s="15" t="s">
@@ -12734,10 +12726,12 @@
       </c>
     </row>
     <row r="219" spans="1:11" ht="15">
-      <c r="A219" s="20"/>
+      <c r="A219" s="20">
+        <v>440</v>
+      </c>
       <c r="B219" s="20"/>
       <c r="C219" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D219" s="25"/>
       <c r="E219" s="15" t="s">
@@ -12767,7 +12761,7 @@
       <c r="A220" s="20"/>
       <c r="B220" s="28"/>
       <c r="C220" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E220" s="15" t="s">
         <v>1006</v>
@@ -12796,7 +12790,7 @@
       <c r="A221" s="20"/>
       <c r="B221" s="28"/>
       <c r="C221" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D221" s="14"/>
       <c r="E221" s="15" t="s">
@@ -12826,7 +12820,7 @@
       <c r="A222" s="20"/>
       <c r="B222" s="28"/>
       <c r="C222" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D222" s="14"/>
       <c r="E222" s="15" t="s">
@@ -12856,7 +12850,7 @@
       <c r="A223" s="20"/>
       <c r="B223" s="28"/>
       <c r="C223" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D223" s="14"/>
       <c r="E223" s="15" t="s">
@@ -12886,7 +12880,7 @@
       <c r="A224" s="20"/>
       <c r="B224" s="28"/>
       <c r="C224" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D224" s="14"/>
       <c r="E224" s="15" t="s">
@@ -12916,7 +12910,7 @@
       <c r="A225" s="20"/>
       <c r="B225" s="28"/>
       <c r="C225" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D225" s="14"/>
       <c r="E225" s="15" t="s">
@@ -12946,7 +12940,7 @@
       <c r="A226" s="20"/>
       <c r="B226" s="28"/>
       <c r="C226" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E226" s="15" t="s">
         <v>533</v>
@@ -12972,12 +12966,10 @@
       </c>
     </row>
     <row r="227" spans="1:11" ht="15">
-      <c r="A227" s="20">
-        <v>300</v>
-      </c>
+      <c r="A227" s="20"/>
       <c r="B227" s="28"/>
       <c r="C227" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E227" s="15" t="s">
         <v>525</v>
@@ -13004,11 +12996,11 @@
     </row>
     <row r="228" spans="1:11" ht="15">
       <c r="A228" s="20">
-        <v>825</v>
+        <v>300</v>
       </c>
       <c r="B228" s="20"/>
       <c r="C228" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D228" s="25"/>
       <c r="E228" s="16" t="s">
@@ -13036,11 +13028,11 @@
     </row>
     <row r="229" spans="1:11" ht="15">
       <c r="A229" s="20">
-        <v>199</v>
+        <v>825</v>
       </c>
       <c r="B229" s="20"/>
       <c r="C229" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D229" s="25"/>
       <c r="E229" s="16" t="s">
@@ -13068,11 +13060,11 @@
     </row>
     <row r="230" spans="1:11" ht="15">
       <c r="A230" s="20">
-        <v>90.75</v>
+        <v>199</v>
       </c>
       <c r="B230" s="20"/>
       <c r="C230" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D230" s="26"/>
       <c r="E230" s="16" t="s">
@@ -13100,11 +13092,11 @@
     </row>
     <row r="231" spans="1:11" ht="15">
       <c r="A231" s="20">
-        <v>229.9</v>
+        <v>90.75</v>
       </c>
       <c r="B231" s="20"/>
       <c r="C231" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D231" s="25"/>
       <c r="E231" s="16" t="s">
@@ -13132,11 +13124,11 @@
     </row>
     <row r="232" spans="1:11" ht="15">
       <c r="A232" s="20">
-        <v>439.69</v>
+        <v>229.9</v>
       </c>
       <c r="B232" s="20"/>
       <c r="C232" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D232" s="25"/>
       <c r="E232" s="16" t="s">
@@ -13164,11 +13156,11 @@
     </row>
     <row r="233" spans="1:11" ht="15">
       <c r="A233" s="20">
-        <v>499</v>
+        <v>439.69</v>
       </c>
       <c r="B233" s="20"/>
       <c r="C233" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D233" s="25"/>
       <c r="E233" s="16" t="s">
@@ -13196,11 +13188,11 @@
     </row>
     <row r="234" spans="1:11" ht="15">
       <c r="A234" s="20">
-        <v>139</v>
+        <v>499</v>
       </c>
       <c r="B234" s="20"/>
       <c r="C234" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D234" s="25"/>
       <c r="E234" s="16" t="s">
@@ -13228,11 +13220,11 @@
     </row>
     <row r="235" spans="1:11" ht="15">
       <c r="A235" s="20">
-        <v>153.6</v>
+        <v>139</v>
       </c>
       <c r="B235" s="20"/>
       <c r="C235" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D235" s="25"/>
       <c r="E235" s="16" t="s">
@@ -13260,11 +13252,11 @@
     </row>
     <row r="236" spans="1:11" ht="15">
       <c r="A236" s="20">
-        <v>260.48</v>
+        <v>153.6</v>
       </c>
       <c r="B236" s="20"/>
       <c r="C236" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D236" s="25"/>
       <c r="E236" s="16" t="s">
@@ -13292,11 +13284,11 @@
     </row>
     <row r="237" spans="1:11" ht="15">
       <c r="A237" s="20">
-        <v>345</v>
+        <v>260.48</v>
       </c>
       <c r="B237" s="20"/>
       <c r="C237" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D237" s="25"/>
       <c r="E237" s="16" t="s">
@@ -13324,11 +13316,11 @@
     </row>
     <row r="238" spans="1:11" ht="15">
       <c r="A238" s="20">
-        <v>150</v>
+        <v>345</v>
       </c>
       <c r="B238" s="20"/>
       <c r="C238" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D238" s="25"/>
       <c r="E238" s="16" t="s">
@@ -13355,10 +13347,12 @@
       </c>
     </row>
     <row r="239" spans="1:11" ht="15">
-      <c r="A239" s="20"/>
+      <c r="A239" s="20">
+        <v>150</v>
+      </c>
       <c r="B239" s="20"/>
       <c r="C239" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D239" s="25"/>
       <c r="E239" s="16" t="s">
@@ -13385,12 +13379,10 @@
       </c>
     </row>
     <row r="240" spans="1:11" ht="15">
-      <c r="A240" s="20">
-        <v>248</v>
-      </c>
+      <c r="A240" s="20"/>
       <c r="B240" s="20"/>
       <c r="C240" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D240" s="25"/>
       <c r="E240" s="16" t="s">
@@ -13418,11 +13410,11 @@
     </row>
     <row r="241" spans="1:11" ht="15">
       <c r="A241" s="20">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B241" s="20"/>
       <c r="C241" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D241" s="25"/>
       <c r="E241" s="16" t="s">
@@ -13450,11 +13442,11 @@
     </row>
     <row r="242" spans="1:11" ht="15">
       <c r="A242" s="20">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="B242" s="20"/>
       <c r="C242" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E242" s="16" t="s">
         <v>1013</v>
@@ -13481,11 +13473,11 @@
     </row>
     <row r="243" spans="1:11" ht="15">
       <c r="A243" s="20">
-        <v>299</v>
+        <v>139</v>
       </c>
       <c r="B243" s="20"/>
       <c r="C243" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D243" s="14"/>
       <c r="E243" s="16" t="s">
@@ -13513,11 +13505,11 @@
     </row>
     <row r="244" spans="1:11" ht="15">
       <c r="A244" s="20">
-        <v>255.75</v>
+        <v>299</v>
       </c>
       <c r="B244" s="20"/>
       <c r="C244" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D244" s="20"/>
       <c r="E244" s="16" t="s">
@@ -13545,11 +13537,11 @@
     </row>
     <row r="245" spans="1:11" ht="15">
       <c r="A245" s="20">
-        <v>739</v>
+        <v>255.75</v>
       </c>
       <c r="B245" s="20"/>
       <c r="C245" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D245" s="25"/>
       <c r="E245" s="16" t="s">
@@ -13577,11 +13569,11 @@
     </row>
     <row r="246" spans="1:11" ht="15">
       <c r="A246" s="20">
-        <v>129</v>
+        <v>739</v>
       </c>
       <c r="B246" s="20"/>
       <c r="C246" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D246" s="25"/>
       <c r="E246" s="16" t="s">
@@ -13609,11 +13601,11 @@
     </row>
     <row r="247" spans="1:11" ht="15">
       <c r="A247" s="20">
-        <v>298</v>
+        <v>129</v>
       </c>
       <c r="B247" s="20"/>
       <c r="C247" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D247" s="25"/>
       <c r="E247" s="16" t="s">
@@ -13641,11 +13633,11 @@
     </row>
     <row r="248" spans="1:11" ht="15">
       <c r="A248" s="20">
-        <v>225</v>
+        <v>298</v>
       </c>
       <c r="B248" s="20"/>
       <c r="C248" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D248" s="25"/>
       <c r="E248" s="16" t="s">
@@ -13672,10 +13664,12 @@
       </c>
     </row>
     <row r="249" spans="1:11" ht="15">
-      <c r="A249" s="20"/>
+      <c r="A249" s="20">
+        <v>225</v>
+      </c>
       <c r="B249" s="20"/>
       <c r="C249" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D249" s="20"/>
       <c r="E249" s="16" t="s">
@@ -13702,12 +13696,10 @@
       </c>
     </row>
     <row r="250" spans="1:11" ht="15">
-      <c r="A250" s="20">
-        <v>148</v>
-      </c>
+      <c r="A250" s="20"/>
       <c r="B250" s="28"/>
       <c r="C250" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D250" s="14"/>
       <c r="E250" s="16" t="s">
@@ -13735,11 +13727,11 @@
     </row>
     <row r="251" spans="1:11" ht="15">
       <c r="A251" s="20">
-        <v>210</v>
+        <v>148</v>
       </c>
       <c r="B251" s="20"/>
       <c r="C251" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D251" s="20"/>
       <c r="E251" s="16" t="s">
@@ -13767,11 +13759,11 @@
     </row>
     <row r="252" spans="1:11" ht="15">
       <c r="A252" s="20">
-        <v>385</v>
+        <v>210</v>
       </c>
       <c r="B252" s="20"/>
       <c r="C252" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D252" s="25"/>
       <c r="E252" s="16" t="s">
@@ -13799,11 +13791,11 @@
     </row>
     <row r="253" spans="1:11" ht="15">
       <c r="A253" s="20">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="B253" s="20"/>
       <c r="C253" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D253" s="20"/>
       <c r="E253" s="16" t="s">
@@ -13831,11 +13823,11 @@
     </row>
     <row r="254" spans="1:11" ht="15">
       <c r="A254" s="20">
-        <v>318</v>
+        <v>230</v>
       </c>
       <c r="B254" s="20"/>
       <c r="C254" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D254" s="25"/>
       <c r="E254" s="16" t="s">
@@ -13863,11 +13855,11 @@
     </row>
     <row r="255" spans="1:11" ht="15">
       <c r="A255" s="20">
-        <v>119.8</v>
+        <v>318</v>
       </c>
       <c r="B255" s="20"/>
       <c r="C255" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D255" s="25"/>
       <c r="E255" s="16" t="s">
@@ -13895,11 +13887,11 @@
     </row>
     <row r="256" spans="1:11" ht="15">
       <c r="A256" s="20">
-        <v>199</v>
+        <v>119.8</v>
       </c>
       <c r="B256" s="20"/>
       <c r="C256" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D256" s="26"/>
       <c r="E256" s="16" t="s">
@@ -13927,11 +13919,11 @@
     </row>
     <row r="257" spans="1:11" ht="15">
       <c r="A257" s="20">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="B257" s="20"/>
       <c r="C257" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D257" s="25"/>
       <c r="E257" s="16" t="s">
@@ -13959,11 +13951,11 @@
     </row>
     <row r="258" spans="1:11" ht="15">
       <c r="A258" s="20">
-        <v>315</v>
+        <v>218</v>
       </c>
       <c r="B258" s="20"/>
       <c r="C258" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D258" s="25"/>
       <c r="E258" s="16" t="s">
@@ -13991,11 +13983,11 @@
     </row>
     <row r="259" spans="1:11" ht="15">
       <c r="A259" s="20">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="B259" s="20"/>
       <c r="C259" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D259" s="25"/>
       <c r="E259" s="16" t="s">
@@ -14023,11 +14015,11 @@
     </row>
     <row r="260" spans="1:11" ht="15">
       <c r="A260" s="20">
-        <v>358.6</v>
+        <v>359</v>
       </c>
       <c r="B260" s="20"/>
       <c r="C260" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D260" s="14"/>
       <c r="E260" s="16" t="s">
@@ -14055,11 +14047,11 @@
     </row>
     <row r="261" spans="1:11" ht="15">
       <c r="A261" s="20">
-        <v>498</v>
+        <v>358.6</v>
       </c>
       <c r="B261" s="20"/>
       <c r="C261" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D261" s="25"/>
       <c r="E261" s="16" t="s">
@@ -14087,11 +14079,11 @@
     </row>
     <row r="262" spans="1:11" ht="15">
       <c r="A262" s="20">
-        <v>470.8</v>
+        <v>498</v>
       </c>
       <c r="B262" s="20"/>
       <c r="C262" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D262" s="25"/>
       <c r="E262" s="16" t="s">
@@ -14119,11 +14111,11 @@
     </row>
     <row r="263" spans="1:11" ht="15">
       <c r="A263" s="20">
-        <v>551.79999999999995</v>
+        <v>470.8</v>
       </c>
       <c r="B263" s="20"/>
       <c r="C263" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D263" s="25"/>
       <c r="E263" s="16" t="s">
@@ -14151,11 +14143,11 @@
     </row>
     <row r="264" spans="1:11" ht="15">
       <c r="A264" s="20">
-        <v>2100</v>
+        <v>551.79999999999995</v>
       </c>
       <c r="B264" s="20"/>
       <c r="C264" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D264" s="20"/>
       <c r="E264" s="16" t="s">
@@ -14183,11 +14175,11 @@
     </row>
     <row r="265" spans="1:11" ht="15">
       <c r="A265" s="20">
-        <v>255</v>
+        <v>2100</v>
       </c>
       <c r="B265" s="20"/>
       <c r="C265" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D265" s="26"/>
       <c r="E265" s="16" t="s">
@@ -14215,11 +14207,11 @@
     </row>
     <row r="266" spans="1:11" ht="15">
       <c r="A266" s="20">
-        <v>758</v>
+        <v>255</v>
       </c>
       <c r="B266" s="20"/>
       <c r="C266" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D266" s="25"/>
       <c r="E266" s="16" t="s">
@@ -14247,11 +14239,11 @@
     </row>
     <row r="267" spans="1:11" ht="15">
       <c r="A267" s="20">
-        <v>399</v>
+        <v>758</v>
       </c>
       <c r="B267" s="20"/>
       <c r="C267" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D267" s="25"/>
       <c r="E267" s="16" t="s">
@@ -14279,11 +14271,11 @@
     </row>
     <row r="268" spans="1:11" ht="15">
       <c r="A268" s="20">
-        <v>781</v>
+        <v>399</v>
       </c>
       <c r="B268" s="20"/>
       <c r="C268" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D268" s="25"/>
       <c r="E268" s="16" t="s">
@@ -14311,11 +14303,11 @@
     </row>
     <row r="269" spans="1:11" ht="15">
       <c r="A269" s="20">
-        <v>568</v>
+        <v>781</v>
       </c>
       <c r="B269" s="20"/>
       <c r="C269" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D269" s="20"/>
       <c r="E269" s="16" t="s">
@@ -14343,11 +14335,11 @@
     </row>
     <row r="270" spans="1:11" ht="15">
       <c r="A270" s="20">
-        <v>89.79</v>
+        <v>568</v>
       </c>
       <c r="B270" s="20"/>
       <c r="C270" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D270" s="26"/>
       <c r="E270" s="16" t="s">
@@ -14375,11 +14367,11 @@
     </row>
     <row r="271" spans="1:11" ht="15">
       <c r="A271" s="20">
-        <v>390</v>
+        <v>89.79</v>
       </c>
       <c r="B271" s="20"/>
       <c r="C271" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D271" s="26"/>
       <c r="E271" s="16" t="s">
@@ -14411,7 +14403,7 @@
       </c>
       <c r="B272" s="20"/>
       <c r="C272" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D272" s="25"/>
       <c r="E272" s="16" t="s">
@@ -14439,11 +14431,11 @@
     </row>
     <row r="273" spans="1:11" ht="17">
       <c r="A273" s="20">
-        <v>266.2</v>
+        <v>390</v>
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D273" s="25"/>
       <c r="E273" s="16" t="s">
@@ -14471,11 +14463,11 @@
     </row>
     <row r="274" spans="1:11" ht="15">
       <c r="A274" s="20">
-        <v>73.7</v>
+        <v>266.2</v>
       </c>
       <c r="B274" s="20"/>
       <c r="C274" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D274" s="25"/>
       <c r="E274" s="16" t="s">
@@ -14503,11 +14495,11 @@
     </row>
     <row r="275" spans="1:11" ht="15">
       <c r="A275" s="20">
-        <v>162</v>
+        <v>73.7</v>
       </c>
       <c r="B275" s="20"/>
       <c r="C275" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D275" s="25"/>
       <c r="E275" s="16" t="s">
@@ -14535,11 +14527,11 @@
     </row>
     <row r="276" spans="1:11" ht="15">
       <c r="A276" s="20">
-        <v>659</v>
+        <v>162</v>
       </c>
       <c r="B276" s="20"/>
       <c r="C276" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D276" s="25"/>
       <c r="E276" s="16" t="s">
@@ -14567,11 +14559,11 @@
     </row>
     <row r="277" spans="1:11" ht="15">
       <c r="A277" s="20">
-        <v>499</v>
+        <v>659</v>
       </c>
       <c r="B277" s="20"/>
       <c r="C277" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D277" s="25"/>
       <c r="E277" s="16" t="s">
@@ -14599,11 +14591,11 @@
     </row>
     <row r="278" spans="1:11" ht="15">
       <c r="A278" s="20">
-        <v>329</v>
+        <v>499</v>
       </c>
       <c r="B278" s="20"/>
       <c r="C278" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D278" s="25"/>
       <c r="E278" s="16" t="s">
@@ -14631,11 +14623,11 @@
     </row>
     <row r="279" spans="1:11" ht="15">
       <c r="A279" s="20">
-        <v>659</v>
+        <v>329</v>
       </c>
       <c r="B279" s="20"/>
       <c r="C279" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D279" s="25"/>
       <c r="E279" s="16" t="s">
@@ -14663,11 +14655,11 @@
     </row>
     <row r="280" spans="1:11" ht="15">
       <c r="A280" s="20">
-        <v>325.60000000000002</v>
+        <v>659</v>
       </c>
       <c r="B280" s="20"/>
       <c r="C280" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D280" s="25"/>
       <c r="E280" s="16" t="s">
@@ -14695,11 +14687,11 @@
     </row>
     <row r="281" spans="1:11" ht="15">
       <c r="A281" s="20">
-        <v>202.4</v>
+        <v>325.60000000000002</v>
       </c>
       <c r="B281" s="20"/>
       <c r="C281" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D281" s="25"/>
       <c r="E281" s="16" t="s">
@@ -14727,11 +14719,11 @@
     </row>
     <row r="282" spans="1:11" ht="15">
       <c r="A282" s="20">
-        <v>225.5</v>
+        <v>202.4</v>
       </c>
       <c r="B282" s="20"/>
       <c r="C282" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D282" s="25"/>
       <c r="E282" s="16" t="s">
@@ -14759,11 +14751,11 @@
     </row>
     <row r="283" spans="1:11" ht="15">
       <c r="A283" s="20">
-        <v>191.4</v>
+        <v>225.5</v>
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D283" s="25"/>
       <c r="E283" s="16" t="s">
@@ -14791,11 +14783,11 @@
     </row>
     <row r="284" spans="1:11" ht="15">
       <c r="A284" s="20">
-        <v>880</v>
+        <v>191.4</v>
       </c>
       <c r="B284" s="20"/>
       <c r="C284" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D284" s="25"/>
       <c r="E284" s="16" t="s">
@@ -14823,11 +14815,11 @@
     </row>
     <row r="285" spans="1:11" ht="15">
       <c r="A285" s="20">
-        <v>369</v>
+        <v>880</v>
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D285" s="25"/>
       <c r="E285" s="16" t="s">
@@ -14855,11 +14847,11 @@
     </row>
     <row r="286" spans="1:11" ht="15">
       <c r="A286" s="20">
-        <v>285</v>
+        <v>369</v>
       </c>
       <c r="B286" s="20"/>
       <c r="C286" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D286" s="25"/>
       <c r="E286" s="16" t="s">
@@ -14887,11 +14879,11 @@
     </row>
     <row r="287" spans="1:11" ht="15">
       <c r="A287" s="20">
-        <v>175</v>
+        <v>285</v>
       </c>
       <c r="B287" s="20"/>
       <c r="C287" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D287" s="21"/>
       <c r="E287" s="16" t="s">
@@ -14919,11 +14911,11 @@
     </row>
     <row r="288" spans="1:11" ht="15">
       <c r="A288" s="20">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="B288" s="20"/>
       <c r="C288" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D288" s="20"/>
       <c r="E288" s="16" t="s">
@@ -14951,11 +14943,11 @@
     </row>
     <row r="289" spans="1:11" ht="15">
       <c r="A289" s="20">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c r="B289" s="20"/>
       <c r="C289" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E289" s="16" t="s">
         <v>66</v>
@@ -14982,11 +14974,11 @@
     </row>
     <row r="290" spans="1:11" ht="15">
       <c r="A290" s="20">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B290" s="20"/>
       <c r="C290" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D290" s="25"/>
       <c r="E290" s="16" t="s">
@@ -15014,11 +15006,11 @@
     </row>
     <row r="291" spans="1:11" ht="15">
       <c r="A291" s="20">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="B291" s="20"/>
       <c r="C291" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D291" s="25"/>
       <c r="E291" s="16" t="s">
@@ -15046,11 +15038,11 @@
     </row>
     <row r="292" spans="1:11" ht="15">
       <c r="A292" s="20">
-        <v>545.25</v>
+        <v>198</v>
       </c>
       <c r="B292" s="20"/>
       <c r="C292" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D292" s="20"/>
       <c r="E292" s="16" t="s">
@@ -15078,11 +15070,11 @@
     </row>
     <row r="293" spans="1:11" ht="15">
       <c r="A293" s="20">
-        <v>431.2</v>
+        <v>545.25</v>
       </c>
       <c r="B293" s="20"/>
       <c r="C293" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D293" s="25"/>
       <c r="E293" s="16" t="s">
@@ -15110,11 +15102,11 @@
     </row>
     <row r="294" spans="1:11" ht="15">
       <c r="A294" s="20">
-        <v>426</v>
+        <v>431.2</v>
       </c>
       <c r="B294" s="20"/>
       <c r="C294" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D294" s="20"/>
       <c r="E294" s="16" t="s">
@@ -15142,11 +15134,11 @@
     </row>
     <row r="295" spans="1:11" ht="15">
       <c r="A295" s="20">
-        <v>455.4</v>
+        <v>426</v>
       </c>
       <c r="B295" s="20"/>
       <c r="C295" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D295" s="20"/>
       <c r="E295" s="16" t="s">
@@ -15174,11 +15166,11 @@
     </row>
     <row r="296" spans="1:11" ht="15">
       <c r="A296" s="20">
-        <v>499</v>
+        <v>455.4</v>
       </c>
       <c r="B296" s="20"/>
       <c r="C296" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D296" s="25"/>
       <c r="E296" s="16" t="s">
@@ -15206,11 +15198,11 @@
     </row>
     <row r="297" spans="1:11" ht="15">
       <c r="A297" s="20">
-        <v>679</v>
+        <v>499</v>
       </c>
       <c r="B297" s="20"/>
       <c r="C297" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D297" s="14"/>
       <c r="E297" s="16" t="s">
@@ -15238,11 +15230,11 @@
     </row>
     <row r="298" spans="1:11" ht="15">
       <c r="A298" s="20">
-        <v>198</v>
+        <v>679</v>
       </c>
       <c r="B298" s="20"/>
       <c r="C298" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D298" s="26"/>
       <c r="E298" s="16" t="s">
@@ -15270,11 +15262,11 @@
     </row>
     <row r="299" spans="1:11" ht="15">
       <c r="A299" s="20">
-        <v>701.8</v>
+        <v>198</v>
       </c>
       <c r="B299" s="20"/>
       <c r="C299" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D299" s="25"/>
       <c r="E299" s="16" t="s">
@@ -15302,11 +15294,11 @@
     </row>
     <row r="300" spans="1:11" ht="15">
       <c r="A300" s="20">
-        <v>490.6</v>
+        <v>701.8</v>
       </c>
       <c r="B300" s="20"/>
       <c r="C300" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D300" s="25"/>
       <c r="E300" s="16" t="s">
@@ -15334,11 +15326,11 @@
     </row>
     <row r="301" spans="1:11" ht="15">
       <c r="A301" s="20">
-        <v>998</v>
+        <v>490.6</v>
       </c>
       <c r="B301" s="20"/>
       <c r="C301" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D301" s="25"/>
       <c r="E301" s="16" t="s">
@@ -15366,11 +15358,11 @@
     </row>
     <row r="302" spans="1:11" ht="15">
       <c r="A302" s="20">
-        <v>498</v>
+        <v>998</v>
       </c>
       <c r="B302" s="20"/>
       <c r="C302" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D302" s="25"/>
       <c r="E302" s="16" t="s">
@@ -15398,11 +15390,11 @@
     </row>
     <row r="303" spans="1:11" ht="15">
       <c r="A303" s="20">
-        <v>299.5</v>
+        <v>498</v>
       </c>
       <c r="B303" s="20"/>
       <c r="C303" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D303" s="25"/>
       <c r="E303" s="16" t="s">
@@ -15430,11 +15422,11 @@
     </row>
     <row r="304" spans="1:11" ht="15">
       <c r="A304" s="20">
-        <v>536.79999999999995</v>
+        <v>299.5</v>
       </c>
       <c r="B304" s="20"/>
       <c r="C304" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D304" s="20"/>
       <c r="E304" s="16" t="s">
@@ -15466,7 +15458,7 @@
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D305" s="25"/>
       <c r="E305" s="16" t="s">
@@ -15494,11 +15486,11 @@
     </row>
     <row r="306" spans="1:11" ht="15">
       <c r="A306" s="20">
-        <v>738.1</v>
+        <v>536.79999999999995</v>
       </c>
       <c r="B306" s="20"/>
       <c r="C306" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D306" s="25"/>
       <c r="E306" s="16" t="s">
@@ -15526,11 +15518,11 @@
     </row>
     <row r="307" spans="1:11" ht="15">
       <c r="A307" s="20">
-        <v>59.9</v>
+        <v>738.1</v>
       </c>
       <c r="B307" s="20"/>
       <c r="C307" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D307" s="25"/>
       <c r="E307" s="16" t="s">
@@ -15558,11 +15550,11 @@
     </row>
     <row r="308" spans="1:11" ht="15">
       <c r="A308" s="20">
-        <v>221.99</v>
+        <v>59.9</v>
       </c>
       <c r="B308" s="20"/>
       <c r="C308" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D308" s="20"/>
       <c r="E308" s="16" t="s">
@@ -15590,11 +15582,11 @@
     </row>
     <row r="309" spans="1:11" ht="15">
       <c r="A309" s="20">
-        <v>149</v>
+        <v>221.99</v>
       </c>
       <c r="B309" s="20"/>
       <c r="C309" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D309" s="20"/>
       <c r="E309" s="16" t="s">
@@ -15622,11 +15614,11 @@
     </row>
     <row r="310" spans="1:11" ht="15">
       <c r="A310" s="20">
-        <v>395</v>
+        <v>149</v>
       </c>
       <c r="B310" s="20"/>
       <c r="C310" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D310" s="21"/>
       <c r="E310" s="16" t="s">
@@ -15654,11 +15646,11 @@
     </row>
     <row r="311" spans="1:11" ht="15">
       <c r="A311" s="20">
-        <v>999</v>
+        <v>395</v>
       </c>
       <c r="B311" s="20"/>
       <c r="C311" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D311" s="20"/>
       <c r="E311" s="16" t="s">
@@ -15686,11 +15678,11 @@
     </row>
     <row r="312" spans="1:11" ht="17">
       <c r="A312" s="20">
-        <v>1398</v>
+        <v>999</v>
       </c>
       <c r="B312" s="20"/>
       <c r="C312" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D312" s="25"/>
       <c r="E312" s="16" t="s">
@@ -15718,11 +15710,11 @@
     </row>
     <row r="313" spans="1:11" ht="15">
       <c r="A313" s="20">
-        <v>255.2</v>
+        <v>1398</v>
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D313" s="25"/>
       <c r="E313" s="16" t="s">
@@ -15750,11 +15742,11 @@
     </row>
     <row r="314" spans="1:11" ht="15">
       <c r="A314" s="20">
-        <v>158</v>
+        <v>255.2</v>
       </c>
       <c r="B314" s="20"/>
       <c r="C314" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D314" s="25"/>
       <c r="E314" s="16" t="s">
@@ -15782,11 +15774,11 @@
     </row>
     <row r="315" spans="1:11" ht="15">
       <c r="A315" s="20">
-        <v>147.4</v>
+        <v>158</v>
       </c>
       <c r="B315" s="20"/>
       <c r="C315" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D315" s="26"/>
       <c r="E315" s="16" t="s">
@@ -15814,11 +15806,11 @@
     </row>
     <row r="316" spans="1:11" ht="15">
       <c r="A316" s="20">
-        <v>207.9</v>
+        <v>147.4</v>
       </c>
       <c r="B316" s="20"/>
       <c r="C316" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D316" s="25"/>
       <c r="E316" s="16" t="s">
@@ -15846,11 +15838,11 @@
     </row>
     <row r="317" spans="1:11" ht="15">
       <c r="A317" s="20">
-        <v>261.8</v>
+        <v>207.9</v>
       </c>
       <c r="B317" s="20"/>
       <c r="C317" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D317" s="25"/>
       <c r="E317" s="16" t="s">
@@ -15878,11 +15870,11 @@
     </row>
     <row r="318" spans="1:11" ht="15">
       <c r="A318" s="20">
-        <v>2600</v>
+        <v>261.8</v>
       </c>
       <c r="B318" s="20"/>
       <c r="C318" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D318" s="14"/>
       <c r="E318" s="16" t="s">
@@ -15910,11 +15902,11 @@
     </row>
     <row r="319" spans="1:11" ht="15">
       <c r="A319" s="20">
-        <v>633</v>
+        <v>2600</v>
       </c>
       <c r="B319" s="20"/>
       <c r="C319" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D319" s="25"/>
       <c r="E319" s="16" t="s">
@@ -15942,11 +15934,11 @@
     </row>
     <row r="320" spans="1:11" ht="15">
       <c r="A320" s="20">
-        <v>100.65</v>
+        <v>633</v>
       </c>
       <c r="B320" s="20"/>
       <c r="C320" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D320" s="25"/>
       <c r="E320" s="16" t="s">
@@ -15974,11 +15966,11 @@
     </row>
     <row r="321" spans="1:11" ht="15">
       <c r="A321" s="20">
-        <v>219</v>
+        <v>100.65</v>
       </c>
       <c r="B321" s="20"/>
       <c r="C321" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D321" s="25"/>
       <c r="E321" s="16" t="s">
@@ -16006,11 +15998,11 @@
     </row>
     <row r="322" spans="1:11" ht="15">
       <c r="A322" s="20">
-        <v>359</v>
+        <v>219</v>
       </c>
       <c r="B322" s="20"/>
       <c r="C322" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D322" s="25"/>
       <c r="E322" s="16" t="s">
@@ -16038,11 +16030,11 @@
     </row>
     <row r="323" spans="1:11" ht="15">
       <c r="A323" s="20">
-        <v>249</v>
+        <v>359</v>
       </c>
       <c r="B323" s="20"/>
       <c r="C323" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D323" s="25"/>
       <c r="E323" s="16" t="s">
@@ -16070,11 +16062,11 @@
     </row>
     <row r="324" spans="1:11" ht="15">
       <c r="A324" s="20">
-        <v>387.2</v>
+        <v>249</v>
       </c>
       <c r="B324" s="20"/>
       <c r="C324" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D324" s="20"/>
       <c r="E324" s="16" t="s">
@@ -16102,11 +16094,11 @@
     </row>
     <row r="325" spans="1:11" ht="15">
       <c r="A325" s="20">
-        <v>100.65</v>
+        <v>387.2</v>
       </c>
       <c r="B325" s="20"/>
       <c r="C325" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D325" s="25"/>
       <c r="E325" s="16" t="s">
@@ -16134,11 +16126,11 @@
     </row>
     <row r="326" spans="1:11" ht="15">
       <c r="A326" s="20">
-        <v>504.9</v>
+        <v>100.65</v>
       </c>
       <c r="B326" s="20"/>
       <c r="C326" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D326" s="25"/>
       <c r="E326" s="16" t="s">
@@ -16166,11 +16158,11 @@
     </row>
     <row r="327" spans="1:11" ht="17">
       <c r="A327" s="20">
-        <v>478.5</v>
+        <v>504.9</v>
       </c>
       <c r="B327" s="20"/>
       <c r="C327" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D327" s="25"/>
       <c r="E327" s="16" t="s">
@@ -16198,11 +16190,11 @@
     </row>
     <row r="328" spans="1:11" ht="15">
       <c r="A328" s="20">
-        <v>479</v>
+        <v>478.5</v>
       </c>
       <c r="B328" s="20"/>
       <c r="C328" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D328" s="25"/>
       <c r="E328" s="16" t="s">
@@ -16230,11 +16222,11 @@
     </row>
     <row r="329" spans="1:11" ht="15">
       <c r="A329" s="20">
-        <v>359</v>
+        <v>479</v>
       </c>
       <c r="B329" s="20"/>
       <c r="C329" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D329" s="25"/>
       <c r="E329" s="16" t="s">
@@ -16266,7 +16258,7 @@
       </c>
       <c r="B330" s="20"/>
       <c r="C330" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D330" s="20"/>
       <c r="E330" s="16" t="s">
@@ -16294,11 +16286,11 @@
     </row>
     <row r="331" spans="1:11" ht="15">
       <c r="A331" s="20">
-        <v>309</v>
+        <v>359</v>
       </c>
       <c r="B331" s="20"/>
       <c r="C331" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D331" s="25"/>
       <c r="E331" s="16" t="s">
@@ -16326,11 +16318,11 @@
     </row>
     <row r="332" spans="1:11" ht="13.5" customHeight="1">
       <c r="A332" s="20">
-        <v>599</v>
+        <v>309</v>
       </c>
       <c r="B332" s="20"/>
       <c r="C332" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D332" s="25"/>
       <c r="E332" s="16" t="s">
@@ -16358,11 +16350,11 @@
     </row>
     <row r="333" spans="1:11" ht="15">
       <c r="A333" s="20">
-        <v>248</v>
+        <v>599</v>
       </c>
       <c r="B333" s="20"/>
       <c r="C333" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D333" s="25"/>
       <c r="E333" s="16" t="s">
@@ -16390,11 +16382,11 @@
     </row>
     <row r="334" spans="1:11" ht="15">
       <c r="A334" s="20">
-        <v>456.5</v>
+        <v>248</v>
       </c>
       <c r="B334" s="20"/>
       <c r="C334" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D334" s="20"/>
       <c r="E334" s="16" t="s">
@@ -16422,11 +16414,11 @@
     </row>
     <row r="335" spans="1:11" ht="17">
       <c r="A335" s="20">
-        <v>157</v>
+        <v>456.5</v>
       </c>
       <c r="B335" s="20"/>
       <c r="C335" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D335" s="26"/>
       <c r="E335" s="16" t="s">
@@ -16454,11 +16446,11 @@
     </row>
     <row r="336" spans="1:11" ht="15">
       <c r="A336" s="20">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="B336" s="20"/>
       <c r="C336" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D336" s="20"/>
       <c r="E336" s="16" t="s">
@@ -16486,11 +16478,11 @@
     </row>
     <row r="337" spans="1:11" ht="15">
       <c r="A337" s="20">
-        <v>899</v>
+        <v>178</v>
       </c>
       <c r="B337" s="20"/>
       <c r="C337" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D337" s="25"/>
       <c r="E337" s="16" t="s">
@@ -16518,11 +16510,11 @@
     </row>
     <row r="338" spans="1:11" ht="15">
       <c r="A338" s="20">
-        <v>189</v>
+        <v>899</v>
       </c>
       <c r="B338" s="20"/>
       <c r="C338" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D338" s="14"/>
       <c r="E338" s="15" t="s">
@@ -16550,11 +16542,11 @@
     </row>
     <row r="339" spans="1:11" ht="15">
       <c r="A339" s="20">
-        <v>81.84</v>
+        <v>189</v>
       </c>
       <c r="B339" s="20"/>
       <c r="C339" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D339" s="20"/>
       <c r="E339" s="16" t="s">
@@ -16582,11 +16574,11 @@
     </row>
     <row r="340" spans="1:11" ht="15">
       <c r="A340" s="20">
-        <v>661</v>
+        <v>81.84</v>
       </c>
       <c r="B340" s="20"/>
       <c r="C340" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D340" s="20"/>
       <c r="E340" s="16" t="s">
@@ -16614,11 +16606,11 @@
     </row>
     <row r="341" spans="1:11" ht="15">
       <c r="A341" s="20">
-        <v>180</v>
+        <v>661</v>
       </c>
       <c r="B341" s="20"/>
       <c r="C341" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D341" s="20"/>
       <c r="E341" s="16" t="s">
@@ -16646,11 +16638,11 @@
     </row>
     <row r="342" spans="1:11" ht="15">
       <c r="A342" s="20">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="B342" s="20"/>
       <c r="C342" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D342" s="20"/>
       <c r="E342" s="16" t="s">
@@ -16678,11 +16670,11 @@
     </row>
     <row r="343" spans="1:11" ht="15">
       <c r="A343" s="20">
-        <v>899</v>
+        <v>320</v>
       </c>
       <c r="B343" s="20"/>
       <c r="C343" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D343" s="25"/>
       <c r="E343" s="16" t="s">
@@ -16710,11 +16702,11 @@
     </row>
     <row r="344" spans="1:11" ht="15">
       <c r="A344" s="20">
-        <v>58.3</v>
+        <v>899</v>
       </c>
       <c r="B344" s="20"/>
       <c r="C344" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D344" s="25"/>
       <c r="E344" s="16" t="s">
@@ -16742,11 +16734,11 @@
     </row>
     <row r="345" spans="1:11" ht="15">
       <c r="A345" s="20">
-        <v>390</v>
+        <v>58.3</v>
       </c>
       <c r="B345" s="20"/>
       <c r="C345" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D345" s="25"/>
       <c r="E345" s="16" t="s">
@@ -16774,11 +16766,11 @@
     </row>
     <row r="346" spans="1:11" ht="15">
       <c r="A346" s="20">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="B346" s="20"/>
       <c r="C346" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D346" s="20"/>
       <c r="E346" s="16" t="s">
@@ -16805,10 +16797,12 @@
       </c>
     </row>
     <row r="347" spans="1:11" ht="15">
-      <c r="A347" s="20"/>
+      <c r="A347" s="20">
+        <v>328</v>
+      </c>
       <c r="B347" s="20"/>
       <c r="C347" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D347" s="20"/>
       <c r="E347" s="16" t="s">
@@ -16835,12 +16829,10 @@
       </c>
     </row>
     <row r="348" spans="1:11" ht="15">
-      <c r="A348" s="20">
-        <v>115</v>
-      </c>
+      <c r="A348" s="20"/>
       <c r="B348" s="20"/>
       <c r="C348" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D348" s="20"/>
       <c r="E348" s="16" t="s">
@@ -16868,11 +16860,11 @@
     </row>
     <row r="349" spans="1:11" ht="15">
       <c r="A349" s="20">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B349" s="20"/>
       <c r="C349" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D349" s="20"/>
       <c r="E349" s="16" t="s">
@@ -16900,11 +16892,11 @@
     </row>
     <row r="350" spans="1:11" ht="15">
       <c r="A350" s="20">
-        <v>1299</v>
+        <v>99</v>
       </c>
       <c r="B350" s="20"/>
       <c r="C350" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D350" s="25"/>
       <c r="E350" s="16" t="s">
@@ -16932,11 +16924,11 @@
     </row>
     <row r="351" spans="1:11" ht="15">
       <c r="A351" s="20">
-        <v>587</v>
+        <v>1299</v>
       </c>
       <c r="B351" s="20"/>
       <c r="C351" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D351" s="25"/>
       <c r="E351" s="16" t="s">
@@ -16964,11 +16956,11 @@
     </row>
     <row r="352" spans="1:11" ht="15">
       <c r="A352" s="20">
-        <v>666.6</v>
+        <v>587</v>
       </c>
       <c r="B352" s="20"/>
       <c r="C352" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D352" s="25"/>
       <c r="E352" s="16" t="s">
@@ -16996,11 +16988,11 @@
     </row>
     <row r="353" spans="1:11" ht="15">
       <c r="A353" s="20">
-        <v>130.9</v>
+        <v>666.6</v>
       </c>
       <c r="B353" s="20"/>
       <c r="C353" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D353" s="25"/>
       <c r="E353" s="16" t="s">
@@ -17028,11 +17020,11 @@
     </row>
     <row r="354" spans="1:11" ht="15">
       <c r="A354" s="20">
-        <v>918.5</v>
+        <v>130.9</v>
       </c>
       <c r="B354" s="20"/>
       <c r="C354" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D354" s="26"/>
       <c r="E354" s="16" t="s">
@@ -17060,11 +17052,11 @@
     </row>
     <row r="355" spans="1:11" ht="15">
       <c r="A355" s="20">
-        <v>320</v>
+        <v>918.5</v>
       </c>
       <c r="B355" s="20"/>
       <c r="C355" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D355" s="25"/>
       <c r="E355" s="16" t="s">
@@ -17092,11 +17084,11 @@
     </row>
     <row r="356" spans="1:11" ht="15">
       <c r="A356" s="20">
-        <v>1269.9000000000001</v>
+        <v>320</v>
       </c>
       <c r="B356" s="20"/>
       <c r="C356" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D356" s="25"/>
       <c r="E356" s="16" t="s">
@@ -17124,11 +17116,11 @@
     </row>
     <row r="357" spans="1:11" ht="15">
       <c r="A357" s="20">
-        <v>679</v>
+        <v>1269.9000000000001</v>
       </c>
       <c r="B357" s="20"/>
       <c r="C357" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E357" s="16" t="s">
         <v>1085</v>
@@ -17155,11 +17147,11 @@
     </row>
     <row r="358" spans="1:11" ht="15">
       <c r="A358" s="20">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="B358" s="20"/>
       <c r="C358" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D358" s="27"/>
       <c r="E358" s="16" t="s">
@@ -17187,11 +17179,11 @@
     </row>
     <row r="359" spans="1:11" ht="15">
       <c r="A359" s="20">
-        <v>418</v>
+        <v>663</v>
       </c>
       <c r="B359" s="20"/>
       <c r="C359" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D359" s="25"/>
       <c r="E359" s="16" t="s">
@@ -17219,11 +17211,11 @@
     </row>
     <row r="360" spans="1:11" ht="15">
       <c r="A360" s="20">
-        <v>745</v>
+        <v>418</v>
       </c>
       <c r="B360" s="20"/>
       <c r="C360" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D360" s="25"/>
       <c r="E360" s="16" t="s">
@@ -17251,11 +17243,11 @@
     </row>
     <row r="361" spans="1:11" ht="15">
       <c r="A361" s="20">
-        <v>402.6</v>
+        <v>745</v>
       </c>
       <c r="B361" s="20"/>
       <c r="C361" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D361" s="27"/>
       <c r="E361" s="16" t="s">
@@ -17283,11 +17275,11 @@
     </row>
     <row r="362" spans="1:11" ht="15">
       <c r="A362" s="20">
-        <v>337.26</v>
+        <v>402.6</v>
       </c>
       <c r="B362" s="20"/>
       <c r="C362" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D362" s="26"/>
       <c r="E362" s="16" t="s">
@@ -17315,11 +17307,11 @@
     </row>
     <row r="363" spans="1:11" ht="15">
       <c r="A363" s="20">
-        <v>330.44</v>
+        <v>337.26</v>
       </c>
       <c r="B363" s="20"/>
       <c r="C363" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D363" s="25"/>
       <c r="E363" s="16" t="s">
@@ -17347,11 +17339,11 @@
     </row>
     <row r="364" spans="1:11" ht="15">
       <c r="A364" s="20">
-        <v>106</v>
+        <v>330.44</v>
       </c>
       <c r="B364" s="20"/>
       <c r="C364" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D364" s="25"/>
       <c r="E364" s="16" t="s">
@@ -17379,11 +17371,11 @@
     </row>
     <row r="365" spans="1:11" ht="15">
       <c r="A365" s="20">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B365" s="20"/>
       <c r="C365" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D365" s="25"/>
       <c r="E365" s="16" t="s">
@@ -17411,11 +17403,11 @@
     </row>
     <row r="366" spans="1:11" ht="15">
       <c r="A366" s="20">
-        <v>608</v>
+        <v>113</v>
       </c>
       <c r="B366" s="20"/>
       <c r="C366" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D366" s="26"/>
       <c r="E366" s="16" t="s">
@@ -17443,11 +17435,11 @@
     </row>
     <row r="367" spans="1:11" ht="15">
       <c r="A367" s="20">
-        <v>105.6</v>
+        <v>608</v>
       </c>
       <c r="B367" s="20"/>
       <c r="C367" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D367" s="25"/>
       <c r="E367" s="16" t="s">
@@ -17475,11 +17467,11 @@
     </row>
     <row r="368" spans="1:11" ht="15">
       <c r="A368" s="20">
-        <v>132</v>
+        <v>105.6</v>
       </c>
       <c r="B368" s="20"/>
       <c r="C368" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D368" s="20"/>
       <c r="E368" s="16" t="s">
@@ -17507,11 +17499,11 @@
     </row>
     <row r="369" spans="1:11" ht="15">
       <c r="A369" s="20">
-        <v>144.1</v>
+        <v>132</v>
       </c>
       <c r="B369" s="20"/>
       <c r="C369" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D369" s="20"/>
       <c r="E369" s="16" t="s">
@@ -17539,11 +17531,11 @@
     </row>
     <row r="370" spans="1:11" ht="15">
       <c r="A370" s="20">
-        <v>169.4</v>
+        <v>144.1</v>
       </c>
       <c r="B370" s="20"/>
       <c r="C370" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D370" s="25"/>
       <c r="E370" s="16" t="s">
@@ -17571,11 +17563,11 @@
     </row>
     <row r="371" spans="1:11" ht="15">
       <c r="A371" s="20">
-        <v>103.95</v>
+        <v>169.4</v>
       </c>
       <c r="B371" s="20"/>
       <c r="C371" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D371" s="25"/>
       <c r="E371" s="16" t="s">
@@ -17603,11 +17595,11 @@
     </row>
     <row r="372" spans="1:11" ht="15">
       <c r="A372" s="20">
-        <v>102</v>
+        <v>103.95</v>
       </c>
       <c r="B372" s="20"/>
       <c r="C372" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D372" s="25"/>
       <c r="E372" s="16" t="s">
@@ -17635,11 +17627,11 @@
     </row>
     <row r="373" spans="1:11" ht="15">
       <c r="A373" s="20">
-        <v>217.8</v>
+        <v>102</v>
       </c>
       <c r="B373" s="20"/>
       <c r="C373" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D373" s="20"/>
       <c r="E373" s="16" t="s">
@@ -17667,11 +17659,11 @@
     </row>
     <row r="374" spans="1:11" ht="15">
       <c r="A374" s="20">
-        <v>127.05</v>
+        <v>217.8</v>
       </c>
       <c r="B374" s="20"/>
       <c r="C374" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D374" s="20"/>
       <c r="E374" s="16" t="s">
@@ -17699,11 +17691,11 @@
     </row>
     <row r="375" spans="1:11" ht="15">
       <c r="A375" s="20">
-        <v>210.1</v>
+        <v>127.05</v>
       </c>
       <c r="B375" s="20"/>
       <c r="C375" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D375" s="25"/>
       <c r="E375" s="16" t="s">
@@ -17731,11 +17723,11 @@
     </row>
     <row r="376" spans="1:11" ht="15">
       <c r="A376" s="20">
-        <v>220</v>
+        <v>210.1</v>
       </c>
       <c r="B376" s="20"/>
       <c r="C376" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D376" s="20"/>
       <c r="E376" s="16" t="s">
@@ -17763,11 +17755,11 @@
     </row>
     <row r="377" spans="1:11" ht="15">
       <c r="A377" s="20">
-        <v>217.36</v>
+        <v>220</v>
       </c>
       <c r="B377" s="20"/>
       <c r="C377" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D377" s="25"/>
       <c r="E377" s="16" t="s">
@@ -17795,11 +17787,11 @@
     </row>
     <row r="378" spans="1:11" ht="15">
       <c r="A378" s="20">
-        <v>95</v>
+        <v>217.36</v>
       </c>
       <c r="B378" s="20"/>
       <c r="C378" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D378" s="20"/>
       <c r="E378" s="16" t="s">
@@ -17827,11 +17819,11 @@
     </row>
     <row r="379" spans="1:11" ht="15">
       <c r="A379" s="20">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B379" s="20"/>
       <c r="C379" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D379" s="20"/>
       <c r="E379" s="16" t="s">
@@ -17859,11 +17851,11 @@
     </row>
     <row r="380" spans="1:11" ht="15">
       <c r="A380" s="20">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="B380" s="20"/>
       <c r="C380" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D380" s="25"/>
       <c r="E380" s="16" t="s">
@@ -17891,11 +17883,11 @@
     </row>
     <row r="381" spans="1:11" ht="15">
       <c r="A381" s="20">
-        <v>270.05</v>
+        <v>128</v>
       </c>
       <c r="B381" s="20"/>
       <c r="C381" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D381" s="25"/>
       <c r="E381" s="16" t="s">
@@ -17923,11 +17915,11 @@
     </row>
     <row r="382" spans="1:11" ht="15">
       <c r="A382" s="20">
-        <v>150.27000000000001</v>
+        <v>270.05</v>
       </c>
       <c r="B382" s="20"/>
       <c r="C382" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D382" s="25"/>
       <c r="E382" s="16" t="s">
@@ -17955,11 +17947,11 @@
     </row>
     <row r="383" spans="1:11" ht="15">
       <c r="A383" s="20">
-        <v>57.2</v>
+        <v>150.27000000000001</v>
       </c>
       <c r="B383" s="20"/>
       <c r="C383" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D383" s="25"/>
       <c r="E383" s="16" t="s">
@@ -17987,11 +17979,11 @@
     </row>
     <row r="384" spans="1:11" ht="15">
       <c r="A384" s="20">
-        <v>393</v>
+        <v>57.2</v>
       </c>
       <c r="B384" s="20"/>
       <c r="C384" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D384" s="25"/>
       <c r="E384" s="16" t="s">
@@ -18018,10 +18010,12 @@
       </c>
     </row>
     <row r="385" spans="1:11" ht="15">
-      <c r="A385" s="20"/>
+      <c r="A385" s="20">
+        <v>393</v>
+      </c>
       <c r="B385" s="20"/>
       <c r="C385" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D385" s="25"/>
       <c r="E385" s="16" t="s">
@@ -18051,7 +18045,7 @@
       <c r="A386" s="20"/>
       <c r="B386" s="20"/>
       <c r="C386" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E386" s="16" t="s">
         <v>1163</v>
@@ -18077,12 +18071,10 @@
       </c>
     </row>
     <row r="387" spans="1:11" ht="15">
-      <c r="A387" s="20">
-        <v>624</v>
-      </c>
+      <c r="A387" s="20"/>
       <c r="B387" s="28"/>
       <c r="C387" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D387" s="27"/>
       <c r="E387" s="16" t="s">
@@ -18110,11 +18102,11 @@
     </row>
     <row r="388" spans="1:11" ht="15">
       <c r="A388" s="20">
-        <v>159</v>
+        <v>624</v>
       </c>
       <c r="B388" s="20"/>
       <c r="C388" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D388" s="27"/>
       <c r="E388" s="16" t="s">
@@ -18142,11 +18134,11 @@
     </row>
     <row r="389" spans="1:11" ht="15">
       <c r="A389" s="20">
-        <v>919</v>
+        <v>159</v>
       </c>
       <c r="B389" s="20"/>
       <c r="C389" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D389" s="20"/>
       <c r="E389" s="16" t="s">
@@ -18174,11 +18166,11 @@
     </row>
     <row r="390" spans="1:11" ht="15">
       <c r="A390" s="20">
-        <v>380</v>
+        <v>919</v>
       </c>
       <c r="B390" s="20"/>
       <c r="C390" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D390" s="25"/>
       <c r="E390" s="16" t="s">
@@ -18206,11 +18198,11 @@
     </row>
     <row r="391" spans="1:11" ht="15">
       <c r="A391" s="20">
-        <v>55.5</v>
+        <v>380</v>
       </c>
       <c r="B391" s="20"/>
       <c r="C391" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D391" s="20"/>
       <c r="E391" s="16" t="s">
@@ -18238,11 +18230,11 @@
     </row>
     <row r="392" spans="1:11" ht="15">
       <c r="A392" s="20">
-        <v>74.900000000000006</v>
+        <v>55.5</v>
       </c>
       <c r="B392" s="20"/>
       <c r="C392" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D392" s="25"/>
       <c r="E392" s="16" t="s">
@@ -18270,11 +18262,11 @@
     </row>
     <row r="393" spans="1:11" ht="15">
       <c r="A393" s="20">
-        <v>452</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="B393" s="20"/>
       <c r="C393" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D393" s="25"/>
       <c r="E393" s="16" t="s">
@@ -18302,11 +18294,11 @@
     </row>
     <row r="394" spans="1:11" ht="15">
       <c r="A394" s="20">
-        <v>459.8</v>
+        <v>452</v>
       </c>
       <c r="B394" s="20"/>
       <c r="C394" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D394" s="20"/>
       <c r="E394" s="16" t="s">
@@ -18333,10 +18325,12 @@
       </c>
     </row>
     <row r="395" spans="1:11" ht="15">
-      <c r="A395" s="20"/>
+      <c r="A395" s="20">
+        <v>459.8</v>
+      </c>
       <c r="B395" s="20"/>
       <c r="C395" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D395" s="25"/>
       <c r="E395" s="16" t="s">
@@ -18366,7 +18360,7 @@
       <c r="A396" s="20"/>
       <c r="B396" s="28"/>
       <c r="C396" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D396" s="27"/>
       <c r="E396" s="16" t="s">
@@ -18393,12 +18387,10 @@
       </c>
     </row>
     <row r="397" spans="1:11" ht="15">
-      <c r="A397" s="20">
-        <v>67.099999999999994</v>
-      </c>
+      <c r="A397" s="20"/>
       <c r="B397" s="28"/>
       <c r="C397" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E397" s="16" t="s">
         <v>1192</v>
@@ -18425,11 +18417,11 @@
     </row>
     <row r="398" spans="1:11" ht="15">
       <c r="A398" s="20">
-        <v>110.11</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="B398" s="20"/>
       <c r="C398" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D398" s="25"/>
       <c r="E398" s="16" t="s">
@@ -18457,11 +18449,11 @@
     </row>
     <row r="399" spans="1:11" ht="15">
       <c r="A399" s="20">
-        <v>121</v>
+        <v>110.11</v>
       </c>
       <c r="B399" s="20"/>
       <c r="C399" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E399" s="16" t="s">
         <v>1198</v>
@@ -18488,11 +18480,11 @@
     </row>
     <row r="400" spans="1:11" ht="15">
       <c r="A400" s="20">
-        <v>110.11</v>
+        <v>121</v>
       </c>
       <c r="B400" s="20"/>
       <c r="C400" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D400" s="14"/>
       <c r="E400" s="16" t="s">
@@ -18520,11 +18512,11 @@
     </row>
     <row r="401" spans="1:11" ht="15">
       <c r="A401" s="20">
-        <v>72.28</v>
+        <v>110.11</v>
       </c>
       <c r="B401" s="20"/>
       <c r="C401" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D401" s="14"/>
       <c r="E401" s="16" t="s">
@@ -18552,11 +18544,11 @@
     </row>
     <row r="402" spans="1:11" ht="15">
       <c r="A402" s="20">
-        <v>342.1</v>
+        <v>72.28</v>
       </c>
       <c r="B402" s="20"/>
       <c r="C402" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D402" s="25"/>
       <c r="E402" s="16" t="s">
@@ -18584,11 +18576,11 @@
     </row>
     <row r="403" spans="1:11" ht="15">
       <c r="A403" s="20">
-        <v>33.72</v>
+        <v>342.1</v>
       </c>
       <c r="B403" s="20"/>
       <c r="C403" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D403" s="25"/>
       <c r="E403" s="16" t="s">
@@ -18616,11 +18608,11 @@
     </row>
     <row r="404" spans="1:11" ht="15">
       <c r="A404" s="20">
-        <v>366</v>
+        <v>33.72</v>
       </c>
       <c r="B404" s="20"/>
       <c r="C404" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D404" s="25"/>
       <c r="E404" s="16" t="s">
@@ -18648,11 +18640,11 @@
     </row>
     <row r="405" spans="1:11" ht="15">
       <c r="A405" s="20">
-        <v>535</v>
+        <v>366</v>
       </c>
       <c r="B405" s="20"/>
       <c r="C405" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D405" s="25"/>
       <c r="E405" s="16" t="s">
@@ -18680,11 +18672,11 @@
     </row>
     <row r="406" spans="1:11" ht="15">
       <c r="A406" s="20">
-        <v>335.5</v>
+        <v>535</v>
       </c>
       <c r="B406" s="20"/>
       <c r="C406" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D406" s="20"/>
       <c r="E406" s="16" t="s">
@@ -18712,11 +18704,11 @@
     </row>
     <row r="407" spans="1:11" ht="15">
       <c r="A407" s="20">
-        <v>369.99</v>
+        <v>335.5</v>
       </c>
       <c r="B407" s="20"/>
       <c r="C407" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D407" s="20"/>
       <c r="E407" s="16" t="s">
@@ -18744,11 +18736,11 @@
     </row>
     <row r="408" spans="1:11" ht="15">
       <c r="A408" s="20">
-        <v>680</v>
+        <v>369.99</v>
       </c>
       <c r="B408" s="20"/>
       <c r="C408" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D408" s="25"/>
       <c r="E408" s="16" t="s">
@@ -18776,18 +18768,18 @@
     </row>
     <row r="409" spans="1:11" ht="15">
       <c r="A409" s="20">
-        <v>96.8</v>
+        <v>680</v>
       </c>
       <c r="B409" s="20"/>
       <c r="C409" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D409" s="25"/>
       <c r="E409" s="16" t="s">
         <v>1232</v>
       </c>
       <c r="F409" s="15" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="G409" s="8" t="s">
         <v>1233</v>
@@ -18808,11 +18800,11 @@
     </row>
     <row r="410" spans="1:11" ht="15">
       <c r="A410" s="20">
-        <v>36.5</v>
+        <v>96.8</v>
       </c>
       <c r="B410" s="20"/>
       <c r="C410" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D410" s="23"/>
       <c r="E410" s="16" t="s">
@@ -18840,21 +18832,21 @@
     </row>
     <row r="411" spans="1:11" ht="15">
       <c r="A411" s="20">
-        <v>225.5</v>
+        <v>36.5</v>
       </c>
       <c r="B411" s="20"/>
       <c r="C411" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D411" s="20"/>
       <c r="E411" s="16" t="s">
         <v>1237</v>
       </c>
       <c r="F411" s="11" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G411" s="11" t="s">
         <v>1400</v>
-      </c>
-      <c r="G411" s="11" t="s">
-        <v>1401</v>
       </c>
       <c r="H411" s="4">
         <f t="shared" si="23"/>
@@ -18872,11 +18864,11 @@
     </row>
     <row r="412" spans="1:11" ht="15">
       <c r="A412" s="20">
-        <v>183</v>
+        <v>225.5</v>
       </c>
       <c r="B412" s="20"/>
       <c r="C412" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D412" s="25"/>
       <c r="E412" s="16" t="s">
@@ -18904,11 +18896,11 @@
     </row>
     <row r="413" spans="1:11" ht="15">
       <c r="A413" s="20">
-        <v>149.6</v>
+        <v>183</v>
       </c>
       <c r="B413" s="20"/>
       <c r="C413" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D413" s="25"/>
       <c r="E413" s="16" t="s">
@@ -18936,11 +18928,11 @@
     </row>
     <row r="414" spans="1:11" ht="15">
       <c r="A414" s="20">
-        <v>599</v>
+        <v>149.6</v>
       </c>
       <c r="B414" s="20"/>
       <c r="C414" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D414" s="25"/>
       <c r="E414" s="15" t="s">
@@ -18968,11 +18960,11 @@
     </row>
     <row r="415" spans="1:11" ht="15">
       <c r="A415" s="20">
-        <v>145</v>
+        <v>599</v>
       </c>
       <c r="B415" s="20"/>
       <c r="C415" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E415" s="16" t="s">
         <v>1247</v>
@@ -18999,11 +18991,11 @@
     </row>
     <row r="416" spans="1:11" ht="15">
       <c r="A416" s="20">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="B416" s="20"/>
       <c r="C416" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E416" s="16" t="s">
         <v>1250</v>
@@ -19030,11 +19022,11 @@
     </row>
     <row r="417" spans="1:11" ht="15">
       <c r="A417" s="20">
-        <v>96.8</v>
+        <v>105</v>
       </c>
       <c r="B417" s="20"/>
       <c r="C417" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E417" s="16" t="s">
         <v>1253</v>
@@ -19061,11 +19053,11 @@
     </row>
     <row r="418" spans="1:11" ht="15">
       <c r="A418" s="20">
-        <v>146.30000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="B418" s="20"/>
       <c r="C418" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D418" s="20"/>
       <c r="E418" s="16" t="s">
@@ -19093,11 +19085,11 @@
     </row>
     <row r="419" spans="1:11" ht="15">
       <c r="A419" s="20">
-        <v>83</v>
+        <v>146.30000000000001</v>
       </c>
       <c r="B419" s="20"/>
       <c r="C419" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D419" s="25"/>
       <c r="E419" s="16" t="s">
@@ -19125,11 +19117,11 @@
     </row>
     <row r="420" spans="1:11" ht="15">
       <c r="A420" s="20">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="B420" s="20"/>
       <c r="C420" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D420" s="25"/>
       <c r="E420" s="16" t="s">
@@ -19157,11 +19149,11 @@
     </row>
     <row r="421" spans="1:11" ht="15">
       <c r="A421" s="20">
-        <v>94.6</v>
+        <v>117</v>
       </c>
       <c r="B421" s="20"/>
       <c r="C421" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D421" s="25"/>
       <c r="E421" s="16" t="s">
@@ -19189,11 +19181,11 @@
     </row>
     <row r="422" spans="1:11" ht="15">
       <c r="A422" s="20">
-        <v>115</v>
+        <v>94.6</v>
       </c>
       <c r="B422" s="20"/>
       <c r="C422" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E422" s="15">
         <v>88300196814</v>
@@ -19220,11 +19212,11 @@
     </row>
     <row r="423" spans="1:11" ht="15">
       <c r="A423" s="20">
-        <v>416.76</v>
+        <v>115</v>
       </c>
       <c r="B423" s="20"/>
       <c r="C423" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D423" s="25"/>
       <c r="E423" s="16" t="s">
@@ -19252,11 +19244,11 @@
     </row>
     <row r="424" spans="1:11" ht="15">
       <c r="A424" s="20">
-        <v>95.7</v>
+        <v>416.76</v>
       </c>
       <c r="B424" s="20"/>
       <c r="C424" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D424" s="25"/>
       <c r="E424" s="16" t="s">
@@ -19284,11 +19276,11 @@
     </row>
     <row r="425" spans="1:11" ht="15">
       <c r="A425" s="20">
-        <v>112.2</v>
+        <v>95.7</v>
       </c>
       <c r="B425" s="20"/>
       <c r="C425" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D425" s="20"/>
       <c r="E425" s="16" t="s">
@@ -19316,11 +19308,11 @@
     </row>
     <row r="426" spans="1:11" ht="15">
       <c r="A426" s="20">
-        <v>150</v>
+        <v>112.2</v>
       </c>
       <c r="B426" s="20"/>
       <c r="C426" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E426" s="16" t="s">
         <v>1276</v>
@@ -19347,11 +19339,11 @@
     </row>
     <row r="427" spans="1:11" ht="15">
       <c r="A427" s="20">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="B427" s="20"/>
       <c r="C427" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D427" s="20"/>
       <c r="E427" s="16" t="s">
@@ -19379,11 +19371,11 @@
     </row>
     <row r="428" spans="1:11" ht="15">
       <c r="A428" s="20">
-        <v>121.55</v>
+        <v>219</v>
       </c>
       <c r="B428" s="20"/>
       <c r="C428" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D428" s="20"/>
       <c r="E428" s="16" t="s">
@@ -19411,11 +19403,11 @@
     </row>
     <row r="429" spans="1:11" ht="15">
       <c r="A429" s="20">
-        <v>219</v>
+        <v>121.55</v>
       </c>
       <c r="B429" s="20"/>
       <c r="C429" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D429" s="25"/>
       <c r="E429" s="16" t="s">
@@ -19443,11 +19435,11 @@
     </row>
     <row r="430" spans="1:11" ht="15">
       <c r="A430" s="20">
-        <v>553.29999999999995</v>
+        <v>219</v>
       </c>
       <c r="B430" s="20"/>
       <c r="C430" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D430" s="26"/>
       <c r="E430" s="16" t="s">
@@ -19475,11 +19467,11 @@
     </row>
     <row r="431" spans="1:11" ht="15">
       <c r="A431" s="20">
-        <v>169</v>
+        <v>553.29999999999995</v>
       </c>
       <c r="B431" s="20"/>
       <c r="C431" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D431" s="25"/>
       <c r="E431" s="16" t="s">
@@ -19507,11 +19499,11 @@
     </row>
     <row r="432" spans="1:11" ht="15">
       <c r="A432" s="20">
-        <v>33.5</v>
+        <v>169</v>
       </c>
       <c r="B432" s="20"/>
       <c r="C432" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D432" s="26"/>
       <c r="E432" s="16" t="s">
@@ -19539,11 +19531,11 @@
     </row>
     <row r="433" spans="1:11" ht="15">
       <c r="A433" s="20">
-        <v>214.5</v>
+        <v>33.5</v>
       </c>
       <c r="B433" s="20"/>
       <c r="C433" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="D433" s="20"/>
       <c r="E433" s="16" t="s">
@@ -19571,17 +19563,17 @@
     </row>
     <row r="434" spans="1:11" ht="15">
       <c r="A434" s="20">
-        <v>101.2</v>
+        <v>214.5</v>
       </c>
       <c r="B434" s="20"/>
       <c r="C434" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E434" s="16" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F434" s="16" t="s">
         <v>1382</v>
-      </c>
-      <c r="F434" s="16" t="s">
-        <v>1383</v>
       </c>
       <c r="G434" s="16" t="s">
         <v>699</v>
@@ -19602,20 +19594,20 @@
     </row>
     <row r="435" spans="1:11" ht="15">
       <c r="A435" s="20">
-        <v>127.6</v>
+        <v>101.2</v>
       </c>
       <c r="B435" s="20"/>
       <c r="C435" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E435" s="16" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F435" s="16" t="s">
         <v>1385</v>
       </c>
-      <c r="F435" s="16" t="s">
+      <c r="G435" s="16" t="s">
         <v>1386</v>
-      </c>
-      <c r="G435" s="16" t="s">
-        <v>1387</v>
       </c>
       <c r="H435" s="4">
         <f t="shared" si="24"/>
@@ -19633,20 +19625,20 @@
     </row>
     <row r="436" spans="1:11" ht="15">
       <c r="A436" s="20">
-        <v>259.05</v>
+        <v>127.6</v>
       </c>
       <c r="B436" s="20"/>
       <c r="C436" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E436" s="16" t="s">
+        <v>1387</v>
+      </c>
+      <c r="F436" s="16" t="s">
         <v>1388</v>
       </c>
-      <c r="F436" s="16" t="s">
-        <v>1389</v>
-      </c>
       <c r="G436" s="16" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H436" s="4">
         <f t="shared" si="24"/>
@@ -19664,19 +19656,19 @@
     </row>
     <row r="437" spans="1:11" ht="15">
       <c r="A437" s="20">
-        <v>198</v>
+        <v>259.05</v>
       </c>
       <c r="C437" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E437" s="16" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="F437" s="8" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G437" s="8" t="s">
         <v>1390</v>
-      </c>
-      <c r="G437" s="8" t="s">
-        <v>1391</v>
       </c>
       <c r="H437" s="4">
         <f t="shared" si="24"/>
@@ -19693,20 +19685,20 @@
       </c>
     </row>
     <row r="438" spans="1:11" ht="15">
-      <c r="A438">
-        <v>218.5</v>
+      <c r="A438" s="20">
+        <v>198</v>
       </c>
       <c r="C438" s="22" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="E438" s="16" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F438" s="8" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G438" s="8" t="s">
         <v>1392</v>
-      </c>
-      <c r="G438" s="8" t="s">
-        <v>1393</v>
       </c>
       <c r="H438" s="4">
         <f t="shared" si="24"/>
@@ -19728,14 +19720,14 @@
       </c>
       <c r="B439" s="20"/>
       <c r="C439" s="22" t="s">
-        <v>1404</v>
+        <v>1376</v>
       </c>
       <c r="D439" s="20"/>
       <c r="E439" s="16" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F439" s="16" t="s">
         <v>1402</v>
-      </c>
-      <c r="F439" s="16" t="s">
-        <v>1403</v>
       </c>
       <c r="H439" s="4">
         <f t="shared" si="24"/>
@@ -19750,6 +19742,39 @@
       <c r="K439" s="29">
         <v>2130</v>
       </c>
+    </row>
+    <row r="440" spans="1:11">
+      <c r="A440" s="20"/>
+    </row>
+    <row r="441" spans="1:11">
+      <c r="A441" s="20"/>
+    </row>
+    <row r="442" spans="1:11">
+      <c r="A442" s="20"/>
+    </row>
+    <row r="443" spans="1:11">
+      <c r="A443" s="20"/>
+    </row>
+    <row r="444" spans="1:11">
+      <c r="A444" s="20"/>
+    </row>
+    <row r="445" spans="1:11">
+      <c r="A445" s="20"/>
+    </row>
+    <row r="446" spans="1:11">
+      <c r="A446" s="20"/>
+    </row>
+    <row r="447" spans="1:11">
+      <c r="A447" s="20"/>
+    </row>
+    <row r="448" spans="1:11">
+      <c r="A448" s="20"/>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="20"/>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="20"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -21301,6 +21326,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+  <pixelatorList sheetStid="3"/>
+</pixelators>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0">
@@ -21318,16 +21351,8 @@
 </woProps>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-  <pixelatorList sheetStid="3"/>
-</pixelators>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -21336,7 +21361,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>

--- a/模块开发/录入表.xlsx
+++ b/模块开发/录入表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/上手/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vincentli/PycharmProjects/PythonProject/2026-4 群控/yolo/整合详情页采集/模块开发/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDD949E-ECE5-6E4E-BBBE-BD39A328EDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026F6385-21B4-814F-AD2F-3D3E72B04A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30160" yWindow="-6360" windowWidth="30960" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5798,14 +5798,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="112">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="111">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6559,19 +6552,19 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6808,25 +6801,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
     <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{3AD70849-3F6B-ADC2-5487-646933379502}">
-      <tableStyleElement type="wholeTable" dxfId="111"/>
-      <tableStyleElement type="headerRow" dxfId="110"/>
-      <tableStyleElement type="totalRow" dxfId="109"/>
-      <tableStyleElement type="firstColumn" dxfId="108"/>
-      <tableStyleElement type="lastColumn" dxfId="107"/>
-      <tableStyleElement type="firstRowStripe" dxfId="106"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="105"/>
+      <tableStyleElement type="wholeTable" dxfId="110"/>
+      <tableStyleElement type="headerRow" dxfId="109"/>
+      <tableStyleElement type="totalRow" dxfId="108"/>
+      <tableStyleElement type="firstColumn" dxfId="107"/>
+      <tableStyleElement type="lastColumn" dxfId="106"/>
+      <tableStyleElement type="firstRowStripe" dxfId="105"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="104"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{B0E6D76F-EA8E-7237-5487-6469988B1DE4}">
-      <tableStyleElement type="headerRow" dxfId="104"/>
-      <tableStyleElement type="totalRow" dxfId="103"/>
-      <tableStyleElement type="firstRowStripe" dxfId="102"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="101"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="100"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="99"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="98"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="97"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="96"/>
-      <tableStyleElement type="pageFieldValues" dxfId="95"/>
+      <tableStyleElement type="headerRow" dxfId="103"/>
+      <tableStyleElement type="totalRow" dxfId="102"/>
+      <tableStyleElement type="firstRowStripe" dxfId="101"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="100"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="99"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="98"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="97"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="96"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="95"/>
+      <tableStyleElement type="pageFieldValues" dxfId="94"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -7189,7 +7182,7 @@
     </row>
     <row r="3" spans="1:11" ht="15">
       <c r="A3" s="20">
-        <v>162.80000000000001</v>
+        <v>170.5</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="22" t="s">
@@ -7221,7 +7214,7 @@
     </row>
     <row r="4" spans="1:11" ht="15">
       <c r="A4" s="20">
-        <v>206.8</v>
+        <v>278</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="22" t="s">
@@ -7253,7 +7246,7 @@
     </row>
     <row r="5" spans="1:11" ht="15">
       <c r="A5" s="20">
-        <v>182.6</v>
+        <v>183.15</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="22" t="s">
@@ -7285,7 +7278,7 @@
     </row>
     <row r="6" spans="1:11" ht="15">
       <c r="A6" s="20">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="22" t="s">
@@ -7317,7 +7310,7 @@
     </row>
     <row r="7" spans="1:11" ht="15">
       <c r="A7" s="20">
-        <v>79.900000000000006</v>
+        <v>58</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="22" t="s">
@@ -7349,7 +7342,7 @@
     </row>
     <row r="8" spans="1:11" ht="15">
       <c r="A8" s="20">
-        <v>230</v>
+        <v>125.4</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="22" t="s">
@@ -7381,7 +7374,7 @@
     </row>
     <row r="9" spans="1:11" ht="15">
       <c r="A9" s="20">
-        <v>440</v>
+        <v>460.9</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="22" t="s">
@@ -7413,7 +7406,7 @@
     </row>
     <row r="10" spans="1:11" ht="15">
       <c r="A10" s="20">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="22" t="s">
@@ -7445,7 +7438,7 @@
     </row>
     <row r="11" spans="1:11" ht="15">
       <c r="A11" s="20">
-        <v>208</v>
+        <v>229.9</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="22" t="s">
@@ -7477,7 +7470,7 @@
     </row>
     <row r="12" spans="1:11" ht="15">
       <c r="A12" s="20">
-        <v>168.3</v>
+        <v>209</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="22" t="s">
@@ -7509,7 +7502,7 @@
     </row>
     <row r="13" spans="1:11" ht="15">
       <c r="A13" s="20">
-        <v>239.8</v>
+        <v>220</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="22" t="s">
@@ -7541,7 +7534,7 @@
     </row>
     <row r="14" spans="1:11" ht="15">
       <c r="A14" s="20">
-        <v>169.4</v>
+        <v>245.3</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="22" t="s">
@@ -7573,7 +7566,7 @@
     </row>
     <row r="15" spans="1:11" ht="15">
       <c r="A15" s="20">
-        <v>135.30000000000001</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="22" t="s">
@@ -7605,7 +7598,7 @@
     </row>
     <row r="16" spans="1:11" ht="15">
       <c r="A16" s="20">
-        <v>225.5</v>
+        <v>245.3</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="22" t="s">
@@ -7636,7 +7629,7 @@
     </row>
     <row r="17" spans="1:11" ht="15">
       <c r="A17" s="20">
-        <v>171.6</v>
+        <v>205.08</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="22" t="s">
@@ -7668,7 +7661,7 @@
     </row>
     <row r="18" spans="1:11" ht="15">
       <c r="A18" s="20">
-        <v>161.69999999999999</v>
+        <v>152</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="22" t="s">
@@ -7700,7 +7693,7 @@
     </row>
     <row r="19" spans="1:11" ht="15">
       <c r="A19" s="20">
-        <v>51.8</v>
+        <v>49.4</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="22" t="s">
@@ -7860,7 +7853,7 @@
     </row>
     <row r="24" spans="1:11" ht="15">
       <c r="A24" s="20">
-        <v>12.95</v>
+        <v>14.24</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="22" t="s">
@@ -7892,7 +7885,7 @@
     </row>
     <row r="25" spans="1:11" ht="15">
       <c r="A25" s="20">
-        <v>777.7</v>
+        <v>857</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="22" t="s">
@@ -7923,9 +7916,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15">
-      <c r="A26" s="20">
-        <v>959</v>
-      </c>
+      <c r="A26" s="20"/>
       <c r="B26" s="20"/>
       <c r="C26" s="22" t="s">
         <v>1376</v>
@@ -7956,7 +7947,7 @@
     </row>
     <row r="27" spans="1:11" ht="15">
       <c r="A27" s="20">
-        <v>1089</v>
+        <v>1399</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="22" t="s">
@@ -7988,7 +7979,7 @@
     </row>
     <row r="28" spans="1:11" ht="15">
       <c r="A28" s="20">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="22" t="s">
@@ -8020,7 +8011,7 @@
     </row>
     <row r="29" spans="1:11" ht="15">
       <c r="A29" s="20">
-        <v>931.7</v>
+        <v>950</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="22" t="s">
@@ -8052,7 +8043,7 @@
     </row>
     <row r="30" spans="1:11" ht="15">
       <c r="A30" s="20">
-        <v>1150</v>
+        <v>2179</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="22" t="s">
@@ -8084,7 +8075,7 @@
     </row>
     <row r="31" spans="1:11" ht="15">
       <c r="A31" s="20">
-        <v>1150</v>
+        <v>2179</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="22" t="s">
@@ -8180,7 +8171,7 @@
     </row>
     <row r="34" spans="1:11" ht="15">
       <c r="A34" s="20">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="22" t="s">
@@ -8212,7 +8203,7 @@
     </row>
     <row r="35" spans="1:11" ht="15">
       <c r="A35" s="20">
-        <v>77.599999999999994</v>
+        <v>196.9</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="22" t="s">
@@ -8308,7 +8299,7 @@
     </row>
     <row r="38" spans="1:11" ht="15">
       <c r="A38" s="20">
-        <v>157.99</v>
+        <v>157.97999999999999</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="22" t="s">
@@ -8340,7 +8331,7 @@
     </row>
     <row r="39" spans="1:11" ht="15">
       <c r="A39" s="20">
-        <v>1555.4</v>
+        <v>1593.9</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="22" t="s">
@@ -8404,7 +8395,7 @@
     </row>
     <row r="41" spans="1:11" ht="15">
       <c r="A41" s="20">
-        <v>26.29</v>
+        <v>29.45</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="22" t="s">
@@ -8467,7 +8458,7 @@
     </row>
     <row r="43" spans="1:11" ht="15">
       <c r="A43" s="20">
-        <v>140.36000000000001</v>
+        <v>133.9</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="22" t="s">
@@ -8499,7 +8490,7 @@
     </row>
     <row r="44" spans="1:11" ht="15">
       <c r="A44" s="20">
-        <v>140.36000000000001</v>
+        <v>133.9</v>
       </c>
       <c r="B44" s="20"/>
       <c r="C44" s="22" t="s">
@@ -8531,7 +8522,7 @@
     </row>
     <row r="45" spans="1:11" ht="15">
       <c r="A45" s="20">
-        <v>499</v>
+        <v>465.08</v>
       </c>
       <c r="B45" s="20"/>
       <c r="C45" s="22" t="s">
@@ -8563,7 +8554,7 @@
     </row>
     <row r="46" spans="1:11" ht="15">
       <c r="A46" s="20">
-        <v>235</v>
+        <v>328</v>
       </c>
       <c r="B46" s="20"/>
       <c r="C46" s="22" t="s">
@@ -8595,7 +8586,7 @@
     </row>
     <row r="47" spans="1:11" ht="15">
       <c r="A47" s="20">
-        <v>303.60000000000002</v>
+        <v>488</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="22" t="s">
@@ -8627,7 +8618,7 @@
     </row>
     <row r="48" spans="1:11" ht="15">
       <c r="A48" s="20">
-        <v>218</v>
+        <v>286</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="22" t="s">
@@ -8691,7 +8682,7 @@
     </row>
     <row r="50" spans="1:11" ht="15">
       <c r="A50" s="20">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="22" t="s">
@@ -8723,7 +8714,7 @@
     </row>
     <row r="51" spans="1:11" ht="15">
       <c r="A51" s="20">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="22" t="s">
@@ -8755,7 +8746,7 @@
     </row>
     <row r="52" spans="1:11" ht="15">
       <c r="A52" s="20">
-        <v>340.45</v>
+        <v>254.43</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="22" t="s">
@@ -8787,7 +8778,7 @@
     </row>
     <row r="53" spans="1:11" ht="15">
       <c r="A53" s="20">
-        <v>312</v>
+        <v>317.35000000000002</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="22" t="s">
@@ -8819,7 +8810,7 @@
     </row>
     <row r="54" spans="1:11" ht="15">
       <c r="A54" s="20">
-        <v>249.04</v>
+        <v>231.66</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="22" t="s">
@@ -8851,7 +8842,7 @@
     </row>
     <row r="55" spans="1:11" ht="15">
       <c r="A55" s="20">
-        <v>438</v>
+        <v>492.18</v>
       </c>
       <c r="B55" s="20"/>
       <c r="C55" s="22" t="s">
@@ -8883,7 +8874,7 @@
     </row>
     <row r="56" spans="1:11" ht="15">
       <c r="A56" s="20">
-        <v>569</v>
+        <v>619.82000000000005</v>
       </c>
       <c r="B56" s="20"/>
       <c r="C56" s="22" t="s">
@@ -8915,7 +8906,7 @@
     </row>
     <row r="57" spans="1:11" ht="15">
       <c r="A57" s="20">
-        <v>736.9</v>
+        <v>676.5</v>
       </c>
       <c r="B57" s="20"/>
       <c r="C57" s="22" t="s">
@@ -8947,7 +8938,7 @@
     </row>
     <row r="58" spans="1:11" ht="15">
       <c r="A58" s="20">
-        <v>327.47000000000003</v>
+        <v>310.2</v>
       </c>
       <c r="B58" s="20"/>
       <c r="C58" s="22" t="s">
@@ -9011,7 +9002,7 @@
     </row>
     <row r="60" spans="1:11" ht="15">
       <c r="A60" s="20">
-        <v>163.79</v>
+        <v>152.02000000000001</v>
       </c>
       <c r="B60" s="20"/>
       <c r="C60" s="22" t="s">
@@ -9043,7 +9034,7 @@
     </row>
     <row r="61" spans="1:11" ht="15">
       <c r="A61" s="20">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="B61" s="20"/>
       <c r="C61" s="22" t="s">
@@ -9075,7 +9066,7 @@
     </row>
     <row r="62" spans="1:11" ht="15">
       <c r="A62" s="20">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B62" s="20"/>
       <c r="C62" s="22" t="s">
@@ -9107,7 +9098,7 @@
     </row>
     <row r="63" spans="1:11" ht="15">
       <c r="A63" s="20">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="22" t="s">
@@ -9139,7 +9130,7 @@
     </row>
     <row r="64" spans="1:11" ht="15">
       <c r="A64" s="20">
-        <v>146.6</v>
+        <v>202</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="22" t="s">
@@ -9171,7 +9162,7 @@
     </row>
     <row r="65" spans="1:11" ht="15">
       <c r="A65" s="20">
-        <v>56.9</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="22" t="s">
@@ -9203,7 +9194,7 @@
     </row>
     <row r="66" spans="1:11" ht="15">
       <c r="A66" s="20">
-        <v>176</v>
+        <v>299</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="22" t="s">
@@ -9267,7 +9258,7 @@
     </row>
     <row r="68" spans="1:11" ht="15">
       <c r="A68" s="20">
-        <v>299.5</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="22" t="s">
@@ -9299,7 +9290,7 @@
     </row>
     <row r="69" spans="1:11" ht="15">
       <c r="A69" s="20">
-        <v>176</v>
+        <v>199.98</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="22" t="s">
@@ -9331,7 +9322,7 @@
     </row>
     <row r="70" spans="1:11" ht="15">
       <c r="A70" s="20">
-        <v>1141.8</v>
+        <v>1406.9</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="22" t="s">
@@ -9363,7 +9354,7 @@
     </row>
     <row r="71" spans="1:11" ht="15">
       <c r="A71" s="20">
-        <v>113.3</v>
+        <v>113.85</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="22" t="s">
@@ -9395,7 +9386,7 @@
     </row>
     <row r="72" spans="1:11" ht="15">
       <c r="A72" s="20">
-        <v>96.2</v>
+        <v>107.25</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="22" t="s">
@@ -9459,7 +9450,7 @@
     </row>
     <row r="74" spans="1:11" ht="15">
       <c r="A74" s="20">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="22" t="s">
@@ -9491,7 +9482,7 @@
     </row>
     <row r="75" spans="1:11" ht="15">
       <c r="A75" s="20">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="22" t="s">
@@ -9523,7 +9514,7 @@
     </row>
     <row r="76" spans="1:11" ht="15">
       <c r="A76" s="20">
-        <v>468</v>
+        <v>395</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="22" t="s">
@@ -9555,7 +9546,7 @@
     </row>
     <row r="77" spans="1:11" ht="15">
       <c r="A77" s="20">
-        <v>218</v>
+        <v>218.99</v>
       </c>
       <c r="B77" s="20"/>
       <c r="C77" s="22" t="s">
@@ -9587,7 +9578,7 @@
     </row>
     <row r="78" spans="1:11" ht="15">
       <c r="A78" s="20">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B78" s="20"/>
       <c r="C78" s="22" t="s">
@@ -9619,7 +9610,7 @@
     </row>
     <row r="79" spans="1:11" ht="15">
       <c r="A79" s="20">
-        <v>191.1</v>
+        <v>371</v>
       </c>
       <c r="B79" s="20"/>
       <c r="C79" s="22" t="s">
@@ -9683,7 +9674,7 @@
     </row>
     <row r="81" spans="1:11" ht="15">
       <c r="A81" s="20">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B81" s="20"/>
       <c r="C81" s="22" t="s">
@@ -9714,9 +9705,7 @@
       </c>
     </row>
     <row r="82" spans="1:11" ht="15">
-      <c r="A82" s="20">
-        <v>103.4</v>
-      </c>
+      <c r="A82" s="20"/>
       <c r="B82" s="20"/>
       <c r="C82" s="22" t="s">
         <v>1376</v>
@@ -9747,7 +9736,7 @@
     </row>
     <row r="83" spans="1:11" ht="15">
       <c r="A83" s="20">
-        <v>94</v>
+        <v>107.8</v>
       </c>
       <c r="B83" s="20"/>
       <c r="C83" s="22" t="s">
@@ -9779,7 +9768,7 @@
     </row>
     <row r="84" spans="1:11" ht="15">
       <c r="A84" s="20">
-        <v>117</v>
+        <v>117.7</v>
       </c>
       <c r="B84" s="20"/>
       <c r="C84" s="22" t="s">
@@ -9843,7 +9832,7 @@
     </row>
     <row r="86" spans="1:11" ht="15">
       <c r="A86" s="20">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="22" t="s">
@@ -9875,7 +9864,7 @@
     </row>
     <row r="87" spans="1:11" ht="15">
       <c r="A87" s="20">
-        <v>110</v>
+        <v>98.2</v>
       </c>
       <c r="B87" s="20"/>
       <c r="C87" s="22" t="s">
@@ -9907,7 +9896,7 @@
     </row>
     <row r="88" spans="1:11" ht="15">
       <c r="A88" s="20">
-        <v>97.8</v>
+        <v>169</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="22" t="s">
@@ -9939,7 +9928,7 @@
     </row>
     <row r="89" spans="1:11" ht="15">
       <c r="A89" s="20">
-        <v>82</v>
+        <v>78.8</v>
       </c>
       <c r="B89" s="20"/>
       <c r="C89" s="22" t="s">
@@ -9971,7 +9960,7 @@
     </row>
     <row r="90" spans="1:11" ht="15">
       <c r="A90" s="20">
-        <v>53.9</v>
+        <v>54.56</v>
       </c>
       <c r="B90" s="20"/>
       <c r="C90" s="22" t="s">
@@ -10003,7 +9992,7 @@
     </row>
     <row r="91" spans="1:11" ht="15">
       <c r="A91" s="20">
-        <v>470.8</v>
+        <v>438.9</v>
       </c>
       <c r="B91" s="20"/>
       <c r="C91" s="22" t="s">
@@ -10035,7 +10024,7 @@
     </row>
     <row r="92" spans="1:11" ht="15">
       <c r="A92" s="20">
-        <v>160.6</v>
+        <v>167</v>
       </c>
       <c r="B92" s="20"/>
       <c r="C92" s="22" t="s">
@@ -10067,7 +10056,7 @@
     </row>
     <row r="93" spans="1:11" ht="15">
       <c r="A93" s="20">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="B93" s="20"/>
       <c r="C93" s="22" t="s">
@@ -10099,7 +10088,7 @@
     </row>
     <row r="94" spans="1:11" ht="15">
       <c r="A94" s="20">
-        <v>499</v>
+        <v>218</v>
       </c>
       <c r="B94" s="20"/>
       <c r="C94" s="22" t="s">
@@ -10195,7 +10184,7 @@
     </row>
     <row r="97" spans="1:11" ht="15">
       <c r="A97" s="20">
-        <v>239</v>
+        <v>207.9</v>
       </c>
       <c r="B97" s="20"/>
       <c r="C97" s="22" t="s">
@@ -10227,7 +10216,7 @@
     </row>
     <row r="98" spans="1:11" ht="15">
       <c r="A98" s="20">
-        <v>243.1</v>
+        <v>350.9</v>
       </c>
       <c r="B98" s="20"/>
       <c r="C98" s="22" t="s">
@@ -10323,7 +10312,7 @@
     </row>
     <row r="101" spans="1:11" ht="15">
       <c r="A101" s="20">
-        <v>691.9</v>
+        <v>650.1</v>
       </c>
       <c r="B101" s="20"/>
       <c r="C101" s="22" t="s">
@@ -10387,7 +10376,7 @@
     </row>
     <row r="103" spans="1:11" ht="15">
       <c r="A103" s="20">
-        <v>1954.7</v>
+        <v>2198.9</v>
       </c>
       <c r="B103" s="20"/>
       <c r="C103" s="22" t="s">
@@ -10419,7 +10408,7 @@
     </row>
     <row r="104" spans="1:11" ht="15">
       <c r="A104" s="20">
-        <v>688</v>
+        <v>753.61</v>
       </c>
       <c r="B104" s="20"/>
       <c r="C104" s="22" t="s">
@@ -10451,7 +10440,7 @@
     </row>
     <row r="105" spans="1:11" ht="15">
       <c r="A105" s="20">
-        <v>1999</v>
+        <v>2858.9</v>
       </c>
       <c r="B105" s="20"/>
       <c r="C105" s="22" t="s">
@@ -10483,7 +10472,7 @@
     </row>
     <row r="106" spans="1:11" ht="15">
       <c r="A106" s="20">
-        <v>686</v>
+        <v>799</v>
       </c>
       <c r="B106" s="20"/>
       <c r="C106" s="22" t="s">
@@ -10515,7 +10504,7 @@
     </row>
     <row r="107" spans="1:11" ht="15">
       <c r="A107" s="20">
-        <v>1999</v>
+        <v>2263</v>
       </c>
       <c r="B107" s="20"/>
       <c r="C107" s="22" t="s">
@@ -10547,7 +10536,7 @@
     </row>
     <row r="108" spans="1:11" ht="15">
       <c r="A108" s="20">
-        <v>2859</v>
+        <v>3958.9</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="22" t="s">
@@ -10608,7 +10597,7 @@
     </row>
     <row r="110" spans="1:11" ht="15">
       <c r="A110" s="20">
-        <v>2180</v>
+        <v>1200</v>
       </c>
       <c r="B110" s="20"/>
       <c r="C110" s="22" t="s">
@@ -10672,7 +10661,7 @@
     </row>
     <row r="112" spans="1:11" ht="15">
       <c r="A112" s="20">
-        <v>1098.9000000000001</v>
+        <v>1097.8</v>
       </c>
       <c r="B112" s="20"/>
       <c r="C112" s="22" t="s">
@@ -10704,7 +10693,7 @@
     </row>
     <row r="113" spans="1:11" ht="15">
       <c r="A113" s="20">
-        <v>92.4</v>
+        <v>92.3</v>
       </c>
       <c r="B113" s="20"/>
       <c r="C113" s="22" t="s">
@@ -10736,7 +10725,7 @@
     </row>
     <row r="114" spans="1:11" ht="15">
       <c r="A114" s="20">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B114" s="20"/>
       <c r="C114" s="22" t="s">
@@ -10864,7 +10853,7 @@
     </row>
     <row r="118" spans="1:11" ht="15">
       <c r="A118" s="20">
-        <v>175.86</v>
+        <v>117</v>
       </c>
       <c r="B118" s="20"/>
       <c r="C118" s="22" t="s">
@@ -10896,7 +10885,7 @@
     </row>
     <row r="119" spans="1:11" ht="15">
       <c r="A119" s="20">
-        <v>209</v>
+        <v>262.89999999999998</v>
       </c>
       <c r="B119" s="20"/>
       <c r="C119" s="22" t="s">
@@ -10960,7 +10949,7 @@
     </row>
     <row r="121" spans="1:11" ht="15">
       <c r="A121" s="20">
-        <v>131</v>
+        <v>145.19999999999999</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="22" t="s">
@@ -10992,7 +10981,7 @@
     </row>
     <row r="122" spans="1:11" ht="15">
       <c r="A122" s="20">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="22" t="s">
@@ -11024,7 +11013,7 @@
     </row>
     <row r="123" spans="1:11" ht="15">
       <c r="A123" s="20">
-        <v>126.5</v>
+        <v>115</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="22" t="s">
@@ -11055,9 +11044,7 @@
       </c>
     </row>
     <row r="124" spans="1:11" ht="15">
-      <c r="A124" s="20">
-        <v>231</v>
-      </c>
+      <c r="A124" s="20"/>
       <c r="B124" s="20"/>
       <c r="C124" s="22" t="s">
         <v>1376</v>
@@ -11088,7 +11075,7 @@
     </row>
     <row r="125" spans="1:11" ht="15">
       <c r="A125" s="20">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B125" s="20"/>
       <c r="C125" s="22" t="s">
@@ -11120,7 +11107,7 @@
     </row>
     <row r="126" spans="1:11" ht="15">
       <c r="A126" s="20">
-        <v>198</v>
+        <v>202.4</v>
       </c>
       <c r="B126" s="20"/>
       <c r="C126" s="22" t="s">
@@ -11152,7 +11139,7 @@
     </row>
     <row r="127" spans="1:11" ht="15">
       <c r="A127" s="20">
-        <v>484.55</v>
+        <v>1097.8</v>
       </c>
       <c r="B127" s="20"/>
       <c r="C127" s="22" t="s">
@@ -11184,7 +11171,7 @@
     </row>
     <row r="128" spans="1:11" ht="15">
       <c r="A128" s="20">
-        <v>242.55</v>
+        <v>229</v>
       </c>
       <c r="B128" s="20"/>
       <c r="C128" s="22" t="s">
@@ -11248,7 +11235,7 @@
     </row>
     <row r="130" spans="1:11" ht="15">
       <c r="A130" s="20">
-        <v>468.6</v>
+        <v>427.35</v>
       </c>
       <c r="B130" s="20"/>
       <c r="C130" s="22" t="s">
@@ -11280,7 +11267,7 @@
     </row>
     <row r="131" spans="1:11" ht="15">
       <c r="A131" s="20">
-        <v>235</v>
+        <v>539</v>
       </c>
       <c r="B131" s="20"/>
       <c r="C131" s="22" t="s">
@@ -11312,7 +11299,7 @@
     </row>
     <row r="132" spans="1:11" ht="15">
       <c r="A132" s="20">
-        <v>232.1</v>
+        <v>233.2</v>
       </c>
       <c r="B132" s="20"/>
       <c r="C132" s="22" t="s">
@@ -11344,7 +11331,7 @@
     </row>
     <row r="133" spans="1:11" ht="15">
       <c r="A133" s="20">
-        <v>119.9</v>
+        <v>106.92</v>
       </c>
       <c r="B133" s="20"/>
       <c r="C133" s="22" t="s">
@@ -11376,7 +11363,7 @@
     </row>
     <row r="134" spans="1:11" ht="15">
       <c r="A134" s="20">
-        <v>199</v>
+        <v>194.92</v>
       </c>
       <c r="B134" s="20"/>
       <c r="C134" s="22" t="s">
@@ -11408,7 +11395,7 @@
     </row>
     <row r="135" spans="1:11" ht="15">
       <c r="A135" s="20">
-        <v>101</v>
+        <v>118.69</v>
       </c>
       <c r="B135" s="20"/>
       <c r="C135" s="22" t="s">
@@ -11440,7 +11427,7 @@
     </row>
     <row r="136" spans="1:11" ht="15">
       <c r="A136" s="20">
-        <v>306</v>
+        <v>318.39999999999998</v>
       </c>
       <c r="B136" s="20"/>
       <c r="C136" s="22" t="s">
@@ -11472,7 +11459,7 @@
     </row>
     <row r="137" spans="1:11" ht="15">
       <c r="A137" s="20">
-        <v>215</v>
+        <v>129.83000000000001</v>
       </c>
       <c r="B137" s="20"/>
       <c r="C137" s="22" t="s">
@@ -11504,7 +11491,7 @@
     </row>
     <row r="138" spans="1:11" ht="15">
       <c r="A138" s="20">
-        <v>99</v>
+        <v>128.04</v>
       </c>
       <c r="B138" s="20"/>
       <c r="C138" s="22" t="s">
@@ -11536,7 +11523,7 @@
     </row>
     <row r="139" spans="1:11" ht="15">
       <c r="A139" s="20">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="B139" s="20"/>
       <c r="C139" s="22" t="s">
@@ -11568,7 +11555,7 @@
     </row>
     <row r="140" spans="1:11" ht="15">
       <c r="A140" s="20">
-        <v>399.97</v>
+        <v>389</v>
       </c>
       <c r="B140" s="20"/>
       <c r="C140" s="22" t="s">
@@ -11600,7 +11587,7 @@
     </row>
     <row r="141" spans="1:11" ht="15">
       <c r="A141" s="20">
-        <v>465</v>
+        <v>314.60000000000002</v>
       </c>
       <c r="B141" s="20"/>
       <c r="C141" s="22" t="s">
@@ -11632,7 +11619,7 @@
     </row>
     <row r="142" spans="1:11" ht="15">
       <c r="A142" s="20">
-        <v>152.9</v>
+        <v>198.99</v>
       </c>
       <c r="B142" s="20"/>
       <c r="C142" s="22" t="s">
@@ -11664,7 +11651,7 @@
     </row>
     <row r="143" spans="1:11" ht="15">
       <c r="A143" s="20">
-        <v>100.8</v>
+        <v>203.5</v>
       </c>
       <c r="B143" s="20"/>
       <c r="C143" s="22" t="s">
@@ -11696,7 +11683,7 @@
     </row>
     <row r="144" spans="1:11" ht="15">
       <c r="A144" s="20">
-        <v>112.09</v>
+        <v>73.25</v>
       </c>
       <c r="B144" s="20"/>
       <c r="C144" s="22" t="s">
@@ -11728,7 +11715,7 @@
     </row>
     <row r="145" spans="1:11" ht="15">
       <c r="A145" s="20">
-        <v>859</v>
+        <v>658.9</v>
       </c>
       <c r="B145" s="20"/>
       <c r="C145" s="22" t="s">
@@ -11792,7 +11779,7 @@
     </row>
     <row r="147" spans="1:11" ht="15">
       <c r="A147" s="20">
-        <v>3677</v>
+        <v>2999</v>
       </c>
       <c r="B147" s="20"/>
       <c r="C147" s="22" t="s">
@@ -11824,7 +11811,7 @@
     </row>
     <row r="148" spans="1:11" ht="15">
       <c r="A148" s="20">
-        <v>208</v>
+        <v>173.8</v>
       </c>
       <c r="B148" s="20"/>
       <c r="C148" s="22" t="s">
@@ -11856,7 +11843,7 @@
     </row>
     <row r="149" spans="1:11" ht="15">
       <c r="A149" s="20">
-        <v>409</v>
+        <v>482.9</v>
       </c>
       <c r="B149" s="20"/>
       <c r="C149" s="22" t="s">
@@ -11888,7 +11875,7 @@
     </row>
     <row r="150" spans="1:11" ht="15">
       <c r="A150" s="20">
-        <v>658</v>
+        <v>582.45000000000005</v>
       </c>
       <c r="B150" s="20"/>
       <c r="C150" s="22" t="s">
@@ -11920,7 +11907,7 @@
     </row>
     <row r="151" spans="1:11" ht="15">
       <c r="A151" s="20">
-        <v>479</v>
+        <v>878.9</v>
       </c>
       <c r="B151" s="20"/>
       <c r="C151" s="22" t="s">
@@ -11952,7 +11939,7 @@
     </row>
     <row r="152" spans="1:11" ht="15">
       <c r="A152" s="20">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B152" s="20"/>
       <c r="C152" s="22" t="s">
@@ -11984,7 +11971,7 @@
     </row>
     <row r="153" spans="1:11" ht="15">
       <c r="A153" s="20">
-        <v>179</v>
+        <v>134.75</v>
       </c>
       <c r="B153" s="20"/>
       <c r="C153" s="22" t="s">
@@ -12016,7 +12003,7 @@
     </row>
     <row r="154" spans="1:11" ht="15">
       <c r="A154" s="20">
-        <v>380</v>
+        <v>456.5</v>
       </c>
       <c r="B154" s="20"/>
       <c r="C154" s="22" t="s">
@@ -12080,7 +12067,7 @@
     </row>
     <row r="156" spans="1:11" ht="15">
       <c r="A156" s="20">
-        <v>347.6</v>
+        <v>444</v>
       </c>
       <c r="B156" s="20"/>
       <c r="C156" s="22" t="s">
@@ -12112,7 +12099,7 @@
     </row>
     <row r="157" spans="1:11" ht="15">
       <c r="A157" s="20">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B157" s="20"/>
       <c r="C157" s="22" t="s">
@@ -12144,7 +12131,7 @@
     </row>
     <row r="158" spans="1:11" ht="15">
       <c r="A158" s="20">
-        <v>271.7</v>
+        <v>438.9</v>
       </c>
       <c r="B158" s="20"/>
       <c r="C158" s="22" t="s">
@@ -12208,7 +12195,7 @@
     </row>
     <row r="160" spans="1:11" ht="15">
       <c r="A160" s="20">
-        <v>419</v>
+        <v>613.79999999999995</v>
       </c>
       <c r="B160" s="20"/>
       <c r="C160" s="22" t="s">
@@ -12240,7 +12227,7 @@
     </row>
     <row r="161" spans="1:11" ht="15">
       <c r="A161" s="20">
-        <v>197</v>
+        <v>210.98</v>
       </c>
       <c r="B161" s="20"/>
       <c r="C161" s="22" t="s">
@@ -12272,7 +12259,7 @@
     </row>
     <row r="162" spans="1:11" ht="15">
       <c r="A162" s="20">
-        <v>760</v>
+        <v>830</v>
       </c>
       <c r="B162" s="20"/>
       <c r="C162" s="22" t="s">
@@ -12368,7 +12355,7 @@
     </row>
     <row r="165" spans="1:11" ht="15">
       <c r="A165" s="20">
-        <v>133.1</v>
+        <v>100.98</v>
       </c>
       <c r="B165" s="20"/>
       <c r="C165" s="22" t="s">
@@ -12400,7 +12387,7 @@
     </row>
     <row r="166" spans="1:11" ht="15">
       <c r="A166" s="20">
-        <v>403.81</v>
+        <v>405.9</v>
       </c>
       <c r="B166" s="20"/>
       <c r="C166" s="22" t="s">
@@ -12432,7 +12419,7 @@
     </row>
     <row r="167" spans="1:11" ht="15">
       <c r="A167" s="20">
-        <v>178.76</v>
+        <v>399</v>
       </c>
       <c r="B167" s="20"/>
       <c r="C167" s="22" t="s">
@@ -12464,7 +12451,7 @@
     </row>
     <row r="168" spans="1:11" ht="15">
       <c r="A168" s="20">
-        <v>75</v>
+        <v>63.2</v>
       </c>
       <c r="B168" s="20"/>
       <c r="C168" s="22" t="s">
@@ -12496,7 +12483,7 @@
     </row>
     <row r="169" spans="1:11" ht="15">
       <c r="A169" s="20">
-        <v>647.9</v>
+        <v>599</v>
       </c>
       <c r="B169" s="20"/>
       <c r="C169" s="22" t="s">
@@ -12528,7 +12515,7 @@
     </row>
     <row r="170" spans="1:11" ht="15">
       <c r="A170" s="20">
-        <v>647.9</v>
+        <v>493.9</v>
       </c>
       <c r="B170" s="20"/>
       <c r="C170" s="22" t="s">
@@ -12559,7 +12546,7 @@
     </row>
     <row r="171" spans="1:11" ht="15">
       <c r="A171" s="20">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="B171" s="20"/>
       <c r="C171" s="22" t="s">
@@ -12591,7 +12578,7 @@
     </row>
     <row r="172" spans="1:11" ht="15">
       <c r="A172" s="20">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="B172" s="20"/>
       <c r="C172" s="22" t="s">
@@ -12623,7 +12610,7 @@
     </row>
     <row r="173" spans="1:11" ht="15">
       <c r="A173" s="20">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="B173" s="20"/>
       <c r="C173" s="22" t="s">
@@ -12717,7 +12704,7 @@
     </row>
     <row r="176" spans="1:11" ht="15">
       <c r="A176" s="20">
-        <v>170.5</v>
+        <v>97.9</v>
       </c>
       <c r="B176" s="20"/>
       <c r="C176" s="22" t="s">
@@ -12749,7 +12736,7 @@
     </row>
     <row r="177" spans="1:11" ht="15">
       <c r="A177" s="20">
-        <v>111.98</v>
+        <v>110</v>
       </c>
       <c r="B177" s="20"/>
       <c r="C177" s="22" t="s">
@@ -12781,7 +12768,7 @@
     </row>
     <row r="178" spans="1:11" ht="15">
       <c r="A178" s="20">
-        <v>56.8</v>
+        <v>109</v>
       </c>
       <c r="B178" s="20"/>
       <c r="C178" s="22" t="s">
@@ -12813,7 +12800,7 @@
     </row>
     <row r="179" spans="1:11" ht="15">
       <c r="A179" s="20">
-        <v>69.430000000000007</v>
+        <v>119</v>
       </c>
       <c r="B179" s="20"/>
       <c r="C179" s="22" t="s">
@@ -12909,7 +12896,7 @@
     </row>
     <row r="182" spans="1:11" ht="15">
       <c r="A182" s="20">
-        <v>503.8</v>
+        <v>393.8</v>
       </c>
       <c r="B182" s="20"/>
       <c r="C182" s="22" t="s">
@@ -12941,7 +12928,7 @@
     </row>
     <row r="183" spans="1:11" ht="15">
       <c r="A183" s="20">
-        <v>480.7</v>
+        <v>472.45</v>
       </c>
       <c r="B183" s="20"/>
       <c r="C183" s="22" t="s">
@@ -13005,7 +12992,7 @@
     </row>
     <row r="185" spans="1:11" ht="15">
       <c r="A185" s="20">
-        <v>209</v>
+        <v>202.4</v>
       </c>
       <c r="B185" s="20"/>
       <c r="C185" s="22" t="s">
@@ -13037,7 +13024,7 @@
     </row>
     <row r="186" spans="1:11" ht="15">
       <c r="A186" s="20">
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="B186" s="20"/>
       <c r="C186" s="22" t="s">
@@ -13069,7 +13056,7 @@
     </row>
     <row r="187" spans="1:11" ht="15">
       <c r="A187" s="20">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="B187" s="20"/>
       <c r="C187" s="22" t="s">
@@ -13101,7 +13088,7 @@
     </row>
     <row r="188" spans="1:11" ht="15">
       <c r="A188" s="20">
-        <v>1199</v>
+        <v>1039</v>
       </c>
       <c r="B188" s="20"/>
       <c r="C188" s="22" t="s">
@@ -13165,7 +13152,7 @@
     </row>
     <row r="190" spans="1:11" ht="15">
       <c r="A190" s="20">
-        <v>236.5</v>
+        <v>207.9</v>
       </c>
       <c r="B190" s="20"/>
       <c r="C190" s="22" t="s">
@@ -13197,7 +13184,7 @@
     </row>
     <row r="191" spans="1:11" ht="15">
       <c r="A191" s="20">
-        <v>499</v>
+        <v>599</v>
       </c>
       <c r="B191" s="20"/>
       <c r="C191" s="22" t="s">
@@ -13261,7 +13248,7 @@
     </row>
     <row r="193" spans="1:11" ht="15">
       <c r="A193" s="20">
-        <v>74</v>
+        <v>79.13</v>
       </c>
       <c r="B193" s="20"/>
       <c r="C193" s="22" t="s">
@@ -13293,7 +13280,7 @@
     </row>
     <row r="194" spans="1:11" ht="15">
       <c r="A194" s="20">
-        <v>302.5</v>
+        <v>239.58</v>
       </c>
       <c r="B194" s="20"/>
       <c r="C194" s="22" t="s">
@@ -13325,7 +13312,7 @@
     </row>
     <row r="195" spans="1:11" ht="15">
       <c r="A195" s="20">
-        <v>112.2</v>
+        <v>113.08</v>
       </c>
       <c r="B195" s="20"/>
       <c r="C195" s="22" t="s">
@@ -13357,7 +13344,7 @@
     </row>
     <row r="196" spans="1:11" ht="15">
       <c r="A196" s="20">
-        <v>93.28</v>
+        <v>100.1</v>
       </c>
       <c r="B196" s="20"/>
       <c r="C196" s="22" t="s">
@@ -13389,7 +13376,7 @@
     </row>
     <row r="197" spans="1:11" ht="15">
       <c r="A197" s="20">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="B197" s="20"/>
       <c r="C197" s="22" t="s">
@@ -13421,7 +13408,7 @@
     </row>
     <row r="198" spans="1:11" ht="15">
       <c r="A198" s="20">
-        <v>121.66</v>
+        <v>117.7</v>
       </c>
       <c r="B198" s="20"/>
       <c r="C198" s="22" t="s">
@@ -13453,7 +13440,7 @@
     </row>
     <row r="199" spans="1:11" ht="15">
       <c r="A199" s="20">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="B199" s="20"/>
       <c r="C199" s="22" t="s">
@@ -13549,7 +13536,7 @@
     </row>
     <row r="202" spans="1:11" ht="15">
       <c r="A202" s="20">
-        <v>61.88</v>
+        <v>62.15</v>
       </c>
       <c r="B202" s="20"/>
       <c r="C202" s="22" t="s">
@@ -13581,7 +13568,7 @@
     </row>
     <row r="203" spans="1:11" ht="15">
       <c r="A203" s="20">
-        <v>77</v>
+        <v>84.15</v>
       </c>
       <c r="B203" s="20"/>
       <c r="C203" s="22" t="s">
@@ -13645,7 +13632,7 @@
     </row>
     <row r="205" spans="1:11" ht="15">
       <c r="A205" s="20">
-        <v>176</v>
+        <v>174.35</v>
       </c>
       <c r="B205" s="20"/>
       <c r="C205" s="22" t="s">
@@ -13677,7 +13664,7 @@
     </row>
     <row r="206" spans="1:11" ht="15">
       <c r="A206" s="20">
-        <v>236.5</v>
+        <v>213.4</v>
       </c>
       <c r="B206" s="20"/>
       <c r="C206" s="22" t="s">
@@ -13709,7 +13696,7 @@
     </row>
     <row r="207" spans="1:11" ht="15">
       <c r="A207" s="20">
-        <v>219</v>
+        <v>172.54</v>
       </c>
       <c r="B207" s="20"/>
       <c r="C207" s="22" t="s">
@@ -13773,7 +13760,7 @@
     </row>
     <row r="209" spans="1:11" ht="15">
       <c r="A209" s="20">
-        <v>680.9</v>
+        <v>523.6</v>
       </c>
       <c r="B209" s="20"/>
       <c r="C209" s="22" t="s">
@@ -13837,7 +13824,7 @@
     </row>
     <row r="211" spans="1:11" ht="15">
       <c r="A211" s="20">
-        <v>176.44</v>
+        <v>181.5</v>
       </c>
       <c r="B211" s="20"/>
       <c r="C211" s="22" t="s">
@@ -13901,7 +13888,7 @@
     </row>
     <row r="213" spans="1:11" ht="15">
       <c r="A213" s="20">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="B213" s="20"/>
       <c r="C213" s="22" t="s">
@@ -13933,7 +13920,7 @@
     </row>
     <row r="214" spans="1:11" ht="15">
       <c r="A214" s="20">
-        <v>186.52</v>
+        <v>299</v>
       </c>
       <c r="B214" s="20"/>
       <c r="C214" s="22" t="s">
@@ -13965,7 +13952,7 @@
     </row>
     <row r="215" spans="1:11" ht="15">
       <c r="A215" s="20">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B215" s="20"/>
       <c r="C215" s="22" t="s">
@@ -13997,7 +13984,7 @@
     </row>
     <row r="216" spans="1:11" ht="15">
       <c r="A216" s="20">
-        <v>228.8</v>
+        <v>315.39999999999998</v>
       </c>
       <c r="B216" s="20"/>
       <c r="C216" s="22" t="s">
@@ -14029,7 +14016,7 @@
     </row>
     <row r="217" spans="1:11" ht="15">
       <c r="A217" s="20">
-        <v>361.9</v>
+        <v>380.6</v>
       </c>
       <c r="B217" s="20"/>
       <c r="C217" s="22" t="s">
@@ -14061,7 +14048,7 @@
     </row>
     <row r="218" spans="1:11" ht="15">
       <c r="A218" s="20">
-        <v>302.5</v>
+        <v>306.79000000000002</v>
       </c>
       <c r="B218" s="20"/>
       <c r="C218" s="22" t="s">
@@ -14362,7 +14349,7 @@
     </row>
     <row r="228" spans="1:11" ht="15">
       <c r="A228" s="20">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="B228" s="20"/>
       <c r="C228" s="22" t="s">
@@ -14394,7 +14381,7 @@
     </row>
     <row r="229" spans="1:11" ht="15">
       <c r="A229" s="20">
-        <v>825</v>
+        <v>723.12</v>
       </c>
       <c r="B229" s="20"/>
       <c r="C229" s="22" t="s">
@@ -14458,7 +14445,7 @@
     </row>
     <row r="231" spans="1:11" ht="15">
       <c r="A231" s="20">
-        <v>93.22</v>
+        <v>90.75</v>
       </c>
       <c r="B231" s="20"/>
       <c r="C231" s="22" t="s">
@@ -14490,7 +14477,7 @@
     </row>
     <row r="232" spans="1:11" ht="15">
       <c r="A232" s="20">
-        <v>219.92</v>
+        <v>222.2</v>
       </c>
       <c r="B232" s="20"/>
       <c r="C232" s="22" t="s">
@@ -14522,7 +14509,7 @@
     </row>
     <row r="233" spans="1:11" ht="15">
       <c r="A233" s="20">
-        <v>405.9</v>
+        <v>269.5</v>
       </c>
       <c r="B233" s="20"/>
       <c r="C233" s="22" t="s">
@@ -14554,7 +14541,7 @@
     </row>
     <row r="234" spans="1:11" ht="15">
       <c r="A234" s="20">
-        <v>499</v>
+        <v>283.8</v>
       </c>
       <c r="B234" s="20"/>
       <c r="C234" s="22" t="s">
@@ -14618,7 +14605,7 @@
     </row>
     <row r="236" spans="1:11" ht="15">
       <c r="A236" s="20">
-        <v>218.9</v>
+        <v>168.3</v>
       </c>
       <c r="B236" s="20"/>
       <c r="C236" s="22" t="s">
@@ -14682,7 +14669,7 @@
     </row>
     <row r="238" spans="1:11" ht="15">
       <c r="A238" s="20">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="B238" s="20"/>
       <c r="C238" s="22" t="s">
@@ -14776,7 +14763,7 @@
     </row>
     <row r="241" spans="1:11" ht="15">
       <c r="A241" s="20">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="B241" s="20"/>
       <c r="C241" s="22" t="s">
@@ -14871,7 +14858,7 @@
     </row>
     <row r="244" spans="1:11" ht="15">
       <c r="A244" s="20">
-        <v>328.9</v>
+        <v>308</v>
       </c>
       <c r="B244" s="20"/>
       <c r="C244" s="22" t="s">
@@ -14935,7 +14922,7 @@
     </row>
     <row r="246" spans="1:11" ht="15">
       <c r="A246" s="20">
-        <v>575.29999999999995</v>
+        <v>775.5</v>
       </c>
       <c r="B246" s="20"/>
       <c r="C246" s="22" t="s">
@@ -14967,7 +14954,7 @@
     </row>
     <row r="247" spans="1:11" ht="15">
       <c r="A247" s="20">
-        <v>118.8</v>
+        <v>189</v>
       </c>
       <c r="B247" s="20"/>
       <c r="C247" s="22" t="s">
@@ -15031,7 +15018,7 @@
     </row>
     <row r="249" spans="1:11" ht="15">
       <c r="A249" s="20">
-        <v>548.9</v>
+        <v>394.9</v>
       </c>
       <c r="B249" s="20"/>
       <c r="C249" s="22" t="s">
@@ -15093,7 +15080,7 @@
     </row>
     <row r="251" spans="1:11" ht="15">
       <c r="A251" s="20">
-        <v>159.13999999999999</v>
+        <v>206.8</v>
       </c>
       <c r="B251" s="20"/>
       <c r="C251" s="22" t="s">
@@ -15125,7 +15112,7 @@
     </row>
     <row r="252" spans="1:11" ht="15">
       <c r="A252" s="20">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B252" s="20"/>
       <c r="C252" s="22" t="s">
@@ -15157,7 +15144,7 @@
     </row>
     <row r="253" spans="1:11" ht="15">
       <c r="A253" s="20">
-        <v>373</v>
+        <v>369.6</v>
       </c>
       <c r="B253" s="20"/>
       <c r="C253" s="22" t="s">
@@ -15189,7 +15176,7 @@
     </row>
     <row r="254" spans="1:11" ht="15">
       <c r="A254" s="20">
-        <v>160.6</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="B254" s="20"/>
       <c r="C254" s="22" t="s">
@@ -15221,7 +15208,7 @@
     </row>
     <row r="255" spans="1:11" ht="15">
       <c r="A255" s="20">
-        <v>239.8</v>
+        <v>318</v>
       </c>
       <c r="B255" s="20"/>
       <c r="C255" s="22" t="s">
@@ -15253,7 +15240,7 @@
     </row>
     <row r="256" spans="1:11" ht="15">
       <c r="A256" s="20">
-        <v>119.8</v>
+        <v>88.9</v>
       </c>
       <c r="B256" s="20"/>
       <c r="C256" s="22" t="s">
@@ -15285,7 +15272,7 @@
     </row>
     <row r="257" spans="1:11" ht="15">
       <c r="A257" s="20">
-        <v>179.9</v>
+        <v>141.99</v>
       </c>
       <c r="B257" s="20"/>
       <c r="C257" s="22" t="s">
@@ -15317,7 +15304,7 @@
     </row>
     <row r="258" spans="1:11" ht="15">
       <c r="A258" s="20">
-        <v>193.27</v>
+        <v>294.8</v>
       </c>
       <c r="B258" s="20"/>
       <c r="C258" s="22" t="s">
@@ -15349,7 +15336,7 @@
     </row>
     <row r="259" spans="1:11" ht="15">
       <c r="A259" s="20">
-        <v>252</v>
+        <v>465</v>
       </c>
       <c r="B259" s="20"/>
       <c r="C259" s="22" t="s">
@@ -15413,7 +15400,7 @@
     </row>
     <row r="261" spans="1:11" ht="15">
       <c r="A261" s="20">
-        <v>363</v>
+        <v>548.9</v>
       </c>
       <c r="B261" s="20"/>
       <c r="C261" s="22" t="s">
@@ -15445,7 +15432,7 @@
     </row>
     <row r="262" spans="1:11" ht="15">
       <c r="A262" s="20">
-        <v>538</v>
+        <v>460</v>
       </c>
       <c r="B262" s="20"/>
       <c r="C262" s="22" t="s">
@@ -15477,7 +15464,7 @@
     </row>
     <row r="263" spans="1:11" ht="15">
       <c r="A263" s="20">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B263" s="20"/>
       <c r="C263" s="22" t="s">
@@ -15509,7 +15496,7 @@
     </row>
     <row r="264" spans="1:11" ht="15">
       <c r="A264" s="20">
-        <v>850</v>
+        <v>585.20000000000005</v>
       </c>
       <c r="B264" s="20"/>
       <c r="C264" s="22" t="s">
@@ -15541,7 +15528,7 @@
     </row>
     <row r="265" spans="1:11" ht="15">
       <c r="A265" s="20">
-        <v>1700</v>
+        <v>1925</v>
       </c>
       <c r="B265" s="20"/>
       <c r="C265" s="22" t="s">
@@ -15573,7 +15560,7 @@
     </row>
     <row r="266" spans="1:11" ht="15">
       <c r="A266" s="20">
-        <v>269.60000000000002</v>
+        <v>328.9</v>
       </c>
       <c r="B266" s="20"/>
       <c r="C266" s="22" t="s">
@@ -15605,7 +15592,7 @@
     </row>
     <row r="267" spans="1:11" ht="15">
       <c r="A267" s="20">
-        <v>758</v>
+        <v>624.79999999999995</v>
       </c>
       <c r="B267" s="20"/>
       <c r="C267" s="22" t="s">
@@ -15637,7 +15624,7 @@
     </row>
     <row r="268" spans="1:11" ht="15">
       <c r="A268" s="20">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B268" s="20"/>
       <c r="C268" s="22" t="s">
@@ -15668,9 +15655,7 @@
       </c>
     </row>
     <row r="269" spans="1:11" ht="15">
-      <c r="A269" s="20">
-        <v>1059</v>
-      </c>
+      <c r="A269" s="20"/>
       <c r="B269" s="20"/>
       <c r="C269" s="22" t="s">
         <v>1376</v>
@@ -15701,7 +15686,7 @@
     </row>
     <row r="270" spans="1:11" ht="15">
       <c r="A270" s="20">
-        <v>659</v>
+        <v>878.9</v>
       </c>
       <c r="B270" s="20"/>
       <c r="C270" s="22" t="s">
@@ -15733,7 +15718,7 @@
     </row>
     <row r="271" spans="1:11" ht="15">
       <c r="A271" s="20">
-        <v>57.4</v>
+        <v>56.79</v>
       </c>
       <c r="B271" s="20"/>
       <c r="C271" s="22" t="s">
@@ -15765,7 +15750,7 @@
     </row>
     <row r="272" spans="1:11" ht="17">
       <c r="A272" s="20">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="B272" s="20"/>
       <c r="C272" s="22" t="s">
@@ -15797,7 +15782,7 @@
     </row>
     <row r="273" spans="1:11" ht="17">
       <c r="A273" s="20">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="B273" s="20"/>
       <c r="C273" s="22" t="s">
@@ -15829,7 +15814,7 @@
     </row>
     <row r="274" spans="1:11" ht="15">
       <c r="A274" s="20">
-        <v>299.14</v>
+        <v>236.5</v>
       </c>
       <c r="B274" s="20"/>
       <c r="C274" s="22" t="s">
@@ -15861,7 +15846,7 @@
     </row>
     <row r="275" spans="1:11" ht="15">
       <c r="A275" s="20">
-        <v>103.48</v>
+        <v>59</v>
       </c>
       <c r="B275" s="20"/>
       <c r="C275" s="22" t="s">
@@ -15925,7 +15910,7 @@
     </row>
     <row r="277" spans="1:11" ht="15">
       <c r="A277" s="20">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="B277" s="20"/>
       <c r="C277" s="22" t="s">
@@ -15957,7 +15942,7 @@
     </row>
     <row r="278" spans="1:11" ht="15">
       <c r="A278" s="20">
-        <v>279.18</v>
+        <v>290.60000000000002</v>
       </c>
       <c r="B278" s="20"/>
       <c r="C278" s="22" t="s">
@@ -15989,7 +15974,7 @@
     </row>
     <row r="279" spans="1:11" ht="15">
       <c r="A279" s="20">
-        <v>289.3</v>
+        <v>286.22000000000003</v>
       </c>
       <c r="B279" s="20"/>
       <c r="C279" s="22" t="s">
@@ -16021,7 +16006,7 @@
     </row>
     <row r="280" spans="1:11" ht="15">
       <c r="A280" s="20">
-        <v>500</v>
+        <v>659</v>
       </c>
       <c r="B280" s="20"/>
       <c r="C280" s="22" t="s">
@@ -16053,7 +16038,7 @@
     </row>
     <row r="281" spans="1:11" ht="15">
       <c r="A281" s="20">
-        <v>359</v>
+        <v>300.85000000000002</v>
       </c>
       <c r="B281" s="20"/>
       <c r="C281" s="22" t="s">
@@ -16085,7 +16070,7 @@
     </row>
     <row r="282" spans="1:11" ht="15">
       <c r="A282" s="20">
-        <v>206.8</v>
+        <v>338</v>
       </c>
       <c r="B282" s="20"/>
       <c r="C282" s="22" t="s">
@@ -16117,7 +16102,7 @@
     </row>
     <row r="283" spans="1:11" ht="15">
       <c r="A283" s="20">
-        <v>221.1</v>
+        <v>225.5</v>
       </c>
       <c r="B283" s="20"/>
       <c r="C283" s="22" t="s">
@@ -16149,7 +16134,7 @@
     </row>
     <row r="284" spans="1:11" ht="15">
       <c r="A284" s="20">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="B284" s="20"/>
       <c r="C284" s="22" t="s">
@@ -16181,7 +16166,7 @@
     </row>
     <row r="285" spans="1:11" ht="15">
       <c r="A285" s="20">
-        <v>880</v>
+        <v>1317.8</v>
       </c>
       <c r="B285" s="20"/>
       <c r="C285" s="22" t="s">
@@ -16213,7 +16198,7 @@
     </row>
     <row r="286" spans="1:11" ht="15">
       <c r="A286" s="20">
-        <v>477</v>
+        <v>372.9</v>
       </c>
       <c r="B286" s="20"/>
       <c r="C286" s="22" t="s">
@@ -16245,7 +16230,7 @@
     </row>
     <row r="287" spans="1:11" ht="15">
       <c r="A287" s="20">
-        <v>123</v>
+        <v>166.99</v>
       </c>
       <c r="B287" s="20"/>
       <c r="C287" s="22" t="s">
@@ -16277,7 +16262,7 @@
     </row>
     <row r="288" spans="1:11" ht="15">
       <c r="A288" s="20">
-        <v>173.8</v>
+        <v>192</v>
       </c>
       <c r="B288" s="20"/>
       <c r="C288" s="22" t="s">
@@ -16309,7 +16294,7 @@
     </row>
     <row r="289" spans="1:11" ht="15">
       <c r="A289" s="20">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B289" s="20"/>
       <c r="C289" s="22" t="s">
@@ -16372,7 +16357,7 @@
     </row>
     <row r="291" spans="1:11" ht="15">
       <c r="A291" s="20">
-        <v>388</v>
+        <v>279.8</v>
       </c>
       <c r="B291" s="20"/>
       <c r="C291" s="22" t="s">
@@ -16404,7 +16389,7 @@
     </row>
     <row r="292" spans="1:11" ht="15">
       <c r="A292" s="20">
-        <v>159.5</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="B292" s="20"/>
       <c r="C292" s="22" t="s">
@@ -16436,7 +16421,7 @@
     </row>
     <row r="293" spans="1:11" ht="15">
       <c r="A293" s="20">
-        <v>635.79999999999995</v>
+        <v>625.9</v>
       </c>
       <c r="B293" s="20"/>
       <c r="C293" s="22" t="s">
@@ -16468,7 +16453,7 @@
     </row>
     <row r="294" spans="1:11" ht="15">
       <c r="A294" s="20">
-        <v>431.2</v>
+        <v>388.3</v>
       </c>
       <c r="B294" s="20"/>
       <c r="C294" s="22" t="s">
@@ -16500,7 +16485,7 @@
     </row>
     <row r="295" spans="1:11" ht="15">
       <c r="A295" s="20">
-        <v>426</v>
+        <v>462.74</v>
       </c>
       <c r="B295" s="20"/>
       <c r="C295" s="22" t="s">
@@ -16532,7 +16517,7 @@
     </row>
     <row r="296" spans="1:11" ht="15">
       <c r="A296" s="20">
-        <v>455.4</v>
+        <v>548.9</v>
       </c>
       <c r="B296" s="20"/>
       <c r="C296" s="22" t="s">
@@ -16564,7 +16549,7 @@
     </row>
     <row r="297" spans="1:11" ht="15">
       <c r="A297" s="20">
-        <v>402.6</v>
+        <v>548.9</v>
       </c>
       <c r="B297" s="20"/>
       <c r="C297" s="22" t="s">
@@ -16596,7 +16581,7 @@
     </row>
     <row r="298" spans="1:11" ht="15">
       <c r="A298" s="20">
-        <v>679</v>
+        <v>438</v>
       </c>
       <c r="B298" s="20"/>
       <c r="C298" s="22" t="s">
@@ -16660,7 +16645,7 @@
     </row>
     <row r="300" spans="1:11" ht="15">
       <c r="A300" s="20">
-        <v>844.8</v>
+        <v>959</v>
       </c>
       <c r="B300" s="20"/>
       <c r="C300" s="22" t="s">
@@ -16692,7 +16677,7 @@
     </row>
     <row r="301" spans="1:11" ht="15">
       <c r="A301" s="20">
-        <v>532.4</v>
+        <v>713.9</v>
       </c>
       <c r="B301" s="20"/>
       <c r="C301" s="22" t="s">
@@ -16724,7 +16709,7 @@
     </row>
     <row r="302" spans="1:11" ht="15">
       <c r="A302" s="20">
-        <v>998</v>
+        <v>1098.9000000000001</v>
       </c>
       <c r="B302" s="20"/>
       <c r="C302" s="22" t="s">
@@ -16756,7 +16741,7 @@
     </row>
     <row r="303" spans="1:11" ht="15">
       <c r="A303" s="20">
-        <v>538</v>
+        <v>599</v>
       </c>
       <c r="B303" s="20"/>
       <c r="C303" s="22" t="s">
@@ -16788,7 +16773,7 @@
     </row>
     <row r="304" spans="1:11" ht="15">
       <c r="A304" s="20">
-        <v>240.79</v>
+        <v>339</v>
       </c>
       <c r="B304" s="20"/>
       <c r="C304" s="22" t="s">
@@ -16820,7 +16805,7 @@
     </row>
     <row r="305" spans="1:11" ht="15">
       <c r="A305" s="20">
-        <v>532.4</v>
+        <v>497.2</v>
       </c>
       <c r="B305" s="20"/>
       <c r="C305" s="22" t="s">
@@ -16852,7 +16837,7 @@
     </row>
     <row r="306" spans="1:11" ht="15">
       <c r="A306" s="20">
-        <v>532.4</v>
+        <v>492.8</v>
       </c>
       <c r="B306" s="20"/>
       <c r="C306" s="22" t="s">
@@ -16884,7 +16869,7 @@
     </row>
     <row r="307" spans="1:11" ht="15">
       <c r="A307" s="20">
-        <v>741.4</v>
+        <v>1098.9000000000001</v>
       </c>
       <c r="B307" s="20"/>
       <c r="C307" s="22" t="s">
@@ -16916,7 +16901,7 @@
     </row>
     <row r="308" spans="1:11" ht="15">
       <c r="A308" s="20">
-        <v>59.9</v>
+        <v>99</v>
       </c>
       <c r="B308" s="20"/>
       <c r="C308" s="22" t="s">
@@ -16948,7 +16933,7 @@
     </row>
     <row r="309" spans="1:11" ht="15">
       <c r="A309" s="20">
-        <v>221.99</v>
+        <v>235</v>
       </c>
       <c r="B309" s="20"/>
       <c r="C309" s="22" t="s">
@@ -16980,7 +16965,7 @@
     </row>
     <row r="310" spans="1:11" ht="15">
       <c r="A310" s="20">
-        <v>222</v>
+        <v>148</v>
       </c>
       <c r="B310" s="20"/>
       <c r="C310" s="22" t="s">
@@ -17012,7 +16997,7 @@
     </row>
     <row r="311" spans="1:11" ht="15">
       <c r="A311" s="20">
-        <v>590.70000000000005</v>
+        <v>435</v>
       </c>
       <c r="B311" s="20"/>
       <c r="C311" s="22" t="s">
@@ -17044,7 +17029,7 @@
     </row>
     <row r="312" spans="1:11" ht="17">
       <c r="A312" s="20">
-        <v>916.15</v>
+        <v>1098.9000000000001</v>
       </c>
       <c r="B312" s="20"/>
       <c r="C312" s="22" t="s">
@@ -17076,7 +17061,7 @@
     </row>
     <row r="313" spans="1:11" ht="15">
       <c r="A313" s="20">
-        <v>1398</v>
+        <v>1559</v>
       </c>
       <c r="B313" s="20"/>
       <c r="C313" s="22" t="s">
@@ -17108,7 +17093,7 @@
     </row>
     <row r="314" spans="1:11" ht="15">
       <c r="A314" s="20">
-        <v>255.2</v>
+        <v>328.9</v>
       </c>
       <c r="B314" s="20"/>
       <c r="C314" s="22" t="s">
@@ -17172,7 +17157,7 @@
     </row>
     <row r="316" spans="1:11" ht="15">
       <c r="A316" s="20">
-        <v>160.6</v>
+        <v>261.8</v>
       </c>
       <c r="B316" s="20"/>
       <c r="C316" s="22" t="s">
@@ -17204,7 +17189,7 @@
     </row>
     <row r="317" spans="1:11" ht="15">
       <c r="A317" s="20">
-        <v>215.05</v>
+        <v>217.8</v>
       </c>
       <c r="B317" s="20"/>
       <c r="C317" s="22" t="s">
@@ -17236,7 +17221,7 @@
     </row>
     <row r="318" spans="1:11" ht="15">
       <c r="A318" s="20">
-        <v>324</v>
+        <v>290.39999999999998</v>
       </c>
       <c r="B318" s="20"/>
       <c r="C318" s="22" t="s">
@@ -17268,7 +17253,7 @@
     </row>
     <row r="319" spans="1:11" ht="15">
       <c r="A319" s="20">
-        <v>1837</v>
+        <v>1639</v>
       </c>
       <c r="B319" s="20"/>
       <c r="C319" s="22" t="s">
@@ -17332,7 +17317,7 @@
     </row>
     <row r="321" spans="1:11" ht="15">
       <c r="A321" s="20">
-        <v>100.65</v>
+        <v>95</v>
       </c>
       <c r="B321" s="20"/>
       <c r="C321" s="22" t="s">
@@ -17364,7 +17349,7 @@
     </row>
     <row r="322" spans="1:11" ht="15">
       <c r="A322" s="20">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B322" s="20"/>
       <c r="C322" s="22" t="s">
@@ -17428,7 +17413,7 @@
     </row>
     <row r="324" spans="1:11" ht="15">
       <c r="A324" s="20">
-        <v>249</v>
+        <v>217.8</v>
       </c>
       <c r="B324" s="20"/>
       <c r="C324" s="22" t="s">
@@ -17492,7 +17477,7 @@
     </row>
     <row r="326" spans="1:11" ht="15">
       <c r="A326" s="20">
-        <v>100.65</v>
+        <v>149</v>
       </c>
       <c r="B326" s="20"/>
       <c r="C326" s="22" t="s">
@@ -17556,7 +17541,7 @@
     </row>
     <row r="328" spans="1:11" ht="15">
       <c r="A328" s="20">
-        <v>478.5</v>
+        <v>545</v>
       </c>
       <c r="B328" s="20"/>
       <c r="C328" s="22" t="s">
@@ -17620,7 +17605,7 @@
     </row>
     <row r="330" spans="1:11" ht="15">
       <c r="A330" s="20">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B330" s="20"/>
       <c r="C330" s="22" t="s">
@@ -17684,7 +17669,7 @@
     </row>
     <row r="332" spans="1:11" ht="13.5" customHeight="1">
       <c r="A332" s="20">
-        <v>268</v>
+        <v>359</v>
       </c>
       <c r="B332" s="20"/>
       <c r="C332" s="22" t="s">
@@ -17716,7 +17701,7 @@
     </row>
     <row r="333" spans="1:11" ht="15">
       <c r="A333" s="20">
-        <v>467.28</v>
+        <v>599</v>
       </c>
       <c r="B333" s="20"/>
       <c r="C333" s="22" t="s">
@@ -17748,7 +17733,7 @@
     </row>
     <row r="334" spans="1:11" ht="15">
       <c r="A334" s="20">
-        <v>174.31</v>
+        <v>181.5</v>
       </c>
       <c r="B334" s="20"/>
       <c r="C334" s="22" t="s">
@@ -17780,7 +17765,7 @@
     </row>
     <row r="335" spans="1:11" ht="17">
       <c r="A335" s="20">
-        <v>456.5</v>
+        <v>157</v>
       </c>
       <c r="B335" s="20"/>
       <c r="C335" s="22" t="s">
@@ -17812,7 +17797,7 @@
     </row>
     <row r="336" spans="1:11" ht="15">
       <c r="A336" s="20">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B336" s="20"/>
       <c r="C336" s="22" t="s">
@@ -17876,7 +17861,7 @@
     </row>
     <row r="338" spans="1:11" ht="15">
       <c r="A338" s="20">
-        <v>899</v>
+        <v>864.6</v>
       </c>
       <c r="B338" s="20"/>
       <c r="C338" s="22" t="s">
@@ -17907,9 +17892,7 @@
       </c>
     </row>
     <row r="339" spans="1:11" ht="15">
-      <c r="A339" s="20">
-        <v>189</v>
-      </c>
+      <c r="A339" s="20"/>
       <c r="B339" s="20"/>
       <c r="C339" s="22" t="s">
         <v>1376</v>
@@ -17940,7 +17923,7 @@
     </row>
     <row r="340" spans="1:11" ht="15">
       <c r="A340" s="20">
-        <v>74.400000000000006</v>
+        <v>87.8</v>
       </c>
       <c r="B340" s="20"/>
       <c r="C340" s="22" t="s">
@@ -17972,7 +17955,7 @@
     </row>
     <row r="341" spans="1:11" ht="15">
       <c r="A341" s="20">
-        <v>668</v>
+        <v>445</v>
       </c>
       <c r="B341" s="20"/>
       <c r="C341" s="22" t="s">
@@ -18004,7 +17987,7 @@
     </row>
     <row r="342" spans="1:11" ht="15">
       <c r="A342" s="20">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="B342" s="20"/>
       <c r="C342" s="22" t="s">
@@ -18036,7 +18019,7 @@
     </row>
     <row r="343" spans="1:11" ht="15">
       <c r="A343" s="20">
-        <v>203</v>
+        <v>540</v>
       </c>
       <c r="B343" s="20"/>
       <c r="C343" s="22" t="s">
@@ -18068,7 +18051,7 @@
     </row>
     <row r="344" spans="1:11" ht="15">
       <c r="A344" s="20">
-        <v>798</v>
+        <v>864.6</v>
       </c>
       <c r="B344" s="20"/>
       <c r="C344" s="22" t="s">
@@ -18100,7 +18083,7 @@
     </row>
     <row r="345" spans="1:11" ht="15">
       <c r="A345" s="20">
-        <v>69.7</v>
+        <v>57.4</v>
       </c>
       <c r="B345" s="20"/>
       <c r="C345" s="22" t="s">
@@ -18131,9 +18114,7 @@
       </c>
     </row>
     <row r="346" spans="1:11" ht="15">
-      <c r="A346" s="20">
-        <v>390</v>
-      </c>
+      <c r="A346" s="20"/>
       <c r="B346" s="20"/>
       <c r="C346" s="22" t="s">
         <v>1376</v>
@@ -18164,7 +18145,7 @@
     </row>
     <row r="347" spans="1:11" ht="15">
       <c r="A347" s="20">
-        <v>390</v>
+        <v>328</v>
       </c>
       <c r="B347" s="20"/>
       <c r="C347" s="22" t="s">
@@ -18226,7 +18207,7 @@
     </row>
     <row r="349" spans="1:11" ht="15">
       <c r="A349" s="20">
-        <v>99.98</v>
+        <v>137</v>
       </c>
       <c r="B349" s="20"/>
       <c r="C349" s="22" t="s">
@@ -18258,7 +18239,7 @@
     </row>
     <row r="350" spans="1:11" ht="15">
       <c r="A350" s="20">
-        <v>98.9</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="B350" s="20"/>
       <c r="C350" s="22" t="s">
@@ -18290,7 +18271,7 @@
     </row>
     <row r="351" spans="1:11" ht="15">
       <c r="A351" s="20">
-        <v>919</v>
+        <v>1299</v>
       </c>
       <c r="B351" s="20"/>
       <c r="C351" s="22" t="s">
@@ -18322,7 +18303,7 @@
     </row>
     <row r="352" spans="1:11" ht="15">
       <c r="A352" s="20">
-        <v>570</v>
+        <v>700.15</v>
       </c>
       <c r="B352" s="20"/>
       <c r="C352" s="22" t="s">
@@ -18354,7 +18335,7 @@
     </row>
     <row r="353" spans="1:11" ht="15">
       <c r="A353" s="20">
-        <v>511.1</v>
+        <v>655</v>
       </c>
       <c r="B353" s="20"/>
       <c r="C353" s="22" t="s">
@@ -18386,7 +18367,7 @@
     </row>
     <row r="354" spans="1:11" ht="15">
       <c r="A354" s="20">
-        <v>218.9</v>
+        <v>258</v>
       </c>
       <c r="B354" s="20"/>
       <c r="C354" s="22" t="s">
@@ -18418,7 +18399,7 @@
     </row>
     <row r="355" spans="1:11" ht="15">
       <c r="A355" s="20">
-        <v>748</v>
+        <v>819.5</v>
       </c>
       <c r="B355" s="20"/>
       <c r="C355" s="22" t="s">
@@ -18450,7 +18431,7 @@
     </row>
     <row r="356" spans="1:11" ht="15">
       <c r="A356" s="20">
-        <v>176.44</v>
+        <v>181.5</v>
       </c>
       <c r="B356" s="20"/>
       <c r="C356" s="22" t="s">
@@ -18513,7 +18494,7 @@
     </row>
     <row r="358" spans="1:11" ht="15">
       <c r="A358" s="20">
-        <v>743</v>
+        <v>599</v>
       </c>
       <c r="B358" s="20"/>
       <c r="C358" s="22" t="s">
@@ -18544,7 +18525,9 @@
       </c>
     </row>
     <row r="359" spans="1:11" ht="15">
-      <c r="A359" s="20"/>
+      <c r="A359" s="20">
+        <v>599</v>
+      </c>
       <c r="B359" s="20"/>
       <c r="C359" s="22" t="s">
         <v>1376</v>
@@ -18575,7 +18558,7 @@
     </row>
     <row r="360" spans="1:11" ht="15">
       <c r="A360" s="20">
-        <v>614.9</v>
+        <v>396</v>
       </c>
       <c r="B360" s="20"/>
       <c r="C360" s="22" t="s">
@@ -18607,7 +18590,7 @@
     </row>
     <row r="361" spans="1:11" ht="15">
       <c r="A361" s="20">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="B361" s="20"/>
       <c r="C361" s="22" t="s">
@@ -18639,7 +18622,7 @@
     </row>
     <row r="362" spans="1:11" ht="15">
       <c r="A362" s="20">
-        <v>548.9</v>
+        <v>599</v>
       </c>
       <c r="B362" s="20"/>
       <c r="C362" s="22" t="s">
@@ -18671,7 +18654,7 @@
     </row>
     <row r="363" spans="1:11" ht="15">
       <c r="A363" s="20">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B363" s="20"/>
       <c r="C363" s="22" t="s">
@@ -18703,7 +18686,7 @@
     </row>
     <row r="364" spans="1:11" ht="15">
       <c r="A364" s="20">
-        <v>370</v>
+        <v>330.44</v>
       </c>
       <c r="B364" s="20"/>
       <c r="C364" s="22" t="s">
@@ -18767,7 +18750,7 @@
     </row>
     <row r="366" spans="1:11" ht="15">
       <c r="A366" s="20">
-        <v>100.1</v>
+        <v>99</v>
       </c>
       <c r="B366" s="20"/>
       <c r="C366" s="22" t="s">
@@ -18799,7 +18782,7 @@
     </row>
     <row r="367" spans="1:11" ht="15">
       <c r="A367" s="20">
-        <v>768.9</v>
+        <v>510.4</v>
       </c>
       <c r="B367" s="20"/>
       <c r="C367" s="22" t="s">
@@ -18831,7 +18814,7 @@
     </row>
     <row r="368" spans="1:11" ht="15">
       <c r="A368" s="20">
-        <v>105.6</v>
+        <v>144.1</v>
       </c>
       <c r="B368" s="20"/>
       <c r="C368" s="22" t="s">
@@ -18862,9 +18845,7 @@
       </c>
     </row>
     <row r="369" spans="1:11" ht="15">
-      <c r="A369" s="20">
-        <v>199.8</v>
-      </c>
+      <c r="A369" s="20"/>
       <c r="B369" s="20"/>
       <c r="C369" s="22" t="s">
         <v>1376</v>
@@ -18895,7 +18876,7 @@
     </row>
     <row r="370" spans="1:11" ht="15">
       <c r="A370" s="20">
-        <v>166</v>
+        <v>147.94999999999999</v>
       </c>
       <c r="B370" s="20"/>
       <c r="C370" s="22" t="s">
@@ -18927,7 +18908,7 @@
     </row>
     <row r="371" spans="1:11" ht="15">
       <c r="A371" s="20">
-        <v>229.9</v>
+        <v>164.51</v>
       </c>
       <c r="B371" s="20"/>
       <c r="C371" s="22" t="s">
@@ -18959,7 +18940,7 @@
     </row>
     <row r="372" spans="1:11" ht="15">
       <c r="A372" s="20">
-        <v>93.22</v>
+        <v>189</v>
       </c>
       <c r="B372" s="20"/>
       <c r="C372" s="22" t="s">
@@ -18991,7 +18972,7 @@
     </row>
     <row r="373" spans="1:11" ht="15">
       <c r="A373" s="20">
-        <v>112.2</v>
+        <v>89.54</v>
       </c>
       <c r="B373" s="20"/>
       <c r="C373" s="22" t="s">
@@ -19022,9 +19003,7 @@
       </c>
     </row>
     <row r="374" spans="1:11" ht="15">
-      <c r="A374" s="20">
-        <v>192.5</v>
-      </c>
+      <c r="A374" s="20"/>
       <c r="B374" s="20"/>
       <c r="C374" s="22" t="s">
         <v>1376</v>
@@ -19055,7 +19034,7 @@
     </row>
     <row r="375" spans="1:11" ht="15">
       <c r="A375" s="20">
-        <v>123.45</v>
+        <v>158</v>
       </c>
       <c r="B375" s="20"/>
       <c r="C375" s="22" t="s">
@@ -19087,7 +19066,7 @@
     </row>
     <row r="376" spans="1:11" ht="15">
       <c r="A376" s="20">
-        <v>328.9</v>
+        <v>204.6</v>
       </c>
       <c r="B376" s="20"/>
       <c r="C376" s="22" t="s">
@@ -19119,7 +19098,7 @@
     </row>
     <row r="377" spans="1:11" ht="15">
       <c r="A377" s="20">
-        <v>225.5</v>
+        <v>220</v>
       </c>
       <c r="B377" s="20"/>
       <c r="C377" s="22" t="s">
@@ -19151,7 +19130,7 @@
     </row>
     <row r="378" spans="1:11" ht="15">
       <c r="A378" s="20">
-        <v>228.5</v>
+        <v>299</v>
       </c>
       <c r="B378" s="20"/>
       <c r="C378" s="22" t="s">
@@ -19183,7 +19162,7 @@
     </row>
     <row r="379" spans="1:11" ht="15">
       <c r="A379" s="20">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B379" s="20"/>
       <c r="C379" s="22" t="s">
@@ -19215,7 +19194,7 @@
     </row>
     <row r="380" spans="1:11" ht="15">
       <c r="A380" s="20">
-        <v>84</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="B380" s="20"/>
       <c r="C380" s="22" t="s">
@@ -19247,7 +19226,7 @@
     </row>
     <row r="381" spans="1:11" ht="15">
       <c r="A381" s="20">
-        <v>79.900000000000006</v>
+        <v>79.45</v>
       </c>
       <c r="B381" s="20"/>
       <c r="C381" s="22" t="s">
@@ -19279,7 +19258,7 @@
     </row>
     <row r="382" spans="1:11" ht="15">
       <c r="A382" s="20">
-        <v>309</v>
+        <v>283.8</v>
       </c>
       <c r="B382" s="20"/>
       <c r="C382" s="22" t="s">
@@ -19311,7 +19290,7 @@
     </row>
     <row r="383" spans="1:11" ht="15">
       <c r="A383" s="20">
-        <v>220.37</v>
+        <v>150</v>
       </c>
       <c r="B383" s="20"/>
       <c r="C383" s="22" t="s">
@@ -19343,7 +19322,7 @@
     </row>
     <row r="384" spans="1:11" ht="15">
       <c r="A384" s="20">
-        <v>57.2</v>
+        <v>69.33</v>
       </c>
       <c r="B384" s="20"/>
       <c r="C384" s="22" t="s">
@@ -19375,7 +19354,7 @@
     </row>
     <row r="385" spans="1:11" ht="15">
       <c r="A385" s="20">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="B385" s="20"/>
       <c r="C385" s="22" t="s">
@@ -19466,7 +19445,7 @@
     </row>
     <row r="388" spans="1:11" ht="15">
       <c r="A388" s="20">
-        <v>760</v>
+        <v>594</v>
       </c>
       <c r="B388" s="20"/>
       <c r="C388" s="22" t="s">
@@ -19498,7 +19477,7 @@
     </row>
     <row r="389" spans="1:11" ht="15">
       <c r="A389" s="20">
-        <v>147.4</v>
+        <v>172.59</v>
       </c>
       <c r="B389" s="20"/>
       <c r="C389" s="22" t="s">
@@ -19530,7 +19509,7 @@
     </row>
     <row r="390" spans="1:11" ht="15">
       <c r="A390" s="20">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="B390" s="20"/>
       <c r="C390" s="22" t="s">
@@ -19562,7 +19541,7 @@
     </row>
     <row r="391" spans="1:11" ht="15">
       <c r="A391" s="20">
-        <v>360</v>
+        <v>312.39999999999998</v>
       </c>
       <c r="B391" s="20"/>
       <c r="C391" s="22" t="s">
@@ -19594,7 +19573,7 @@
     </row>
     <row r="392" spans="1:11" ht="15">
       <c r="A392" s="20">
-        <v>54.9</v>
+        <v>49</v>
       </c>
       <c r="B392" s="20"/>
       <c r="C392" s="22" t="s">
@@ -19626,7 +19605,7 @@
     </row>
     <row r="393" spans="1:11" ht="15">
       <c r="A393" s="20">
-        <v>74.900000000000006</v>
+        <v>79.09</v>
       </c>
       <c r="B393" s="20"/>
       <c r="C393" s="22" t="s">
@@ -19658,7 +19637,7 @@
     </row>
     <row r="394" spans="1:11" ht="15">
       <c r="A394" s="20">
-        <v>225</v>
+        <v>328</v>
       </c>
       <c r="B394" s="20"/>
       <c r="C394" s="22" t="s">
@@ -19690,7 +19669,7 @@
     </row>
     <row r="395" spans="1:11" ht="15">
       <c r="A395" s="20">
-        <v>799</v>
+        <v>411.4</v>
       </c>
       <c r="B395" s="20"/>
       <c r="C395" s="22" t="s">
@@ -19781,7 +19760,7 @@
     </row>
     <row r="398" spans="1:11" ht="15">
       <c r="A398" s="20">
-        <v>72.28</v>
+        <v>74.8</v>
       </c>
       <c r="B398" s="20"/>
       <c r="C398" s="22" t="s">
@@ -19844,7 +19823,7 @@
     </row>
     <row r="400" spans="1:11" ht="15">
       <c r="A400" s="20">
-        <v>110.11</v>
+        <v>121</v>
       </c>
       <c r="B400" s="20"/>
       <c r="C400" s="22" t="s">
@@ -19908,7 +19887,7 @@
     </row>
     <row r="402" spans="1:11" ht="15">
       <c r="A402" s="20">
-        <v>72.28</v>
+        <v>129</v>
       </c>
       <c r="B402" s="20"/>
       <c r="C402" s="22" t="s">
@@ -19940,7 +19919,7 @@
     </row>
     <row r="403" spans="1:11" ht="15">
       <c r="A403" s="20">
-        <v>353.1</v>
+        <v>517</v>
       </c>
       <c r="B403" s="20"/>
       <c r="C403" s="22" t="s">
@@ -19971,7 +19950,9 @@
       </c>
     </row>
     <row r="404" spans="1:11" ht="15">
-      <c r="A404" s="20"/>
+      <c r="A404" s="20">
+        <v>104.61</v>
+      </c>
       <c r="B404" s="20"/>
       <c r="C404" s="22" t="s">
         <v>1376</v>
@@ -20002,7 +19983,7 @@
     </row>
     <row r="405" spans="1:11" ht="15">
       <c r="A405" s="20">
-        <v>317.99</v>
+        <v>366</v>
       </c>
       <c r="B405" s="20"/>
       <c r="C405" s="22" t="s">
@@ -20034,7 +20015,7 @@
     </row>
     <row r="406" spans="1:11" ht="15">
       <c r="A406" s="20">
-        <v>429</v>
+        <v>540</v>
       </c>
       <c r="B406" s="20"/>
       <c r="C406" s="22" t="s">
@@ -20066,7 +20047,7 @@
     </row>
     <row r="407" spans="1:11" ht="15">
       <c r="A407" s="20">
-        <v>329.45</v>
+        <v>323.39999999999998</v>
       </c>
       <c r="B407" s="20"/>
       <c r="C407" s="22" t="s">
@@ -20098,7 +20079,7 @@
     </row>
     <row r="408" spans="1:11" ht="15">
       <c r="A408" s="20">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B408" s="20"/>
       <c r="C408" s="22" t="s">
@@ -20130,7 +20111,7 @@
     </row>
     <row r="409" spans="1:11" ht="15">
       <c r="A409" s="20">
-        <v>648.87</v>
+        <v>680</v>
       </c>
       <c r="B409" s="20"/>
       <c r="C409" s="22" t="s">
@@ -20162,7 +20143,7 @@
     </row>
     <row r="410" spans="1:11" ht="15">
       <c r="A410" s="20">
-        <v>114</v>
+        <v>107.8</v>
       </c>
       <c r="B410" s="20"/>
       <c r="C410" s="22" t="s">
@@ -20194,7 +20175,7 @@
     </row>
     <row r="411" spans="1:11" ht="15">
       <c r="A411" s="20">
-        <v>36.299999999999997</v>
+        <v>199</v>
       </c>
       <c r="B411" s="20"/>
       <c r="C411" s="22" t="s">
@@ -20226,7 +20207,7 @@
     </row>
     <row r="412" spans="1:11" ht="15">
       <c r="A412" s="20">
-        <v>219.92</v>
+        <v>222.2</v>
       </c>
       <c r="B412" s="20"/>
       <c r="C412" s="22" t="s">
@@ -20258,7 +20239,7 @@
     </row>
     <row r="413" spans="1:11" ht="15">
       <c r="A413" s="20">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B413" s="20"/>
       <c r="C413" s="22" t="s">
@@ -20290,7 +20271,7 @@
     </row>
     <row r="414" spans="1:11" ht="15">
       <c r="A414" s="20">
-        <v>172.7</v>
+        <v>155</v>
       </c>
       <c r="B414" s="20"/>
       <c r="C414" s="22" t="s">
@@ -20322,7 +20303,7 @@
     </row>
     <row r="415" spans="1:11" ht="15">
       <c r="A415" s="20">
-        <v>344.3</v>
+        <v>365.2</v>
       </c>
       <c r="B415" s="20"/>
       <c r="C415" s="22" t="s">
@@ -20353,7 +20334,7 @@
     </row>
     <row r="416" spans="1:11" ht="15">
       <c r="A416" s="20">
-        <v>95.04</v>
+        <v>139.5</v>
       </c>
       <c r="B416" s="20"/>
       <c r="C416" s="22" t="s">
@@ -20384,7 +20365,7 @@
     </row>
     <row r="417" spans="1:11" ht="15">
       <c r="A417" s="20">
-        <v>111.56</v>
+        <v>289</v>
       </c>
       <c r="B417" s="20"/>
       <c r="C417" s="22" t="s">
@@ -20415,7 +20396,7 @@
     </row>
     <row r="418" spans="1:11" ht="15">
       <c r="A418" s="20">
-        <v>95.7</v>
+        <v>119.9</v>
       </c>
       <c r="B418" s="20"/>
       <c r="C418" s="22" t="s">
@@ -20447,7 +20428,7 @@
     </row>
     <row r="419" spans="1:11" ht="15">
       <c r="A419" s="20">
-        <v>134.36000000000001</v>
+        <v>179.3</v>
       </c>
       <c r="B419" s="20"/>
       <c r="C419" s="22" t="s">
@@ -20479,7 +20460,7 @@
     </row>
     <row r="420" spans="1:11" ht="15">
       <c r="A420" s="20">
-        <v>83</v>
+        <v>117.7</v>
       </c>
       <c r="B420" s="20"/>
       <c r="C420" s="22" t="s">
@@ -20511,7 +20492,7 @@
     </row>
     <row r="421" spans="1:11" ht="15">
       <c r="A421" s="20">
-        <v>105.6</v>
+        <v>139</v>
       </c>
       <c r="B421" s="20"/>
       <c r="C421" s="22" t="s">
@@ -20543,7 +20524,7 @@
     </row>
     <row r="422" spans="1:11" ht="15">
       <c r="A422" s="20">
-        <v>82.83</v>
+        <v>82.61</v>
       </c>
       <c r="B422" s="20"/>
       <c r="C422" s="22" t="s">
@@ -20606,7 +20587,7 @@
     </row>
     <row r="424" spans="1:11" ht="15">
       <c r="A424" s="20">
-        <v>480.7</v>
+        <v>548.9</v>
       </c>
       <c r="B424" s="20"/>
       <c r="C424" s="22" t="s">
@@ -20638,7 +20619,7 @@
     </row>
     <row r="425" spans="1:11" ht="15">
       <c r="A425" s="20">
-        <v>86.13</v>
+        <v>184.8</v>
       </c>
       <c r="B425" s="20"/>
       <c r="C425" s="22" t="s">
@@ -20670,7 +20651,7 @@
     </row>
     <row r="426" spans="1:11" ht="15">
       <c r="A426" s="20">
-        <v>114</v>
+        <v>77.72</v>
       </c>
       <c r="B426" s="20"/>
       <c r="C426" s="22" t="s">
@@ -20701,7 +20682,7 @@
     </row>
     <row r="427" spans="1:11" ht="15">
       <c r="A427" s="20">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B427" s="20"/>
       <c r="C427" s="22" t="s">
@@ -20733,7 +20714,7 @@
     </row>
     <row r="428" spans="1:11" ht="15">
       <c r="A428" s="20">
-        <v>148.5</v>
+        <v>155.36000000000001</v>
       </c>
       <c r="B428" s="20"/>
       <c r="C428" s="22" t="s">
@@ -20764,9 +20745,7 @@
       </c>
     </row>
     <row r="429" spans="1:11" ht="15">
-      <c r="A429" s="20">
-        <v>121</v>
-      </c>
+      <c r="A429" s="20"/>
       <c r="B429" s="20"/>
       <c r="C429" s="22" t="s">
         <v>1376</v>
@@ -20797,7 +20776,7 @@
     </row>
     <row r="430" spans="1:11" ht="15">
       <c r="A430" s="20">
-        <v>148.5</v>
+        <v>155.36000000000001</v>
       </c>
       <c r="B430" s="20"/>
       <c r="C430" s="22" t="s">
@@ -20829,7 +20808,7 @@
     </row>
     <row r="431" spans="1:11" ht="15">
       <c r="A431" s="20">
-        <v>576.4</v>
+        <v>749</v>
       </c>
       <c r="B431" s="20"/>
       <c r="C431" s="22" t="s">
@@ -20893,7 +20872,7 @@
     </row>
     <row r="433" spans="1:11" ht="15">
       <c r="A433" s="20">
-        <v>34.6</v>
+        <v>28.5</v>
       </c>
       <c r="B433" s="20"/>
       <c r="C433" s="22" t="s">
@@ -20925,7 +20904,7 @@
     </row>
     <row r="434" spans="1:11" ht="15">
       <c r="A434" s="20">
-        <v>214.5</v>
+        <v>328.9</v>
       </c>
       <c r="B434" s="20"/>
       <c r="C434" s="22" t="s">
@@ -20956,7 +20935,7 @@
     </row>
     <row r="435" spans="1:11" ht="15">
       <c r="A435" s="20">
-        <v>103.4</v>
+        <v>99.22</v>
       </c>
       <c r="B435" s="20"/>
       <c r="C435" s="22" t="s">
@@ -20987,7 +20966,7 @@
     </row>
     <row r="436" spans="1:11" ht="15">
       <c r="A436" s="20">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="B436" s="20"/>
       <c r="C436" s="22" t="s">
@@ -21018,7 +20997,7 @@
     </row>
     <row r="437" spans="1:11" ht="15">
       <c r="A437" s="20">
-        <v>259.05</v>
+        <v>366.3</v>
       </c>
       <c r="C437" s="22" t="s">
         <v>1376</v>
@@ -21048,7 +21027,7 @@
     </row>
     <row r="438" spans="1:11" ht="15">
       <c r="A438" s="20">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="C438" s="22" t="s">
         <v>1376</v>
@@ -21078,7 +21057,7 @@
     </row>
     <row r="439" spans="1:11" ht="15">
       <c r="A439" s="20">
-        <v>3402.3</v>
+        <v>2775.3</v>
       </c>
       <c r="B439" s="20"/>
       <c r="C439" s="22" t="s">
@@ -21167,7 +21146,7 @@
     </row>
     <row r="442" spans="1:11" ht="15">
       <c r="A442" s="20">
-        <v>259.60000000000002</v>
+        <v>259</v>
       </c>
       <c r="C442" s="22" t="s">
         <v>1376</v>
@@ -21196,9 +21175,7 @@
       </c>
     </row>
     <row r="443" spans="1:11" ht="15">
-      <c r="A443" s="20">
-        <v>245.3</v>
-      </c>
+      <c r="A443" s="20"/>
       <c r="C443" s="22" t="s">
         <v>1376</v>
       </c>
@@ -21257,7 +21234,7 @@
     </row>
     <row r="445" spans="1:11" ht="15">
       <c r="A445" s="20">
-        <v>463.41</v>
+        <v>324.5</v>
       </c>
       <c r="C445" s="22" t="s">
         <v>1376</v>
@@ -21317,7 +21294,7 @@
     </row>
     <row r="447" spans="1:11" ht="15">
       <c r="A447">
-        <v>899</v>
+        <v>683</v>
       </c>
       <c r="C447" s="22" t="s">
         <v>1376</v>
@@ -21347,7 +21324,7 @@
     </row>
     <row r="448" spans="1:11" ht="15">
       <c r="A448" s="20">
-        <v>146.96</v>
+        <v>73.7</v>
       </c>
       <c r="C448" s="22" t="s">
         <v>1376</v>
@@ -21377,7 +21354,7 @@
     </row>
     <row r="449" spans="1:11" ht="15">
       <c r="A449" s="20">
-        <v>146.96</v>
+        <v>71.28</v>
       </c>
       <c r="C449" s="22" t="s">
         <v>1376</v>
@@ -21407,7 +21384,7 @@
     </row>
     <row r="450" spans="1:11" ht="15">
       <c r="A450" s="20">
-        <v>100.98</v>
+        <v>99</v>
       </c>
       <c r="C450" s="22" t="s">
         <v>1376</v>
@@ -21466,9 +21443,7 @@
       </c>
     </row>
     <row r="452" spans="1:11" ht="15">
-      <c r="A452" s="20">
-        <v>228.14</v>
-      </c>
+      <c r="A452" s="20"/>
       <c r="C452" s="22" t="s">
         <v>1376</v>
       </c>
@@ -21497,7 +21472,7 @@
     </row>
     <row r="453" spans="1:11" ht="15">
       <c r="A453" s="20">
-        <v>122.1</v>
+        <v>122.5</v>
       </c>
       <c r="C453" s="22" t="s">
         <v>1376</v>
@@ -21527,7 +21502,7 @@
     </row>
     <row r="454" spans="1:11" ht="15">
       <c r="A454" s="20">
-        <v>122.1</v>
+        <v>122.5</v>
       </c>
       <c r="C454" s="22" t="s">
         <v>1376</v>
@@ -21556,7 +21531,7 @@
       </c>
     </row>
     <row r="455" spans="1:11" ht="15">
-      <c r="A455">
+      <c r="A455" s="20">
         <v>750</v>
       </c>
       <c r="C455" s="22" t="s">
@@ -21586,8 +21561,8 @@
       </c>
     </row>
     <row r="456" spans="1:11" ht="15">
-      <c r="A456">
-        <v>322.3</v>
+      <c r="A456" s="20">
+        <v>350</v>
       </c>
       <c r="C456" s="22" t="s">
         <v>1376</v>
@@ -21616,8 +21591,8 @@
       </c>
     </row>
     <row r="457" spans="1:11" ht="15">
-      <c r="A457" s="28">
-        <v>324.5</v>
+      <c r="A457" s="20">
+        <v>313.5</v>
       </c>
       <c r="C457" s="22" t="s">
         <v>1376</v>
@@ -21646,8 +21621,8 @@
       </c>
     </row>
     <row r="458" spans="1:11" ht="15">
-      <c r="A458" s="28">
-        <v>162.80000000000001</v>
+      <c r="A458" s="20">
+        <v>160.57</v>
       </c>
       <c r="C458" s="22" t="s">
         <v>1376</v>
@@ -21676,8 +21651,8 @@
       </c>
     </row>
     <row r="459" spans="1:11" ht="15">
-      <c r="A459" s="28">
-        <v>162.80000000000001</v>
+      <c r="A459" s="20">
+        <v>160.57</v>
       </c>
       <c r="C459" s="22" t="s">
         <v>1376</v>
@@ -21706,8 +21681,8 @@
       </c>
     </row>
     <row r="460" spans="1:11" ht="15">
-      <c r="A460" s="28">
-        <v>162.80000000000001</v>
+      <c r="A460" s="20">
+        <v>160.57</v>
       </c>
       <c r="C460" s="22" t="s">
         <v>1376</v>
@@ -21736,7 +21711,7 @@
       </c>
     </row>
     <row r="461" spans="1:11" ht="15">
-      <c r="A461">
+      <c r="A461" s="20">
         <v>1177</v>
       </c>
       <c r="C461" s="22" t="s">
@@ -21766,8 +21741,8 @@
       </c>
     </row>
     <row r="462" spans="1:11" ht="15">
-      <c r="A462">
-        <v>73.150000000000006</v>
+      <c r="A462" s="20">
+        <v>64.23</v>
       </c>
       <c r="C462" s="22" t="s">
         <v>1376</v>
@@ -21796,7 +21771,7 @@
       </c>
     </row>
     <row r="463" spans="1:11" ht="15">
-      <c r="A463">
+      <c r="A463" s="20">
         <v>862.4</v>
       </c>
       <c r="C463" s="22" t="s">
@@ -21826,8 +21801,8 @@
       </c>
     </row>
     <row r="464" spans="1:11" ht="15">
-      <c r="A464">
-        <v>902</v>
+      <c r="A464" s="20">
+        <v>805.2</v>
       </c>
       <c r="C464" s="22" t="s">
         <v>1376</v>
@@ -21856,8 +21831,8 @@
       </c>
     </row>
     <row r="465" spans="1:11" ht="15">
-      <c r="A465" s="28">
-        <v>490.38</v>
+      <c r="A465" s="20">
+        <v>417.78</v>
       </c>
       <c r="C465" s="22" t="s">
         <v>1376</v>
@@ -21886,8 +21861,8 @@
       </c>
     </row>
     <row r="466" spans="1:11" ht="15">
-      <c r="A466" s="28">
-        <v>243.1</v>
+      <c r="A466" s="20">
+        <v>236.5</v>
       </c>
       <c r="C466" s="22" t="s">
         <v>1376</v>
@@ -21916,8 +21891,8 @@
       </c>
     </row>
     <row r="467" spans="1:11" ht="15">
-      <c r="A467">
-        <v>590.59</v>
+      <c r="A467" s="20">
+        <v>522.28</v>
       </c>
       <c r="C467" s="22" t="s">
         <v>1376</v>
@@ -21946,6 +21921,9 @@
       </c>
     </row>
     <row r="468" spans="1:11" ht="15">
+      <c r="A468" s="20">
+        <v>521.29</v>
+      </c>
       <c r="C468" s="22" t="s">
         <v>1376</v>
       </c>
@@ -21974,7 +21952,7 @@
     </row>
     <row r="469" spans="1:11" ht="15">
       <c r="A469">
-        <v>470</v>
+        <v>453.2</v>
       </c>
       <c r="C469" s="22" t="s">
         <v>1376</v>
@@ -22003,7 +21981,7 @@
       </c>
     </row>
     <row r="470" spans="1:11" ht="15">
-      <c r="A470">
+      <c r="A470" s="20">
         <v>349.8</v>
       </c>
       <c r="C470" s="22" t="s">
@@ -22033,8 +22011,8 @@
       </c>
     </row>
     <row r="471" spans="1:11" ht="15">
-      <c r="A471">
-        <v>498.30000000000013</v>
+      <c r="A471" s="20">
+        <v>388.3</v>
       </c>
       <c r="C471" s="22" t="s">
         <v>1376</v>
@@ -22063,6 +22041,9 @@
       </c>
     </row>
     <row r="472" spans="1:11" ht="15">
+      <c r="A472" s="20">
+        <v>1783.1</v>
+      </c>
       <c r="C472" s="22" t="s">
         <v>1376</v>
       </c>
@@ -22090,6 +22071,7 @@
       </c>
     </row>
     <row r="473" spans="1:11" ht="15">
+      <c r="A473"/>
       <c r="C473" s="22" t="s">
         <v>1376</v>
       </c>
@@ -22117,8 +22099,8 @@
       </c>
     </row>
     <row r="474" spans="1:11" ht="15">
-      <c r="A474">
-        <v>389.4</v>
+      <c r="A474" s="20">
+        <v>399.3</v>
       </c>
       <c r="C474" s="22" t="s">
         <v>1376</v>
@@ -22147,8 +22129,8 @@
       </c>
     </row>
     <row r="475" spans="1:11" ht="15">
-      <c r="A475">
-        <v>237.6</v>
+      <c r="A475" s="20">
+        <v>299</v>
       </c>
       <c r="C475" s="22" t="s">
         <v>1376</v>
@@ -22177,8 +22159,8 @@
       </c>
     </row>
     <row r="476" spans="1:11" ht="15">
-      <c r="A476">
-        <v>114.4</v>
+      <c r="A476" s="20">
+        <v>118.8</v>
       </c>
       <c r="C476" s="22" t="s">
         <v>1376</v>
@@ -22208,7 +22190,7 @@
     </row>
     <row r="477" spans="1:11" ht="15">
       <c r="A477">
-        <v>1834.8</v>
+        <v>1815</v>
       </c>
       <c r="C477" s="22" t="s">
         <v>1376</v>
@@ -22237,8 +22219,8 @@
       </c>
     </row>
     <row r="478" spans="1:11" ht="15">
-      <c r="A478">
-        <v>591.80000000000007</v>
+      <c r="A478" s="20">
+        <v>1254</v>
       </c>
       <c r="C478" s="22" t="s">
         <v>1376</v>
@@ -22267,8 +22249,8 @@
       </c>
     </row>
     <row r="479" spans="1:11" ht="15">
-      <c r="A479">
-        <v>71.5</v>
+      <c r="A479" s="20">
+        <v>60.33</v>
       </c>
       <c r="C479" s="22" t="s">
         <v>1376</v>
@@ -22297,8 +22279,8 @@
       </c>
     </row>
     <row r="480" spans="1:11" ht="15">
-      <c r="A480">
-        <v>71.5</v>
+      <c r="A480" s="20">
+        <v>49.5</v>
       </c>
       <c r="C480" s="22" t="s">
         <v>1376</v>
@@ -22327,8 +22309,8 @@
       </c>
     </row>
     <row r="481" spans="1:11" ht="15">
-      <c r="A481">
-        <v>106.7</v>
+      <c r="A481" s="20">
+        <v>111.1</v>
       </c>
       <c r="C481" s="22" t="s">
         <v>1376</v>
@@ -22357,8 +22339,8 @@
       </c>
     </row>
     <row r="482" spans="1:11" ht="15">
-      <c r="A482">
-        <v>156.19999999999999</v>
+      <c r="A482" s="20">
+        <v>161.69999999999999</v>
       </c>
       <c r="C482" s="22" t="s">
         <v>1376</v>
@@ -22387,9 +22369,7 @@
       </c>
     </row>
     <row r="483" spans="1:11" ht="15">
-      <c r="A483">
-        <v>146.30000000000001</v>
-      </c>
+      <c r="A483" s="20"/>
       <c r="C483" s="22" t="s">
         <v>1376</v>
       </c>
@@ -22417,7 +22397,7 @@
       </c>
     </row>
     <row r="484" spans="1:11" ht="15">
-      <c r="A484">
+      <c r="A484" s="20">
         <v>185.9</v>
       </c>
       <c r="C484" s="22" t="s">
@@ -22447,8 +22427,8 @@
       </c>
     </row>
     <row r="485" spans="1:11" ht="15">
-      <c r="A485">
-        <v>115.5</v>
+      <c r="A485" s="20">
+        <v>100.65</v>
       </c>
       <c r="C485" s="22" t="s">
         <v>1376</v>
@@ -22477,8 +22457,8 @@
       </c>
     </row>
     <row r="486" spans="1:11" ht="15">
-      <c r="A486">
-        <v>173.8</v>
+      <c r="A486" s="20">
+        <v>157.97999999999999</v>
       </c>
       <c r="C486" s="22" t="s">
         <v>1376</v>
@@ -22507,8 +22487,8 @@
       </c>
     </row>
     <row r="487" spans="1:11" ht="15">
-      <c r="A487">
-        <v>224.4</v>
+      <c r="A487" s="20">
+        <v>223.3</v>
       </c>
       <c r="C487" s="22" t="s">
         <v>1376</v>
@@ -22537,7 +22517,7 @@
       </c>
     </row>
     <row r="488" spans="1:11" ht="15">
-      <c r="A488">
+      <c r="A488" s="20">
         <v>306.79000000000002</v>
       </c>
       <c r="C488" s="22" t="s">
@@ -22567,8 +22547,8 @@
       </c>
     </row>
     <row r="489" spans="1:11" ht="15">
-      <c r="A489">
-        <v>485.1</v>
+      <c r="A489" s="20">
+        <v>309.10000000000002</v>
       </c>
       <c r="C489" s="22" t="s">
         <v>1376</v>
@@ -22597,6 +22577,9 @@
       </c>
     </row>
     <row r="490" spans="1:11" ht="15">
+      <c r="A490" s="20">
+        <v>309.10000000000002</v>
+      </c>
       <c r="C490" s="22" t="s">
         <v>1376</v>
       </c>
@@ -22624,8 +22607,8 @@
       </c>
     </row>
     <row r="491" spans="1:11" ht="15">
-      <c r="A491">
-        <v>536.80000000000007</v>
+      <c r="A491" s="20">
+        <v>321</v>
       </c>
       <c r="C491" s="22" t="s">
         <v>1376</v>
@@ -22654,9 +22637,7 @@
       </c>
     </row>
     <row r="492" spans="1:11" ht="15">
-      <c r="A492">
-        <v>1073.5999999999999</v>
-      </c>
+      <c r="A492" s="20"/>
       <c r="C492" s="22" t="s">
         <v>1376</v>
       </c>
@@ -22684,8 +22665,8 @@
       </c>
     </row>
     <row r="493" spans="1:11" ht="15">
-      <c r="A493">
-        <v>737.00000000000011</v>
+      <c r="A493" s="20">
+        <v>704</v>
       </c>
       <c r="C493" s="22" t="s">
         <v>1376</v>
@@ -22714,8 +22695,8 @@
       </c>
     </row>
     <row r="494" spans="1:11" ht="15">
-      <c r="A494">
-        <v>110</v>
+      <c r="A494" s="20">
+        <v>95.15</v>
       </c>
       <c r="C494" s="22" t="s">
         <v>1376</v>
@@ -22744,8 +22725,8 @@
       </c>
     </row>
     <row r="495" spans="1:11" ht="15">
-      <c r="A495">
-        <v>110</v>
+      <c r="A495" s="20">
+        <v>95.15</v>
       </c>
       <c r="C495" s="22" t="s">
         <v>1376</v>
@@ -22774,8 +22755,8 @@
       </c>
     </row>
     <row r="496" spans="1:11" ht="15">
-      <c r="A496">
-        <v>338.8</v>
+      <c r="A496" s="20">
+        <v>308</v>
       </c>
       <c r="C496" s="22" t="s">
         <v>1376</v>
@@ -22804,8 +22785,8 @@
       </c>
     </row>
     <row r="497" spans="1:11" ht="15">
-      <c r="A497">
-        <v>405.9</v>
+      <c r="A497" s="20">
+        <v>377.3</v>
       </c>
       <c r="C497" s="22" t="s">
         <v>1376</v>
@@ -22834,8 +22815,8 @@
       </c>
     </row>
     <row r="498" spans="1:11" ht="15">
-      <c r="A498">
-        <v>566.5</v>
+      <c r="A498" s="20">
+        <v>515</v>
       </c>
       <c r="C498" s="22" t="s">
         <v>1376</v>
@@ -22864,8 +22845,8 @@
       </c>
     </row>
     <row r="499" spans="1:11" ht="15">
-      <c r="A499">
-        <v>478.50000000000011</v>
+      <c r="A499" s="20">
+        <v>435</v>
       </c>
       <c r="C499" s="22" t="s">
         <v>1376</v>
@@ -22894,7 +22875,7 @@
       </c>
     </row>
     <row r="500" spans="1:11" ht="15">
-      <c r="A500">
+      <c r="A500" s="20">
         <v>446.6</v>
       </c>
       <c r="C500" s="22" t="s">
@@ -22924,8 +22905,8 @@
       </c>
     </row>
     <row r="501" spans="1:11" ht="15">
-      <c r="A501">
-        <v>437.8</v>
+      <c r="A501" s="20">
+        <v>398</v>
       </c>
       <c r="C501" s="22" t="s">
         <v>1376</v>
@@ -22954,8 +22935,8 @@
       </c>
     </row>
     <row r="502" spans="1:11" ht="15">
-      <c r="A502">
-        <v>207.9</v>
+      <c r="A502" s="20">
+        <v>187.9</v>
       </c>
       <c r="C502" s="22" t="s">
         <v>1376</v>
@@ -22984,8 +22965,8 @@
       </c>
     </row>
     <row r="503" spans="1:11" ht="15">
-      <c r="A503">
-        <v>470.8</v>
+      <c r="A503" s="20">
+        <v>285</v>
       </c>
       <c r="C503" s="22" t="s">
         <v>1376</v>
@@ -23014,8 +22995,8 @@
       </c>
     </row>
     <row r="504" spans="1:11" ht="15">
-      <c r="A504">
-        <v>191.4</v>
+      <c r="A504" s="20">
+        <v>191.39</v>
       </c>
       <c r="C504" s="22" t="s">
         <v>1376</v>
@@ -23044,8 +23025,8 @@
       </c>
     </row>
     <row r="505" spans="1:11" ht="15">
-      <c r="A505">
-        <v>378.4</v>
+      <c r="A505" s="20">
+        <v>404.8</v>
       </c>
       <c r="C505" s="22" t="s">
         <v>1376</v>
@@ -23074,8 +23055,8 @@
       </c>
     </row>
     <row r="506" spans="1:11" ht="15">
-      <c r="A506">
-        <v>657.80000000000007</v>
+      <c r="A506" s="20">
+        <v>484</v>
       </c>
       <c r="C506" s="22" t="s">
         <v>1376</v>
@@ -23104,8 +23085,8 @@
       </c>
     </row>
     <row r="507" spans="1:11" ht="15">
-      <c r="A507">
-        <v>547.80000000000007</v>
+      <c r="A507" s="20">
+        <v>547.79999999999995</v>
       </c>
       <c r="C507" s="22" t="s">
         <v>1376</v>
@@ -23135,7 +23116,7 @@
     </row>
     <row r="508" spans="1:11" ht="15">
       <c r="A508" s="20">
-        <v>593.20000000000005</v>
+        <v>432.45</v>
       </c>
       <c r="C508" s="22" t="s">
         <v>1376</v>
@@ -23164,7 +23145,7 @@
       </c>
     </row>
     <row r="509" spans="1:11" ht="15">
-      <c r="A509">
+      <c r="A509" s="20">
         <v>194.7</v>
       </c>
       <c r="C509" s="22" t="s">
@@ -23194,7 +23175,7 @@
       </c>
     </row>
     <row r="510" spans="1:11" ht="15">
-      <c r="A510">
+      <c r="A510" s="20">
         <v>250.8</v>
       </c>
       <c r="C510" s="22" t="s">
@@ -23224,8 +23205,8 @@
       </c>
     </row>
     <row r="511" spans="1:11" ht="15">
-      <c r="A511" s="22">
-        <v>128</v>
+      <c r="A511" s="20">
+        <v>139.9</v>
       </c>
       <c r="C511" s="22" t="s">
         <v>1376</v>
@@ -23254,8 +23235,8 @@
       </c>
     </row>
     <row r="512" spans="1:11" ht="15">
-      <c r="A512">
-        <v>125.4</v>
+      <c r="A512" s="20">
+        <v>169.89</v>
       </c>
       <c r="C512" s="22" t="s">
         <v>1376</v>
@@ -23284,8 +23265,8 @@
       </c>
     </row>
     <row r="513" spans="1:11" ht="15">
-      <c r="A513">
-        <v>119.9</v>
+      <c r="A513" s="20">
+        <v>146.30000000000001</v>
       </c>
       <c r="C513" s="22" t="s">
         <v>1376</v>
@@ -23344,9 +23325,7 @@
       </c>
     </row>
     <row r="515" spans="1:11" ht="15">
-      <c r="A515">
-        <v>993</v>
-      </c>
+      <c r="A515" s="20"/>
       <c r="C515" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23374,8 +23353,8 @@
       </c>
     </row>
     <row r="516" spans="1:11" ht="15">
-      <c r="A516">
-        <v>1124</v>
+      <c r="A516" s="20">
+        <v>1317</v>
       </c>
       <c r="C516" s="22" t="s">
         <v>1376</v>
@@ -23404,8 +23383,8 @@
       </c>
     </row>
     <row r="517" spans="1:11" ht="15">
-      <c r="A517">
-        <v>927.1</v>
+      <c r="A517" s="20">
+        <v>659</v>
       </c>
       <c r="C517" s="22" t="s">
         <v>1376</v>
@@ -23434,6 +23413,9 @@
       </c>
     </row>
     <row r="518" spans="1:11" ht="15">
+      <c r="A518" s="20">
+        <v>1317</v>
+      </c>
       <c r="C518" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23461,6 +23443,7 @@
       </c>
     </row>
     <row r="519" spans="1:11" ht="15">
+      <c r="A519" s="20"/>
       <c r="C519" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23488,8 +23471,8 @@
       </c>
     </row>
     <row r="520" spans="1:11" ht="15">
-      <c r="A520">
-        <v>858</v>
+      <c r="A520" s="20">
+        <v>656</v>
       </c>
       <c r="C520" s="22" t="s">
         <v>1376</v>
@@ -23518,8 +23501,8 @@
       </c>
     </row>
     <row r="521" spans="1:11" ht="15">
-      <c r="A521">
-        <v>659</v>
+      <c r="A521" s="20">
+        <v>540</v>
       </c>
       <c r="C521" s="22" t="s">
         <v>1376</v>
@@ -23548,7 +23531,7 @@
       </c>
     </row>
     <row r="522" spans="1:11" ht="15">
-      <c r="A522">
+      <c r="A522" s="20">
         <v>443.5</v>
       </c>
       <c r="C522" s="22" t="s">
@@ -23578,7 +23561,7 @@
       </c>
     </row>
     <row r="523" spans="1:11" ht="15">
-      <c r="A523">
+      <c r="A523" s="20">
         <v>329</v>
       </c>
       <c r="C523" s="22" t="s">
@@ -23608,8 +23591,8 @@
       </c>
     </row>
     <row r="524" spans="1:11" ht="15">
-      <c r="A524">
-        <v>1198</v>
+      <c r="A524" s="20">
+        <v>1100</v>
       </c>
       <c r="C524" s="22" t="s">
         <v>1376</v>
@@ -23638,8 +23621,8 @@
       </c>
     </row>
     <row r="525" spans="1:11" ht="15">
-      <c r="A525">
-        <v>599</v>
+      <c r="A525" s="20">
+        <v>480</v>
       </c>
       <c r="C525" s="22" t="s">
         <v>1376</v>
@@ -23668,6 +23651,9 @@
       </c>
     </row>
     <row r="526" spans="1:11" ht="15">
+      <c r="A526" s="20">
+        <v>876</v>
+      </c>
       <c r="C526" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23695,8 +23681,8 @@
       </c>
     </row>
     <row r="527" spans="1:11" ht="15">
-      <c r="A527">
-        <v>601</v>
+      <c r="A527" s="20">
+        <v>608.29999999999995</v>
       </c>
       <c r="C527" s="22" t="s">
         <v>1376</v>
@@ -23725,8 +23711,8 @@
       </c>
     </row>
     <row r="528" spans="1:11" ht="15">
-      <c r="A528">
-        <v>673</v>
+      <c r="A528" s="20">
+        <v>543</v>
       </c>
       <c r="C528" s="22" t="s">
         <v>1376</v>
@@ -23755,8 +23741,8 @@
       </c>
     </row>
     <row r="529" spans="1:11" ht="15">
-      <c r="A529">
-        <v>843</v>
+      <c r="A529" s="20">
+        <v>838</v>
       </c>
       <c r="C529" s="22" t="s">
         <v>1376</v>
@@ -23785,7 +23771,7 @@
       </c>
     </row>
     <row r="530" spans="1:11" ht="15">
-      <c r="A530">
+      <c r="A530" s="20">
         <v>325.60000000000002</v>
       </c>
       <c r="C530" s="22" t="s">
@@ -23815,8 +23801,8 @@
       </c>
     </row>
     <row r="531" spans="1:11" ht="15">
-      <c r="A531">
-        <v>851</v>
+      <c r="A531" s="20">
+        <v>829.4</v>
       </c>
       <c r="C531" s="22" t="s">
         <v>1376</v>
@@ -23845,9 +23831,7 @@
       </c>
     </row>
     <row r="532" spans="1:11" ht="15">
-      <c r="A532">
-        <v>1702</v>
-      </c>
+      <c r="A532" s="20"/>
       <c r="C532" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23875,8 +23859,8 @@
       </c>
     </row>
     <row r="533" spans="1:11" ht="15">
-      <c r="A533">
-        <v>648</v>
+      <c r="A533" s="20">
+        <v>619</v>
       </c>
       <c r="C533" s="22" t="s">
         <v>1376</v>
@@ -23905,8 +23889,8 @@
       </c>
     </row>
     <row r="534" spans="1:11" ht="15">
-      <c r="A534">
-        <v>756.80000000000007</v>
+      <c r="A534" s="20">
+        <v>997</v>
       </c>
       <c r="C534" s="22" t="s">
         <v>1376</v>
@@ -23935,9 +23919,7 @@
       </c>
     </row>
     <row r="535" spans="1:11" ht="15">
-      <c r="A535">
-        <v>1513.6</v>
-      </c>
+      <c r="A535" s="20"/>
       <c r="C535" s="22" t="s">
         <v>1376</v>
       </c>
@@ -23965,7 +23947,7 @@
       </c>
     </row>
     <row r="536" spans="1:11" ht="15">
-      <c r="A536">
+      <c r="A536" s="20">
         <v>550</v>
       </c>
       <c r="C536" s="22" t="s">
@@ -23995,8 +23977,8 @@
       </c>
     </row>
     <row r="537" spans="1:11" ht="15">
-      <c r="A537">
-        <v>1563</v>
+      <c r="A537" s="20">
+        <v>1578</v>
       </c>
       <c r="C537" s="22" t="s">
         <v>1376</v>
@@ -24025,8 +24007,8 @@
       </c>
     </row>
     <row r="538" spans="1:11" ht="15">
-      <c r="A538">
-        <v>1137</v>
+      <c r="A538" s="20">
+        <v>999</v>
       </c>
       <c r="C538" s="22" t="s">
         <v>1376</v>
@@ -24055,9 +24037,7 @@
       </c>
     </row>
     <row r="539" spans="1:11" ht="15">
-      <c r="A539">
-        <v>291</v>
-      </c>
+      <c r="A539" s="20"/>
       <c r="C539" s="22" t="s">
         <v>1376</v>
       </c>
@@ -24085,8 +24065,8 @@
       </c>
     </row>
     <row r="540" spans="1:11" ht="15">
-      <c r="A540">
-        <v>229.9</v>
+      <c r="A540" s="20">
+        <v>226</v>
       </c>
       <c r="C540" s="22" t="s">
         <v>1376</v>
@@ -24115,7 +24095,7 @@
       </c>
     </row>
     <row r="541" spans="1:11" ht="15">
-      <c r="A541">
+      <c r="A541" s="20">
         <v>560</v>
       </c>
       <c r="C541" s="22" t="s">
@@ -24145,8 +24125,8 @@
       </c>
     </row>
     <row r="542" spans="1:11" ht="15">
-      <c r="A542">
-        <v>1073.5999999999999</v>
+      <c r="A542" s="20">
+        <v>745</v>
       </c>
       <c r="C542" s="22" t="s">
         <v>1376</v>
@@ -24175,8 +24155,8 @@
       </c>
     </row>
     <row r="543" spans="1:11" ht="15">
-      <c r="A543">
-        <v>972</v>
+      <c r="A543" s="20">
+        <v>839</v>
       </c>
       <c r="C543" s="22" t="s">
         <v>1376</v>
@@ -24205,8 +24185,8 @@
       </c>
     </row>
     <row r="544" spans="1:11" ht="15">
-      <c r="A544">
-        <v>683</v>
+      <c r="A544" s="20">
+        <v>656</v>
       </c>
       <c r="C544" s="22" t="s">
         <v>1376</v>
@@ -24235,8 +24215,8 @@
       </c>
     </row>
     <row r="545" spans="1:11" ht="15">
-      <c r="A545">
-        <v>393</v>
+      <c r="A545" s="20">
+        <v>458</v>
       </c>
       <c r="C545" s="22" t="s">
         <v>1376</v>
@@ -24265,8 +24245,8 @@
       </c>
     </row>
     <row r="546" spans="1:11" ht="15">
-      <c r="A546">
-        <v>837</v>
+      <c r="A546" s="20">
+        <v>728.86</v>
       </c>
       <c r="C546" s="22" t="s">
         <v>1376</v>
@@ -24295,8 +24275,8 @@
       </c>
     </row>
     <row r="547" spans="1:11" ht="15">
-      <c r="A547">
-        <v>976</v>
+      <c r="A547" s="20">
+        <v>1267</v>
       </c>
       <c r="C547" s="22" t="s">
         <v>1376</v>
@@ -24325,8 +24305,8 @@
       </c>
     </row>
     <row r="548" spans="1:11" ht="15">
-      <c r="A548">
-        <v>837</v>
+      <c r="A548" s="20">
+        <v>728.86</v>
       </c>
       <c r="C548" s="22" t="s">
         <v>1376</v>
@@ -24355,6 +24335,7 @@
       </c>
     </row>
     <row r="549" spans="1:11" ht="15">
+      <c r="A549" s="20"/>
       <c r="C549" s="22" t="s">
         <v>1376</v>
       </c>
@@ -24382,8 +24363,8 @@
       </c>
     </row>
     <row r="550" spans="1:11" ht="15">
-      <c r="A550">
-        <v>938</v>
+      <c r="A550" s="20">
+        <v>1033</v>
       </c>
       <c r="C550" s="22" t="s">
         <v>1376</v>
@@ -24412,8 +24393,8 @@
       </c>
     </row>
     <row r="551" spans="1:11" ht="15">
-      <c r="A551">
-        <v>938</v>
+      <c r="A551" s="20">
+        <v>730</v>
       </c>
       <c r="C551" s="22" t="s">
         <v>1376</v>
@@ -24442,8 +24423,8 @@
       </c>
     </row>
     <row r="552" spans="1:11" ht="15">
-      <c r="A552">
-        <v>679</v>
+      <c r="A552" s="20">
+        <v>666</v>
       </c>
       <c r="C552" s="22" t="s">
         <v>1376</v>
@@ -24472,8 +24453,8 @@
       </c>
     </row>
     <row r="553" spans="1:11" ht="15">
-      <c r="A553">
-        <v>881.1</v>
+      <c r="A553" s="20">
+        <v>952</v>
       </c>
       <c r="C553" s="22" t="s">
         <v>1376</v>
@@ -24502,8 +24483,8 @@
       </c>
     </row>
     <row r="554" spans="1:11" ht="15">
-      <c r="A554">
-        <v>320</v>
+      <c r="A554" s="20">
+        <v>459.8</v>
       </c>
       <c r="C554" s="22" t="s">
         <v>1376</v>
@@ -24532,8 +24513,8 @@
       </c>
     </row>
     <row r="555" spans="1:11" ht="15">
-      <c r="A555">
-        <v>298</v>
+      <c r="A555" s="20">
+        <v>300.3</v>
       </c>
       <c r="C555" s="22" t="s">
         <v>1376</v>
@@ -24562,8 +24543,8 @@
       </c>
     </row>
     <row r="556" spans="1:11" ht="15">
-      <c r="A556">
-        <v>432</v>
+      <c r="A556" s="20">
+        <v>620</v>
       </c>
       <c r="C556" s="22" t="s">
         <v>1376</v>
@@ -24592,7 +24573,7 @@
       </c>
     </row>
     <row r="557" spans="1:11" ht="15">
-      <c r="A557">
+      <c r="A557" s="20">
         <v>971</v>
       </c>
       <c r="C557" s="22" t="s">
@@ -24622,7 +24603,7 @@
       </c>
     </row>
     <row r="558" spans="1:11" ht="15">
-      <c r="A558">
+      <c r="A558" s="20">
         <v>349</v>
       </c>
       <c r="C558" s="22" t="s">
@@ -24652,8 +24633,8 @@
       </c>
     </row>
     <row r="559" spans="1:11" ht="15">
-      <c r="A559">
-        <v>990.00000000000011</v>
+      <c r="A559" s="20">
+        <v>859</v>
       </c>
       <c r="C559" s="22" t="s">
         <v>1376</v>
@@ -24682,7 +24663,7 @@
       </c>
     </row>
     <row r="560" spans="1:11" ht="15">
-      <c r="A560">
+      <c r="A560" s="20">
         <v>233.2</v>
       </c>
       <c r="C560" s="22" t="s">
@@ -24712,8 +24693,8 @@
       </c>
     </row>
     <row r="561" spans="1:11" ht="15">
-      <c r="A561">
-        <v>198</v>
+      <c r="A561" s="20">
+        <v>367.4</v>
       </c>
       <c r="C561" s="22" t="s">
         <v>1376</v>
@@ -24742,8 +24723,8 @@
       </c>
     </row>
     <row r="562" spans="1:11" ht="15">
-      <c r="A562">
-        <v>374</v>
+      <c r="A562" s="20">
+        <v>390</v>
       </c>
       <c r="C562" s="22" t="s">
         <v>1376</v>
@@ -24772,8 +24753,8 @@
       </c>
     </row>
     <row r="563" spans="1:11" ht="15">
-      <c r="A563">
-        <v>359</v>
+      <c r="A563" s="20">
+        <v>246.4</v>
       </c>
       <c r="C563" s="22" t="s">
         <v>1376</v>
@@ -24802,8 +24783,8 @@
       </c>
     </row>
     <row r="564" spans="1:11" ht="15">
-      <c r="A564">
-        <v>286</v>
+      <c r="A564" s="20">
+        <v>296</v>
       </c>
       <c r="C564" s="22" t="s">
         <v>1376</v>
@@ -24832,8 +24813,8 @@
       </c>
     </row>
     <row r="565" spans="1:11" ht="15">
-      <c r="A565">
-        <v>115</v>
+      <c r="A565" s="20">
+        <v>127.2</v>
       </c>
       <c r="C565" s="22" t="s">
         <v>1376</v>
@@ -24862,8 +24843,8 @@
       </c>
     </row>
     <row r="566" spans="1:11" ht="15">
-      <c r="A566">
-        <v>103.51</v>
+      <c r="A566" s="20">
+        <v>101.2</v>
       </c>
       <c r="C566" s="22" t="s">
         <v>1376</v>
@@ -24892,8 +24873,8 @@
       </c>
     </row>
     <row r="567" spans="1:11" ht="15">
-      <c r="A567">
-        <v>147.18</v>
+      <c r="A567" s="20">
+        <v>147.26</v>
       </c>
       <c r="C567" s="22" t="s">
         <v>1376</v>
@@ -24922,9 +24903,7 @@
       </c>
     </row>
     <row r="568" spans="1:11" ht="15">
-      <c r="A568">
-        <v>200.42</v>
-      </c>
+      <c r="A568" s="20"/>
       <c r="C568" s="22" t="s">
         <v>1376</v>
       </c>
@@ -24952,8 +24931,8 @@
       </c>
     </row>
     <row r="569" spans="1:11" ht="15">
-      <c r="A569">
-        <v>149.6</v>
+      <c r="A569" s="20">
+        <v>271.7</v>
       </c>
       <c r="C569" s="22" t="s">
         <v>1376</v>
@@ -24982,9 +24961,7 @@
       </c>
     </row>
     <row r="570" spans="1:11" ht="15">
-      <c r="A570">
-        <v>398</v>
-      </c>
+      <c r="A570" s="20"/>
       <c r="C570" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25012,6 +24989,9 @@
       </c>
     </row>
     <row r="571" spans="1:11" ht="15">
+      <c r="A571" s="20">
+        <v>147.26</v>
+      </c>
       <c r="C571" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25039,8 +25019,8 @@
       </c>
     </row>
     <row r="572" spans="1:11" ht="15">
-      <c r="A572">
-        <v>159</v>
+      <c r="A572" s="20">
+        <v>225</v>
       </c>
       <c r="C572" s="22" t="s">
         <v>1376</v>
@@ -25069,8 +25049,8 @@
       </c>
     </row>
     <row r="573" spans="1:11" ht="15">
-      <c r="A573">
-        <v>268</v>
+      <c r="A573" s="20">
+        <v>288</v>
       </c>
       <c r="C573" s="22" t="s">
         <v>1376</v>
@@ -25099,7 +25079,7 @@
       </c>
     </row>
     <row r="574" spans="1:11" ht="15">
-      <c r="A574">
+      <c r="A574" s="20">
         <v>149.6</v>
       </c>
       <c r="C574" s="22" t="s">
@@ -25129,8 +25109,8 @@
       </c>
     </row>
     <row r="575" spans="1:11" ht="15">
-      <c r="A575">
-        <v>499</v>
+      <c r="A575" s="20">
+        <v>359</v>
       </c>
       <c r="C575" s="22" t="s">
         <v>1376</v>
@@ -25159,8 +25139,8 @@
       </c>
     </row>
     <row r="576" spans="1:11" ht="15">
-      <c r="A576">
-        <v>366</v>
+      <c r="A576" s="20">
+        <v>402.6</v>
       </c>
       <c r="C576" s="22" t="s">
         <v>1376</v>
@@ -25189,6 +25169,7 @@
       </c>
     </row>
     <row r="577" spans="1:11" ht="15">
+      <c r="A577" s="20"/>
       <c r="C577" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25216,8 +25197,8 @@
       </c>
     </row>
     <row r="578" spans="1:11" ht="15">
-      <c r="A578">
-        <v>294.8</v>
+      <c r="A578" s="20">
+        <v>294.99</v>
       </c>
       <c r="C578" s="22" t="s">
         <v>1376</v>
@@ -25246,8 +25227,8 @@
       </c>
     </row>
     <row r="579" spans="1:11" ht="15">
-      <c r="A579">
-        <v>176</v>
+      <c r="A579" s="20">
+        <v>174.9</v>
       </c>
       <c r="C579" s="22" t="s">
         <v>1376</v>
@@ -25306,7 +25287,7 @@
       </c>
     </row>
     <row r="581" spans="1:11" ht="15">
-      <c r="A581">
+      <c r="A581" s="20">
         <v>1436</v>
       </c>
       <c r="C581" s="22" t="s">
@@ -25336,7 +25317,7 @@
       </c>
     </row>
     <row r="582" spans="1:11" ht="15">
-      <c r="A582">
+      <c r="A582" s="20">
         <v>1946</v>
       </c>
       <c r="C582" s="22" t="s">
@@ -25366,8 +25347,8 @@
       </c>
     </row>
     <row r="583" spans="1:11" ht="15">
-      <c r="A583">
-        <v>383.9</v>
+      <c r="A583" s="20">
+        <v>504.9</v>
       </c>
       <c r="C583" s="22" t="s">
         <v>1376</v>
@@ -25396,8 +25377,8 @@
       </c>
     </row>
     <row r="584" spans="1:11" ht="15">
-      <c r="A584">
-        <v>369.6</v>
+      <c r="A584" s="20">
+        <v>548.9</v>
       </c>
       <c r="C584" s="22" t="s">
         <v>1376</v>
@@ -25426,8 +25407,8 @@
       </c>
     </row>
     <row r="585" spans="1:11" ht="15">
-      <c r="A585">
-        <v>155</v>
+      <c r="A585" s="20">
+        <v>196.9</v>
       </c>
       <c r="C585" s="22" t="s">
         <v>1376</v>
@@ -25456,6 +25437,7 @@
       </c>
     </row>
     <row r="586" spans="1:11" ht="15">
+      <c r="A586" s="20"/>
       <c r="C586" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25483,6 +25465,7 @@
       </c>
     </row>
     <row r="587" spans="1:11" ht="15">
+      <c r="A587" s="20"/>
       <c r="C587" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25510,6 +25493,9 @@
       </c>
     </row>
     <row r="588" spans="1:11" ht="15">
+      <c r="A588" s="20">
+        <v>508.2</v>
+      </c>
       <c r="C588" s="22" t="s">
         <v>1376</v>
       </c>
@@ -25537,7 +25523,7 @@
       </c>
     </row>
     <row r="589" spans="1:11" ht="15">
-      <c r="A589">
+      <c r="A589" s="20">
         <v>968</v>
       </c>
       <c r="C589" s="22" t="s">
@@ -25567,7 +25553,7 @@
       </c>
     </row>
     <row r="590" spans="1:11" ht="15">
-      <c r="A590">
+      <c r="A590" s="20">
         <v>968</v>
       </c>
       <c r="C590" s="22" t="s">
@@ -25597,7 +25583,7 @@
       </c>
     </row>
     <row r="591" spans="1:11" ht="15">
-      <c r="A591">
+      <c r="A591" s="20">
         <v>212.3</v>
       </c>
       <c r="C591" s="22" t="s">
@@ -25628,7 +25614,7 @@
     </row>
     <row r="592" spans="1:11" ht="15">
       <c r="A592" s="20">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="C592" s="22" t="s">
         <v>1376</v>
@@ -25657,7 +25643,7 @@
       </c>
     </row>
     <row r="593" spans="1:11" ht="15">
-      <c r="A593">
+      <c r="A593" s="20">
         <v>258</v>
       </c>
       <c r="C593" s="22" t="s">
@@ -25687,7 +25673,7 @@
       </c>
     </row>
     <row r="594" spans="1:11" ht="15">
-      <c r="A594">
+      <c r="A594" s="20">
         <v>69</v>
       </c>
       <c r="C594" s="22" t="s">
@@ -25717,8 +25703,8 @@
       </c>
     </row>
     <row r="595" spans="1:11" ht="15">
-      <c r="A595">
-        <v>754</v>
+      <c r="A595" s="20">
+        <v>780</v>
       </c>
       <c r="C595" s="22" t="s">
         <v>1376</v>
@@ -25747,7 +25733,7 @@
       </c>
     </row>
     <row r="596" spans="1:11" ht="15">
-      <c r="A596">
+      <c r="A596" s="20">
         <v>1230</v>
       </c>
       <c r="C596" s="22" t="s">
@@ -25777,8 +25763,8 @@
       </c>
     </row>
     <row r="597" spans="1:11" ht="15">
-      <c r="A597">
-        <v>788</v>
+      <c r="A597" s="20">
+        <v>748</v>
       </c>
       <c r="C597" s="22" t="s">
         <v>1376</v>
@@ -25807,8 +25793,8 @@
       </c>
     </row>
     <row r="598" spans="1:11" ht="15">
-      <c r="A598">
-        <v>788</v>
+      <c r="A598" s="20">
+        <v>1208.9000000000001</v>
       </c>
       <c r="C598" s="22" t="s">
         <v>1376</v>
@@ -25837,8 +25823,8 @@
       </c>
     </row>
     <row r="599" spans="1:11" ht="15">
-      <c r="A599">
-        <v>423</v>
+      <c r="A599" s="20">
+        <v>360</v>
       </c>
       <c r="C599" s="22" t="s">
         <v>1376</v>
@@ -25867,8 +25853,8 @@
       </c>
     </row>
     <row r="600" spans="1:11" ht="15">
-      <c r="A600">
-        <v>323</v>
+      <c r="A600" s="20">
+        <v>323.19</v>
       </c>
       <c r="C600" s="22" t="s">
         <v>1376</v>
@@ -25897,8 +25883,8 @@
       </c>
     </row>
     <row r="601" spans="1:11" ht="15">
-      <c r="A601">
-        <v>711</v>
+      <c r="A601" s="20">
+        <v>782.1</v>
       </c>
       <c r="C601" s="22" t="s">
         <v>1376</v>
@@ -25927,7 +25913,7 @@
       </c>
     </row>
     <row r="602" spans="1:11" ht="15">
-      <c r="A602">
+      <c r="A602" s="20">
         <v>1010</v>
       </c>
       <c r="C602" s="22" t="s">
@@ -25957,7 +25943,7 @@
       </c>
     </row>
     <row r="603" spans="1:11" ht="15">
-      <c r="A603">
+      <c r="A603" s="20">
         <v>662</v>
       </c>
       <c r="C603" s="22" t="s">
@@ -25987,8 +25973,8 @@
       </c>
     </row>
     <row r="604" spans="1:11" ht="15">
-      <c r="A604">
-        <v>680</v>
+      <c r="A604" s="20">
+        <v>758</v>
       </c>
       <c r="C604" s="22" t="s">
         <v>1376</v>
@@ -26017,8 +26003,8 @@
       </c>
     </row>
     <row r="605" spans="1:11" ht="15">
-      <c r="A605">
-        <v>844.9</v>
+      <c r="A605" s="20">
+        <v>844.99</v>
       </c>
       <c r="C605" s="22" t="s">
         <v>1376</v>
@@ -26047,8 +26033,8 @@
       </c>
     </row>
     <row r="606" spans="1:11" ht="15">
-      <c r="A606">
-        <v>429</v>
+      <c r="A606" s="20">
+        <v>320</v>
       </c>
       <c r="C606" s="22" t="s">
         <v>1376</v>
@@ -26077,9 +26063,7 @@
       </c>
     </row>
     <row r="607" spans="1:11" ht="15">
-      <c r="A607">
-        <v>422</v>
-      </c>
+      <c r="A607" s="20"/>
       <c r="C607" s="22" t="s">
         <v>1376</v>
       </c>
@@ -26107,8 +26091,8 @@
       </c>
     </row>
     <row r="608" spans="1:11" ht="15">
-      <c r="A608">
-        <v>376</v>
+      <c r="A608" s="20">
+        <v>348</v>
       </c>
       <c r="C608" s="22" t="s">
         <v>1376</v>
@@ -26137,8 +26121,8 @@
       </c>
     </row>
     <row r="609" spans="1:11" ht="15">
-      <c r="A609">
-        <v>1010</v>
+      <c r="A609" s="20">
+        <v>800</v>
       </c>
       <c r="C609" s="22" t="s">
         <v>1376</v>
@@ -26167,7 +26151,7 @@
       </c>
     </row>
     <row r="610" spans="1:11" ht="15">
-      <c r="A610">
+      <c r="A610" s="20">
         <v>761</v>
       </c>
       <c r="C610" s="22" t="s">
@@ -26197,8 +26181,8 @@
       </c>
     </row>
     <row r="611" spans="1:11" ht="15">
-      <c r="A611">
-        <v>401.50000000000011</v>
+      <c r="A611" s="20">
+        <v>548.9</v>
       </c>
       <c r="C611" s="22" t="s">
         <v>1376</v>
@@ -26227,8 +26211,8 @@
       </c>
     </row>
     <row r="612" spans="1:11" ht="15">
-      <c r="A612">
-        <v>710.6</v>
+      <c r="A612" s="20">
+        <v>1086.8</v>
       </c>
       <c r="C612" s="22" t="s">
         <v>1376</v>
@@ -26257,8 +26241,8 @@
       </c>
     </row>
     <row r="613" spans="1:11" ht="15">
-      <c r="A613">
-        <v>457.6</v>
+      <c r="A613" s="20">
+        <v>548.9</v>
       </c>
       <c r="C613" s="22" t="s">
         <v>1376</v>
@@ -26287,8 +26271,8 @@
       </c>
     </row>
     <row r="614" spans="1:11" ht="15">
-      <c r="A614">
-        <v>359</v>
+      <c r="A614" s="20">
+        <v>303.60000000000002</v>
       </c>
       <c r="C614" s="22" t="s">
         <v>1376</v>
@@ -26317,8 +26301,8 @@
       </c>
     </row>
     <row r="615" spans="1:11" ht="15">
-      <c r="A615">
-        <v>356.4</v>
+      <c r="A615" s="20">
+        <v>640</v>
       </c>
       <c r="C615" s="22" t="s">
         <v>1376</v>
@@ -26347,8 +26331,8 @@
       </c>
     </row>
     <row r="616" spans="1:11" ht="15">
-      <c r="A616">
-        <v>631</v>
+      <c r="A616" s="20">
+        <v>940</v>
       </c>
       <c r="C616" s="22" t="s">
         <v>1376</v>
@@ -26377,8 +26361,8 @@
       </c>
     </row>
     <row r="617" spans="1:11" ht="15">
-      <c r="A617">
-        <v>602</v>
+      <c r="A617" s="20">
+        <v>608.29999999999995</v>
       </c>
       <c r="C617" s="22" t="s">
         <v>1376</v>
@@ -26407,8 +26391,8 @@
       </c>
     </row>
     <row r="618" spans="1:11" ht="15">
-      <c r="A618">
-        <v>385</v>
+      <c r="A618" s="20">
+        <v>363</v>
       </c>
       <c r="C618" s="22" t="s">
         <v>1376</v>
@@ -26437,8 +26421,8 @@
       </c>
     </row>
     <row r="619" spans="1:11" ht="15">
-      <c r="A619">
-        <v>719</v>
+      <c r="A619" s="20">
+        <v>858</v>
       </c>
       <c r="C619" s="22" t="s">
         <v>1376</v>
@@ -26467,8 +26451,8 @@
       </c>
     </row>
     <row r="620" spans="1:11" ht="15">
-      <c r="A620">
-        <v>269</v>
+      <c r="A620" s="20">
+        <v>380</v>
       </c>
       <c r="C620" s="22" t="s">
         <v>1376</v>
@@ -26497,8 +26481,8 @@
       </c>
     </row>
     <row r="621" spans="1:11" ht="15">
-      <c r="A621">
-        <v>749</v>
+      <c r="A621" s="20">
+        <v>761</v>
       </c>
       <c r="C621" s="22" t="s">
         <v>1376</v>
@@ -26527,7 +26511,7 @@
       </c>
     </row>
     <row r="622" spans="1:11" ht="15">
-      <c r="A622">
+      <c r="A622" s="20">
         <v>211.2</v>
       </c>
       <c r="C622" s="22" t="s">
@@ -26557,8 +26541,8 @@
       </c>
     </row>
     <row r="623" spans="1:11" ht="15">
-      <c r="A623">
-        <v>444.4</v>
+      <c r="A623" s="20">
+        <v>418</v>
       </c>
       <c r="C623" s="22" t="s">
         <v>1376</v>
@@ -26587,8 +26571,8 @@
       </c>
     </row>
     <row r="624" spans="1:11" ht="15">
-      <c r="A624">
-        <v>286</v>
+      <c r="A624" s="20">
+        <v>266.2</v>
       </c>
       <c r="C624" s="22" t="s">
         <v>1376</v>
@@ -26617,8 +26601,8 @@
       </c>
     </row>
     <row r="625" spans="1:11" ht="15">
-      <c r="A625">
-        <v>840.40000000000009</v>
+      <c r="A625" s="20">
+        <v>840.8</v>
       </c>
       <c r="C625" s="22" t="s">
         <v>1376</v>
@@ -26647,7 +26631,7 @@
       </c>
     </row>
     <row r="626" spans="1:11" ht="15">
-      <c r="A626">
+      <c r="A626" s="20">
         <v>193.6</v>
       </c>
       <c r="C626" s="22" t="s">
@@ -26677,7 +26661,7 @@
       </c>
     </row>
     <row r="627" spans="1:11" ht="15">
-      <c r="A627">
+      <c r="A627" s="20">
         <v>124.5</v>
       </c>
       <c r="C627" s="22" t="s">
@@ -26707,8 +26691,8 @@
       </c>
     </row>
     <row r="628" spans="1:11" ht="15">
-      <c r="A628">
-        <v>224</v>
+      <c r="A628" s="20">
+        <v>280</v>
       </c>
       <c r="C628" s="22" t="s">
         <v>1376</v>
@@ -26737,8 +26721,8 @@
       </c>
     </row>
     <row r="629" spans="1:11" ht="15">
-      <c r="A629">
-        <v>295.89999999999998</v>
+      <c r="A629" s="20">
+        <v>334.9</v>
       </c>
       <c r="C629" s="22" t="s">
         <v>1376</v>
@@ -26767,8 +26751,8 @@
       </c>
     </row>
     <row r="630" spans="1:11" ht="15">
-      <c r="A630">
-        <v>325.38000000000011</v>
+      <c r="A630" s="20">
+        <v>666</v>
       </c>
       <c r="C630" s="22" t="s">
         <v>1376</v>
@@ -26797,7 +26781,7 @@
       </c>
     </row>
     <row r="631" spans="1:11" ht="15">
-      <c r="A631">
+      <c r="A631" s="20">
         <v>479.6</v>
       </c>
       <c r="C631" s="22" t="s">
@@ -26827,8 +26811,8 @@
       </c>
     </row>
     <row r="632" spans="1:11" ht="15">
-      <c r="A632">
-        <v>568</v>
+      <c r="A632" s="20">
+        <v>476.3</v>
       </c>
       <c r="C632" s="22" t="s">
         <v>1376</v>
@@ -26857,8 +26841,8 @@
       </c>
     </row>
     <row r="633" spans="1:11" ht="15">
-      <c r="A633">
-        <v>407.00000000000011</v>
+      <c r="A633" s="20">
+        <v>427.9</v>
       </c>
       <c r="C633" s="22" t="s">
         <v>1376</v>
@@ -26887,8 +26871,8 @@
       </c>
     </row>
     <row r="634" spans="1:11" ht="15">
-      <c r="A634">
-        <v>389.4</v>
+      <c r="A634" s="20">
+        <v>391.6</v>
       </c>
       <c r="C634" s="22" t="s">
         <v>1376</v>
@@ -26917,8 +26901,8 @@
       </c>
     </row>
     <row r="635" spans="1:11" ht="15">
-      <c r="A635">
-        <v>389.4</v>
+      <c r="A635" s="20">
+        <v>391.6</v>
       </c>
       <c r="C635" s="22" t="s">
         <v>1376</v>
@@ -26948,7 +26932,7 @@
     </row>
     <row r="636" spans="1:11" ht="15">
       <c r="A636" s="20">
-        <v>3402.3</v>
+        <v>2263.8000000000002</v>
       </c>
       <c r="C636" s="22" t="s">
         <v>1376</v>
@@ -26977,8 +26961,8 @@
       </c>
     </row>
     <row r="637" spans="1:11" ht="15">
-      <c r="A637">
-        <v>739.2</v>
+      <c r="A637" s="20">
+        <v>701.8</v>
       </c>
       <c r="C637" s="22" t="s">
         <v>1376</v>
@@ -27008,7 +26992,7 @@
     </row>
     <row r="638" spans="1:11" ht="15">
       <c r="A638" s="20">
-        <v>3402.3</v>
+        <v>2263.8000000000002</v>
       </c>
       <c r="C638" s="22" t="s">
         <v>1376</v>
@@ -27038,7 +27022,7 @@
     </row>
     <row r="639" spans="1:11" ht="15">
       <c r="A639">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="C639" s="22" t="s">
         <v>1376</v>
@@ -27067,8 +27051,8 @@
       </c>
     </row>
     <row r="640" spans="1:11" ht="15">
-      <c r="A640">
-        <v>498</v>
+      <c r="A640" s="20">
+        <v>338.8</v>
       </c>
       <c r="C640" s="22" t="s">
         <v>1376</v>
@@ -27097,8 +27081,8 @@
       </c>
     </row>
     <row r="641" spans="1:11" ht="15">
-      <c r="A641">
-        <v>89</v>
+      <c r="A641" s="20">
+        <v>109</v>
       </c>
       <c r="C641" s="22" t="s">
         <v>1376</v>
@@ -27127,8 +27111,8 @@
       </c>
     </row>
     <row r="642" spans="1:11" ht="15">
-      <c r="A642">
-        <v>405.9</v>
+      <c r="A642" s="20">
+        <v>400.4</v>
       </c>
       <c r="C642" s="22" t="s">
         <v>1376</v>
@@ -27157,8 +27141,8 @@
       </c>
     </row>
     <row r="643" spans="1:11" ht="15">
-      <c r="A643">
-        <v>88</v>
+      <c r="A643" s="20">
+        <v>99</v>
       </c>
       <c r="C643" s="22" t="s">
         <v>1376</v>
@@ -27187,8 +27171,8 @@
       </c>
     </row>
     <row r="644" spans="1:11" ht="15">
-      <c r="A644">
-        <v>759</v>
+      <c r="A644" s="20">
+        <v>695.96</v>
       </c>
       <c r="C644" s="22" t="s">
         <v>1376</v>
@@ -27223,226 +27207,226 @@
     <sortCondition ref="F1:F355"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="93" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:I1">
-    <cfRule type="duplicateValues" dxfId="93" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E12 E14:E227">
-    <cfRule type="duplicateValues" dxfId="92" priority="1534"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="1534"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="91" priority="32"/>
     <cfRule type="duplicateValues" dxfId="90" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E338">
-    <cfRule type="duplicateValues" dxfId="88" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E414">
-    <cfRule type="duplicateValues" dxfId="87" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E415:E421 E423:E433 E2:E12 E14:E413">
-    <cfRule type="duplicateValues" dxfId="86" priority="47"/>
     <cfRule type="duplicateValues" dxfId="85" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E422">
-    <cfRule type="duplicateValues" dxfId="84" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E434">
-    <cfRule type="duplicateValues" dxfId="83" priority="27"/>
     <cfRule type="duplicateValues" dxfId="82" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E435">
-    <cfRule type="duplicateValues" dxfId="81" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E436:E438">
-    <cfRule type="duplicateValues" dxfId="79" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E440:E644">
-    <cfRule type="duplicateValues" dxfId="77" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E645:E1048576">
-    <cfRule type="duplicateValues" dxfId="75" priority="1532"/>
     <cfRule type="duplicateValues" dxfId="74" priority="1531"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="1532"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="1530"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E439:F439">
-    <cfRule type="duplicateValues" dxfId="72" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F298">
-    <cfRule type="duplicateValues" dxfId="70" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="76"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F336:F368 F311 F237:F269 F271 F274:F282 F284:F297 F313:F326 F299:F309 F2:F12 F328:F334 F370:F410 F14:F28 F30:F177 F412:F413">
-    <cfRule type="duplicateValues" dxfId="69" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F369">
-    <cfRule type="duplicateValues" dxfId="68" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F415:F433">
-    <cfRule type="duplicateValues" dxfId="67" priority="40"/>
     <cfRule type="duplicateValues" dxfId="66" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F434">
-    <cfRule type="duplicateValues" dxfId="65" priority="25"/>
     <cfRule type="duplicateValues" dxfId="64" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F435">
-    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F436">
-    <cfRule type="duplicateValues" dxfId="61" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F440:F644">
-    <cfRule type="duplicateValues" dxfId="59" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F645:F1048576">
-    <cfRule type="duplicateValues" dxfId="57" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F414:G414">
-    <cfRule type="duplicateValues" dxfId="56" priority="43"/>
     <cfRule type="duplicateValues" dxfId="55" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="54" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="duplicateValues" dxfId="53" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G94">
-    <cfRule type="duplicateValues" dxfId="52" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="64"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G127">
-    <cfRule type="duplicateValues" dxfId="51" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G143">
-    <cfRule type="duplicateValues" dxfId="50" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G146">
-    <cfRule type="duplicateValues" dxfId="49" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G154">
-    <cfRule type="duplicateValues" dxfId="48" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G274">
-    <cfRule type="duplicateValues" dxfId="47" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="83"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G284">
-    <cfRule type="duplicateValues" dxfId="46" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G285">
-    <cfRule type="duplicateValues" dxfId="45" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G286">
-    <cfRule type="duplicateValues" dxfId="44" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G290">
-    <cfRule type="duplicateValues" dxfId="43" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G293:G294 G297:G298">
-    <cfRule type="duplicateValues" dxfId="42" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="77"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G295">
-    <cfRule type="duplicateValues" dxfId="41" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G296">
-    <cfRule type="duplicateValues" dxfId="40" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G302">
-    <cfRule type="duplicateValues" dxfId="39" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G303">
-    <cfRule type="duplicateValues" dxfId="38" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="74"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G311">
-    <cfRule type="duplicateValues" dxfId="37" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G313">
-    <cfRule type="duplicateValues" dxfId="36" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G328">
-    <cfRule type="duplicateValues" dxfId="35" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G329">
-    <cfRule type="duplicateValues" dxfId="34" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G330">
-    <cfRule type="duplicateValues" dxfId="33" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G331">
-    <cfRule type="duplicateValues" dxfId="32" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G333">
-    <cfRule type="duplicateValues" dxfId="31" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="59"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G334">
-    <cfRule type="duplicateValues" dxfId="30" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G336">
-    <cfRule type="duplicateValues" dxfId="29" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G337">
-    <cfRule type="duplicateValues" dxfId="28" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G338">
-    <cfRule type="duplicateValues" dxfId="27" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G339:G340">
-    <cfRule type="duplicateValues" dxfId="26" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G346:G349">
-    <cfRule type="duplicateValues" dxfId="25" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G353">
-    <cfRule type="duplicateValues" dxfId="24" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G354">
-    <cfRule type="duplicateValues" dxfId="23" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G356:G361">
-    <cfRule type="duplicateValues" dxfId="22" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G407">
-    <cfRule type="duplicateValues" dxfId="21" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G408 G2:G12 G410 G14:G28 G30:G406 G412:G413">
-    <cfRule type="duplicateValues" dxfId="20" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G415:G423 G426:G433">
-    <cfRule type="duplicateValues" dxfId="19" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G424">
-    <cfRule type="duplicateValues" dxfId="17" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G425">
-    <cfRule type="duplicateValues" dxfId="15" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G434">
-    <cfRule type="duplicateValues" dxfId="13" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G435">
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G436">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
     <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G440:G644">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -28759,19 +28743,19 @@
   <autoFilter ref="C1:F58" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:B3 A4:A44 A49:A58">
-    <cfRule type="duplicateValues" dxfId="4" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6 B8:B9 B11:B12 B14:B15 B17:B18 B20:B21 B23:B24 B26:B27 B29:B30 B32:B33 B35:B36 B38:B39 B41:B42 B44:B45 B47:B48">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B207:C243 B1:C1 B622:C1048576 B277:C487">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="1" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
